--- a/noticias/piura/excel/noticias_piura_20261012_20261019.xlsx
+++ b/noticias/piura/excel/noticias_piura_20261012_20261019.xlsx
@@ -466,21 +466,21 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Otro ataque en colegio de Piura: escolar queda desfigurada</t>
+          <t>Dos recién nacidos fallecen por complicaciones de salud de alto riesgo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Un nuevo caso de violencia escolar causa preocupación en la provincia de Sullana. Una estudiante de quinto año de secundaria de un conocido colegio de Querecotillo resultó con el rostro seriamente herido luego de ser atacada con un cúter por una compañera durante el recreo el último viernes. PUEDES LEER ► Defensoría exige esclarecer presunta agresión entre dos escolares en Querecotillo Tras la difusión de la denuncia de los familiares de la agraviada a través de las redes sociales, el Módulo Defensorial de Sullana adscrita a la Oficina Defensorial de Piura solicitó a la Comisaría de Querecotillo realizar las diligencias necesarias para esclarecer los hechos denunciados. EL CASO Según denunciaron los familiares de la víctima, identificada con las iniciales H. T. N. , la agresión habría sido una represalia porque un día antes la menor exigió a la dirección del plantel y al tutor que intervinieran ante otro episodio de violencia en el que presuntamente también habría participado la misma estudiante. El padre de la agraviada relató que, tras reclamar medidas correctivas y solicitar que el caso fuera denunciado ante la UGEL, la presunta agresora, identificada como D. A. R., habría llegado a su vivienda acompañada de su madre para amenazar a su hija. La mañana del viernes, cuando la víctima bajaba las escaleras durante el recreo, habría sido interceptada por su compañera, quien sacó un cúter y le cortó el rostro. La intervención de otra estudiante habría evitado que la agresión alcanzara el cuello de la menor.</t>
+          <t>Dos familias de la provincia de Huancabamba atraviesan momentos de profundo dolor tras la muerte de sus recién nacidos en el Hospital de Chulucanas, adonde fueron trasladados de emergencia debido a complicaciones obstétricas de alto riesgo. Puedes Leer | En noviembre se definiría quién competirá con Hilbck Los trágicos sucesos ocurrieron los días 15 y 16 de octubre y han generado preocupación por la capacidad de respuesta del sistema sanitario en esta zona de la sierra piurana. El primer caso se registró el jueves 15 de octubre. Según la información difundida, el certificado de defunción indicaría que el bebé falleció dentro del útero materno antes del parto. La madre, identificada como H. Z. S., de 29 años, tuvo que ser ingresada a UCI. De acuerdo con los reportes, su evolución sería favorable. La segunda tragedia ocurrió el viernes 16 de octubre. En esta ocasión, el recién nacido falleció pocos minutos después de nacer. Según las primeras informaciones, el bebé presentaba hidrocefalia, mientras que la madre padecía preeclampsia severa. Pese a las maniobras realizadas por el personal médico, no fue posible salvarle la vida. Mira También | Estafas virtuales azotan a los piuranos Ambos casos fueron atendidos inicialmente en el establecimiento de salud Jesús Guerrero Cruz, de Huancabamba, que dispuso las referencias de emergencia hacia Chulucanas ante la complejidad de los cuadros clínicos y la necesidad de atención especializada. Los restos de los pequeños fueron trasladados el sábado 17 de octubre a Huancabamba para recibir sepultura junto a sus familiares.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/otro-ataque-en-colegio-de-piura-escolar-queda-desfigurada/</t>
+          <t>https://eltiempo.pe/local/dos-recien-nacidos-fallecen-por-complicaciones-de-salud-de-alto-riesgo/</t>
         </is>
       </c>
     </row>
@@ -491,113 +491,105 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>La solidaridad e innovación serán claves en pescadores artesanales para enfrentar El Niño</t>
+          <t>Jorge Chávez: Latam se pronuncia tras incendio de ala de avión de vuelo Lima-Piura</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Indicó que la pesca en Piura es un sector vital para su economía local y además, representa el 20% del Producto Bruto Interno (PBI) pesquero marino del Perú y sostiene cerca de 49,000 empleos directos e indirectos.
-Refirió que la pandemia del Covid-19 dejó aprendizajes invaluables sobre la capacidad de respuesta de la pesca artesanal, hoy sistematizados en un estudio y publicados en la prestigiosa revista científica Journal of Rural Studies.
-En ese sentido, subrayó que los resultados del estudio demuestran que la flexibilidad, la solidaridad colectiva y el trabajo doméstico de las familias fueron las verdaderas fuerzas que mantuvieron la seguridad alimentaria y la operatividad del sector en el norte peruano.
-"Las respuestas comunitarias no fueron meras reacciones de supervivencia, sino muestras de una profunda capacidad de gobernanza local" , destacó Liza Meza, autora principal del referido estudio.
-"Estas capacidades no deben ser ignoradas.
-El diseño de cualquier hoja de ruta para enfrentar los inminentes choques climáticos globales, como El Niño, debe partir del reconocimiento de la autogestión comunitaria y transitar hacia políticas de auténtica co-producción y respaldo estatal" , enfatizó.
-El estudio titulado: “ Illuminating small-scale fishers’ adaptation strategies to COVID-19: Navigating the challenges in Peruvian coastal communities ” (Iluminando las estrategias de adaptación de los pescadores artesanales al COVID-19: navegando los desafíos en las comunidades costeras del Perú) muestra cómo 12 comunidades pesqueras artesanales de la región Piura desarrollaron respuestas inmediatas antes una situación crítica a nivel sanitario, social y económico.
-Pilares de resiliencia comunitaria El estudio identificó cuatro grandes bloques de estrategias adaptativas aplicadas en la costa norte: 1) la reinvención de las ventas y aseguramiento del sustento familiar, 2) la adaptación de los trabajos de pesca y protección a los adultos mayores, 3) la autogestión para la protección comunitaria, cooperación y solidaridad y 4) la agregación de valor a nivel doméstico y salud local Según el último reporte de la Organización Meteorológica Mundial (OMM) advierte que el próximo Fenómeno de El Niño generará condiciones climáticas extremas y graves impactos sobre los medios de vida de las poblaciones más vulnerables del litoral.
-Más en Andina: ???? La inversión minera en el Perú alcanzó los US$ 4,117 millones entre enero y julio de 2026, un crecimiento de 45% frente al mismo periodo de 2025, cuando sumó US$ 2,389 millones, según el Ministerio de Energía y Minas (Minem).
-?? https://t.co/PyWQ1EnO3w https://t.co/fMfSzTufGV (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 13, 2026</t>
+          <t>Mediante un comunicado, la aerolínea señaló que el evento técnico imprevisto motivó la decisión de desembarcar preventivamente a los pasajeros que iban a bordo del vuelo LA2302, con el objetivo de priorizar su seguridad.
+Latam precisó que sus equipos brindan asistencia a los afectados y coordinan su reubicación en otros vuelos a la brevedad posible .
+Evaluarán las circunstancias del incidente La compañía indicó que las circunstancias de lo ocurrido serán materia de una evaluación técnica, de acuerdo con los procedimientos correspondientes.
+Asimismo, lamentó los inconvenientes ocasionados a los pasajeros y reafirmó su compromiso con la seguridad aérea .
+" LATAM Airlines Perú lamenta los inconvenientes ocasionados y reafirma su compromiso con la seguridad aérea, valor esencial de todas sus operaciones ", subrayó en su comunicado.
+Lee también: EsSalud atendió a más de 130 devotos durante segundo recorrido del Señor de los Milagros El incidente fue registrado por diversos usuarios y viralizados en diversas plataformas de internet como X (antes Twitter).
+De acuerdo a las imágenes, antes de que el avión se encuentre en el aire, se observó la presencia de humo en la ala izquierda, que luego comenzó a incendiarse segundos previos que despegara.
+Hasta el momento, se desconoce la causa que haya generado este incidente, el cual alarmó a cientos de pasajeros y usuarios que estaban en el Aeropuerto Internacional Jorge Chávez.
+La entidad informó que el avión será sometido a evaluación técnica.
+Más en Andina La obra que permitirá conectar el Metropolitano con la estación Grau de la Línea 1 del Metro de Lima estará ejecutada al 100 % durante la primera semana de diciembre de este año, informó Carlos Peña, director de Infraestructura de la ATU.??https://t.co/aCK8zX1RXN https://t.co/MpjdB4OkQl (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 18, 2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-la-solidaridad-e-innovacion-seran-claves-pescadores-artesanales-para-enfrentar-nino-1096431.aspx</t>
+          <t>https://andina.pe/agencia/noticia-jorge-chavez-latam-se-pronuncia-tras-incendio-ala-avion-vuelo-limapiura-1096488.aspx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Resultados ONPE en región Piura al 98.347 %: aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
+          <t>En noviembre se definiría quién competirá con Hilbck</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>El domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación región Piura según la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Los candidatos a gobernador Guillermo La Torre (Podemos) y Santiago Paz (Somos Perú) esperarían hasta noviembre para conocer cuál de ellos competirá con Reynaldo Hilbck de Alianza para el Progreso (APP) en la segunda vuelta. Puedes Leer | Evacuación preventiva para evitar desastres por El Niño Esto debido al tiempo que tomaría acatar el fallo del Jurado Nacional de Elecciones (JNE), que podría ordenar el recuento de votos o aplicar el protocolo de acta siniestrada tras lo sucedido en San Juan de Bigote. Así lo consideró el abogado de APP, Juan Carlos Álamo, que planteó la nulidad de la elección. Como se informó, el JNE revocó la decisión del Jurado Electoral Especial de Morropón de anular la elección por la violencia del 4 de octubre que acabó con la destrucción de actas y cédulas. Hasta el momento, el JNE aún no había notificado la resolución. Fallo Garantista Según Álamo, el JNE ha emitido un fallo garantista para que el JEE Morropón revise el material. “Hay que tener cuidado en decir quién ganó la elección. El JEE Morropón puede tener a la vista el material, pero también puede llegar a la conclusión de no es suficiente y quizás no alcanza el 50% más uno [para que la elección sea válida] o que el material es imposible de visualizar [...] El JNE va a pedir que ese material, que está en la Fiscalía, se devuelva al Jurado”, manifestó Álamo. El letrado precisa que este material no llegó al JEE Morropón, sino que quedó en poder de la Fiscalía para las investigaciones del caso. Debido a ello, el JEE Morropón anuló la elección en primera instancia tomando como referencia los informes de ONPE y de la Fiscalía tras los hechos. La Hora se comunicó con el personero de Somos Perú, Alex Ochoa, quien dijo que San Juan de Bigote definirá quién pasa a segunda vuelta, ya que Somos Perú tendría una ventaja por mesa de 100 votos sobre Podemos.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/resultados-en-piura-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
+          <t>https://eltiempo.pe/local/en-noviembre-se-definiria-quien-competira-con-hilbck/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Agricultores de Sechura se cansaron e irán al paro</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la región de Piura</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Una grave crisis golpea a los pequeños agricultores del Bajo Piura y Sechura. La falta de financiamiento estatal, las dificultades para comercializar sus cosechas y el escaso avance de las obras de prevención ante el Fenómeno El Niño mantienen en incertidumbre a más de 30 mil productores, denunció Máximo Valdiviezo , presidente de la Asociación de Productores Agrarios del Valle de Sechura. El dirigente cuestionó el programa de compra estatal de arroz, al que calificó de “ engaño ”, debido a que, según indicó, los recursos necesarios aún no habrían sido transferidos por el Ministerio de Economía y Finanzas (MEF). Valdiviezo señaló que, de los S/ 15 millones anunciados inicialmente para Piura, se habría reducido el presupuesto a aproximadamente S/ 8,8 millones para adquirir 57 mil sacos de arroz. “En el valle de Sechura ningún agricultor le ha vendido un solo saco de arroz al Estado” , afirmó, reclamando respuestas concretas del Gobierno. Asimismo, informó que los gremios agrarios impulsan un proyecto de ley para proteger la producción nacional de arroz, algodón, maíz y menestras, además de exigir el fortalecimiento de la franja de precios frente a las importaciones. La preocupación también alcanza las obras de prevención. Según el dirigente, de los 77 kilómetros proyectados para intervenir en el río Piura, solo se habría avanzado entre dos y tres kilómetros. A ello se suman los drenes colmatados, la falta de combustible para su mantenimiento y el deterioro de las trochas carrozables. “Soy sincero, no estamos preparados”, advirtió.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Piura, según el conteo oficial de la ONPE al 98.442% , arroja el siguiente resultado (actualizado el 19/10/2026, a las 11:22.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/agricultores-de-sechura-se-cansaron-e-iran-al-paro/</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-region-de-piura-noticia/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mindef: Ejército fortalece sus comunicaciones para respuesta rápida ante fenómeno El Niño</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Morropón (Piura)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Estas comunicaciones permitirán mantener el contacto con las Compañías de Intervención Rápida para Desastres (CIRD), especialmente en comunidades que podrían quedar aisladas.
-Así, se busca agilizar la toma de decisiones y facilitar el desplazamiento de personal, equipos y ayuda humanitaria hacia las zonas afectadas.
-Lea también: Enfen: lluvias aumentarán más de lo normal en la costa y la sierra hasta fines de 2026 Las pruebas estuvieron a cargo de la I División de Ejército y el Batallón de Comunicaciones N° 111, que estableció enlaces con cuatro organizaciones militares: el Cuartel General de la I División de Ejército y el Agrupamiento de Artillería Inclán, en Piura; la 9ª Brigada Blindada, en Tumbes; y la 1ª Brigada de Protección de la Amazonía, en Amazonas.
-Para ello, se emplearon equipos de radiocomunicación Hytera y plataformas tecnológicas que permiten intercambiar información entre las unidades militares.
-Los ejercicios sirvieron para comprobar su funcionamiento y evaluar la continuidad y confiabilidad de las comunicaciones ante situaciones de emergencia.
-También se evaluó la coordinación entre los mandos militares y las unidades encargadas de intervenir ante desastres , a fin de detectar posibles dificultades y optimizar el uso de los equipos disponibles en escenarios de riesgo.
-Lea también: Ministerio de Defensa presenta despliegue a gran escala del Ejército ante fenómeno El Niño Estas acciones forman parte de las medidas impulsadas por el Ministerio de Defensa para fortalecer la capacidad operativa de las Fuerzas Armadas ante el FEN , mediante sistemas de comunicación que permitan coordinar intervenciones oportunas y facilitar el despliegue de recursos en las zonas afectadas.
-Dato El Gobierno informó que las regiones de Piura y Tumbes estarán bajo la responsabilidad del ministro de Defensa, Rafael Belaunde.
-Más en Andina: El papa León XIV saludó a miles de personas congregadas en la plaza de San Pedro del Vaticano este domingo, sonriendo, y afirmó que retomará el trabajo "progresivamente" después de su operación por un cáncer de pulmón.??https://t.co/PG9GTIpJkO https://t.co/4WYK89RM0N (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 18, 2026</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Morropón, según el conteo oficial de la ONPE al 94.758% , arroja el siguiente resultado (actualizado el 19/10/2026, a las 11:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-mindef-ejercito-fortalece-sus-comunicaciones-para-respuesta-rapida-ante-fenomeno-nino-1096387.aspx</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-morropon-piura-noticia/</t>
         </is>
       </c>
     </row>
@@ -608,14 +600,145 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Senamhi: fenómeno El Niño entra en fase extraordinaria y favorecerá lluvias extremas</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>La afirmó que esta condición podría prolongarse, por lo menos, hasta febrero y coincidir con el periodo de lluvias más frecuentes en el país.
+Por ello, pidió mantener actualizada la información meteorológica y adoptar medidas preventivas ante los posibles impactos del evento climático.
+Lea también: El Niño Costero: ¿Qué indicadores señalan que es extraordinario y cómo impactaría en Perú? En declaraciones a canal N, Ávalos explicó que los episodios de El Niño extraordinario se caracterizan por un calentamiento excepcional del mar frente a la costa norte peruana, situación que favorece la disponibilidad de humedad en la atmósfera y puede desencadenar precipitaciones de gran intensidad.
+“Un Niño extraordinario es cuando supera los 3.5 grados de anomalía del mar.
+Este evento está por encima de los 4 grados”, precisó.
+Lea también: Senamhi: Niño Costero extraordinario provocará picos de 40 °C en la costa norte La especialista recordó que los antecedentes de una intensidad comparable corresponden a los eventos de 1982-1983 y 1997-1998, periodos en los que se registraron lluvias intensas y frecuentes en diferentes zonas del país.
+Lluvias podrían alcanzar entre 250 y 300 milímetros Para dimensionar la magnitud de las precipitaciones que podrían presentarse en el norte peruano, Ávalos explicó que, en condiciones normales, durante el periodo de mayor lluvia se pueden registrar acumulados de entre 20 y 30 milímetros, mientras que en un contexto de El Niño los valores podrían alcanzar entre 250 y 300 milímetros.
+La especialista utilizó un ejemplo para explicar el volumen de agua que representan estas precipitaciones: una lluvia de 300 milímetros equivale a acumular aproximadamente 300 litros de agua por metro cuadrado.
+Esta cantidad de lluvia, especialmente si se concentra en periodos cortos o se mantiene de manera persistente, puede incrementar el riesgo de inundaciones, desbordes y activación de quebradas.
+Lea también: Enfen: El Niño extraordinario ha provocado el adelanto de las lluvias en la costa norte Ávalos remarcó que el peligro no se limita a las altas temperaturas que ya se registran en la costa peruana, sino que comprende principalmente las precipitaciones intensas y sus efectos sobre las poblaciones asentadas en zonas vulnerables.
+Costa norte y central, entre las zonas expuestas La especialista indicó que las proyecciones presentadas durante la entrevista muestran condiciones favorables para lluvias por encima de lo normal desde Tumbes y Piura hasta sectores de la costa central.
+Explicó que la franja costera es una de las áreas más expuestas debido al calentamiento del mar.
+En contraste, al otro lado de la cordillera se prevén condiciones más secas, que podrían favorecer la ocurrencia de sequías intensas e incendios forestales.
+Ávalos también alertó sobre la vulnerabilidad de las quebradas de la vertiente occidental de los Andes, que pueden activarse ante precipitaciones intensas.
+En ese contexto, mencionó los sectores de Chosica y Chaclacayo, en Lima este, como zonas cercanas a la capital donde podrían observarse cambios importantes asociados a las lluvias y a la activación de quebradas.
+La especialista recordó los efectos de las precipitaciones registradas durante el fenómeno El Niño costero de 2017 y advirtió que el escenario actual corresponde, según sus declaraciones, a una intensidad extraordinaria.
+Senamhi incorporará nuevos radares meteorológicos Como parte de las herramientas para mejorar el seguimiento de este evento, Ávalos destacó la incorporación de dos estaciones con radar meteorológico, ubicadas en Piura e Ica, que permitirán estudiar las características de las precipitaciones asociadas al fenómeno.
+Explicó que estos equipos proporcionan información más detallada sobre las nubes en desplazamiento, el tipo de gotas y la concentración de agua que transportan los sistemas nubosos.
+Esta información permitirá conocer mejor la tipología de las lluvias y contribuirá a fortalecer los servicios de alerta temprana, con el objetivo de disponer de datos más precisos para las acciones de prevención y respuesta.
+La especialista consideró que esta nueva tecnología representa un avance para el Senamhi y para el país, en un contexto en el que resulta fundamental anticipar los posibles impactos de las precipitaciones.
+Preparación ante los posibles impactos Ante el escenario previsto, Ávalos insistió en la importancia de contar con información actualizada y adoptar medidas de seguridad, especialmente en las localidades expuestas a inundaciones y activación de quebradas.
+Los antecedentes de anteriores episodios extraordinarios muestran que las lluvias pueden ser intensas, frecuentes y persistentes, lo que dificulta las labores de recuperación cuando los daños se producen de manera sucesiva.
+Por ello, la especialista subrayó la necesidad de que las autoridades y la población estén preparadas antes del inicio de las lluvias más intensas, con especial atención a los sectores vulnerables de la costa norte y central.
+Más en Andina: ?? El 17 de octubre se celebra en Perú el Día de las Áreas Naturales Protegidas.
+¿Cómo aportan al desarrollo sostenible del país? https://t.co/RyKvBjrH9W https://t.co/LPvFs1CNTy (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 16, 2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-senamhi-fenomeno-nino-entra-fase-extraordinaria-y-favorecera-lluvias-extremas-1096225.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46314</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Estafas virtuales azotan a los piuranos</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>La delincuencia cambia de rostro y ahora también golpea a través de las pantallas. Los delitos informáticos contra el patrimonio se han convertido en una de las principales preocupaciones en Piura, al registrar un incremento del 27.3% en los primeros nueve meses de este año, en comparación con el mismo periodo del 2025, de acuerdo con las estadísticas del Observatorio Nacional de Seguridad Ciudadana. Puedes Leer | Otro ataque en colegio de Piura: escolar queda desfigurada Entre enero y setiembre del 2026 se reportaron 1,279 denuncias por delitos informáticos, frente a las 930 registradas durante el mismo periodo del año pasado. Esta tendencia evidencia el crecimiento de las modalidades delictivas que pueden afectar económicamente a los ciudadanos mediante engaños y operaciones fraudulentas en entornos digitales. El panorama de la seguridad ciudadana también muestra un aumento en otras modalidades delictivas. Los hurtos alcanzaron las 6,775 denuncias, un 9.4% más que el año pasado, mientras que las lesiones sumaron 2,364 casos, con un incremento del 9%. Asimismo, los delitos de peligro común llegaron a 1,448 denuncias, cifra superior en 6.1% a la registrada en el mismo periodo anterior. Piura en cifras de la delincuencia En total, Piura acumuló 29,063 denuncias por diferentes delitos hasta setiembre, lo que representa una reducción del 5.2% frente a las 30,666 registradas en igual periodo del año pasado. Pese a esta disminución general, el incremento de determinadas modalidades delictivas mantiene en alerta a la población. Mira También | Defensoría exige esclarecer presunta agresión entre dos escolares en Querecotillo Según el reporte, Piura se ubica entre las regiones con mayor cantidad de denuncias del país, con cifras que la colocan en los primeros lugares de las estadísticas nacionales. En cuanto a las estafas, se contabilizaron 1,142 denuncias, un 3.6% menos que en el periodo comparado. Sin embargo, la región ocupa el quinto lugar nacional por este delito, lo que refleja la persistencia de los engaños que afectan el patrimonio de las víctimas. Extorsiones siguen en la mira Otro indicador que preocupa es la extorsión. Aunque las denuncias descendieron un 59.5%, al pasar de 2,361 en el mismo periodo del 2025 a 957 en los primeros nueve meses del 2026, Piura continúa en el cuarto lugar a nivel nacional.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/estafas-virtuales-azotan-a-los-piuranos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
         <v>46313</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Resultados ONPE en región Piura al 98.347 %: aquí el conteo oficial de las Elecciones Regionales y Municipales 2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>El domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y duraron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. Los ciudadanos que fueron elegidos miembros de mesa (tres titulares y seis suplentes) asistieron a sus locales de votación a las 6 a.m., con la finalidad de instalar las mesas de sufragio y garantizar que los comicios se desarrollen sin contratiempos ni demoras. Los que cumplieron con esta función recibirán una compensación económica de S/ 165, monto equivalente al 3% de una UIT, más un día de descanso remunerado y no compensable (en caso complete las jornadas de capacitación). La votación región Piura según la ONPE: ¿Cuál es la multa por no votar? Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. ¿Debo pagar multa si no cumplo con mi función de miembro de mesa? Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/resultados-en-piura-de-las-elecciones-regionales-y-municipales-2026-segun-conteo-oficial-de-la-onpe-erm-2026-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Piura: Comando liderado por Fiscalía incauta más de USD 619 000 en mercancías ilícitas</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>El resultado del trabajo coordinado en materia de prevención, control y represión de los delitos aduaneros, contrabando y piratería en los principales puntos estratégicos y vías de transporte de la región.
+Intervenciones de mayor impacto Entre los operativos más relevantes ejecutados en la jurisdicción, destacan los siguientes.
+-Mercurio para minería ilegal: Incautación de 241.55 kilos de mercurio en el distrito de Suyo, insumo clave destinado a la minería informal e ilegal, valorizado en US$ 397 818.36.
+-Agroquímicos prohibidos: Decomiso de 9073 unidades de plaguicidas agrícolas conteniendo sustancias tóxicas de uso prohibido (Paraquat y Clorpirifos) en la localidad de Ocoto Alto (Tambogrande), por un valor de US$ 154 550.00.
+-Contrabando de cigarrillos: Hallazgo de 140 000 cigarrillos de procedencia extranjera que carecían de documentación legal en un terminal terrestre de la ciudad, valorizados en US$ 58 800.00.
+-Municiones camufladas: Decomiso de 8 800 cartuchos de munición calibre 9 mm Luger, detectados en la modalidad de encomienda en una empresa de transportes.
+Las instituciones integrantes del COR Piura - entre ellas el Ministerio Público de Piura y Sullana, Sunat, PNP, FF.
+AA, Indecopi, Migraciones, Sutran, Produce, Osiptel, Osinergmin, la Sociedad Nacional de Industrias y el Gobierno Regional de Piura - continuarán intensificando las acciones operativas para neutralizar el comercio ilegal y proteger la seguridad ciudadana y la economía nacional.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-piura-comando-liderado-fiscalia-incauta-mas-usd-619-000-mercancias-ilicitas-1096386.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>El Niño:Midagri lideró segunda sesión multisectorial para reforzar preparación y respuesta</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Durante la sesión, se aprobó la distribución de responsabilidades territoriales entre los ministros para fortalecer la coordinación y atención de posibles emergencias en las regiones priorizadas.
 Con el objetivo de fortalecer la capacidad de respuesta del Estado, participaron los ministros de Economía y Finanzas, Vivienda, Construcción y Saneamiento, Defensa, Salud y Transportes y Comunicaciones.
@@ -630,27 +753,27 @@
 Durante la reunión también se revisaron los avances de las intervenciones en marcha y las acciones que desarrollarán los sectores, de acuerdo con sus competencias, para atender posibles emergencias y proteger a la población, la infraestructura y las actividades productivas.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-el-ninomidagri-lidero-segunda-sesion-multisectorial-para-reforzar-preparacion-y-respuesta-1096398.aspx</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B12" s="2" t="n">
         <v>46313</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Gremio exportador: pymes agroexportadoras requieren financiamiento flexible ante El Niño</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Refirió que la situación se está complicando en algunos cultivos y la menor producción reduce la oferta que en ciertos casos, afecta las características organolépticas de la fruta, dificultando el cumplimiento de los requerimientos de los compradores internacionales.
 “Esto repercute en los ingresos y el empleo en las labores de cosecha y las plantas de empaque (packing).
@@ -671,166 +794,76 @@
 ?? https://t.co/PyWQ1EnO3w https://t.co/fMfSzTufGV (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 13, 2026</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-gremio-exportador-pymes-agroexportadoras-requieren-financiamiento-flexible-ante-nino-1096414.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>46313</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Piura: Comando liderado por Fiscalía incauta más de USD 619 000 en mercancías ilícitas</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>El resultado del trabajo coordinado en materia de prevención, control y represión de los delitos aduaneros, contrabando y piratería en los principales puntos estratégicos y vías de transporte de la región.
-Intervenciones de mayor impacto Entre los operativos más relevantes ejecutados en la jurisdicción, destacan los siguientes.
--Mercurio para minería ilegal: Incautación de 241.55 kilos de mercurio en el distrito de Suyo, insumo clave destinado a la minería informal e ilegal, valorizado en US$ 397 818.36.
--Agroquímicos prohibidos: Decomiso de 9073 unidades de plaguicidas agrícolas conteniendo sustancias tóxicas de uso prohibido (Paraquat y Clorpirifos) en la localidad de Ocoto Alto (Tambogrande), por un valor de US$ 154 550.00.
--Contrabando de cigarrillos: Hallazgo de 140 000 cigarrillos de procedencia extranjera que carecían de documentación legal en un terminal terrestre de la ciudad, valorizados en US$ 58 800.00.
--Municiones camufladas: Decomiso de 8 800 cartuchos de munición calibre 9 mm Luger, detectados en la modalidad de encomienda en una empresa de transportes.
-Las instituciones integrantes del COR Piura - entre ellas el Ministerio Público de Piura y Sullana, Sunat, PNP, FF.
-AA, Indecopi, Migraciones, Sutran, Produce, Osiptel, Osinergmin, la Sociedad Nacional de Industrias y el Gobierno Regional de Piura - continuarán intensificando las acciones operativas para neutralizar el comercio ilegal y proteger la seguridad ciudadana y la economía nacional.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-piura-comando-liderado-fiscalia-incauta-mas-usd-619-000-mercancias-ilicitas-1096386.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>46313</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Evacuación preventiva para evitar desastres por El Niño</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>nuevo caso de violencia escolar causa preocupación en la provincia de Sullana. Una estudiante de quinto año de secundaria de un conocido colegio de Querecotillo resultó con el rostro seriamente herido luego de ser atacada con un cúter por una compañera durante el recreo el último viernes. Tras la difusión de la denuncia de los familiares de la agraviada a través de las redes sociales, el Módulo Defensorial de Sullana adscrita a la Oficina Defensorial de Piura solicitó a la Comisaría de Querecotillo realizar las diligencias necesarias para esclarecer los hechos denunciados. EL CASO Según denunciaron los familiares de la víctima, identificada con las iniciales H. T. N. , la agresión habría sido una represalia porque un día antes la menor exigió a la dirección del plantel y al tutor que intervinieran ante otro episodio de violencia en el que presuntamente también habría participado la misma estudiante. El padre de la agraviada relató que, tras reclamar medidas correctivas y solicitar que el caso fuera denunciado ante la UGEL, la presunta agresora, identificada como D. A. R., habría llegado a su vivienda acompañada de su madre para amenazar a su hija. La mañana del viernes, cuando la víctima bajaba las escaleras durante el recreo, habría sido interceptada por su compañera, quien sacó un cúter y le cortó el rostro. La intervención de otra estudiante habría evitado que la agresión alcanzara el cuello de la menor.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/evacuacion-preventiva-para-evitar-desastres-por-el-nino/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>46313</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Defensoría exige esclarecer presunta agresión entre dos escolares en Querecotillo</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>La Defensoría del Pueblo solicitó al Ministerio Público realizar una investigación exhaustiva para esclarecer los hechos de violencia que involucrarían a dos estudiantes de la institución educativa José María Raygada Gallo, ubicada en el distrito de Querecotillo, provincia de Sullana, en Piura. A través de la Oficina Defensorial de Piura, en coordinación con el Módulo Defensorial de Sullana, la entidad viene efectuando acciones de seguimiento para garantizar la protección de los derechos de ambas adolescentes. Según informó la fiscal a cargo del caso, en las primeras diligencias se conoció que las dos escolares se habrían agredido mutuamente. La investigación cuenta con un certificado médico legal y está pendiente la revisión de videos que permitan esclarecer las circunstancias del incidente y determinar las responsabilidades correspondientes. Ante esta situación, la Defensoría pidió al Ministerio Público profundizar las investigaciones, respetando los derechos de ambas menores de edad y garantizando que el caso sea evaluado conforme a ley. Además, exhortó a la UGEL Sullana y a la dirección del colegio a activar los protocolos de atención frente a la violencia escolar, implementar las medidas de protección necesarias y asegurar que ambas estudiantes puedan continuar sus estudios en un ambiente seguro. La institución defensorial indicó que continuará supervisando las actuaciones de las entidades competentes para velar por la integridad de las adolescentes, su protección oportuna y la convivencia adecuada dentro de la comunidad educativa.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/defensoria-exige-esclarecer-presunta-agresion-entre-dos-escolares-en-querecotillo/</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>46312</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Almacenes adelantados deben contar con todos los protocolos para conservar bienes de ayuda humanitaria</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>El Gobierno Regional realiza coordinaciones con los 17 municipios, con los que tiene convenios para el funcionamiento de los almacenes adelantados, a efectos que mejoren las condiciones de la infraestructura, ambiente y seguridad de los mismos. Todo esto, debido a que dichos locales deben garantizar las condiciones de la reserva hasta su uso, que consiste en 113.29 toneladas de bienes de ayuda humanitaria que les ha entregado el GORE. Fuentes de la Oficina Regional de Seguridad y Defensa Nacional, señalaron que en una reciente jornada de supervisión de estos depósitos, se detectaron varias deficiencias, por lo que se notificó documentadamente a los gobiernos locales apara que levanten las observaciones, en cuyo proceso, los municipios, se encuentran abocados según han reportado a la Orsydn. Los almacenes adelantados garantizarán una rápida respuesta ante una emergencia.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/almacenes-adelantados-deben-contar-con-todos-los-protocolos-para-conservar-bienes-de-ayuda-humanitaria/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>JNE declara fundado pedido de nulidad de elecciones en San Juan de Bigote</t>
+          <t>La solidaridad e innovación serán claves en pescadores artesanales para enfrentar El Niño</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>El Jurado Nacional de Elecciones (JNE) declaró fundado el pedido relacionado con las elecciones en el distrito de San Juan de Bigote , ubicado en la provincia de Morropón, región Piura. La decisión fue celebrada por el candidato Santiago Paz, quien destacó que el resultado representa un avance en la defensa de la voluntad popular. A través de sus redes sociales, el candidato de Somos Perú, Santiago Paz, manifestó que el pronunciamiento responde a las protestas y acciones emprendidas por ciudadanos que exigían que se respete el resultado de los comicios. ¿Qué decidió el JNE sobre las elecciones en San Juan de Bigote? La publicación del Jurado Nacional de Elecciones indica que el pedido fue declarado fundado. Este pronunciamiento está relacionado con la controversia surgida por la anulación de los comicios regionales y municipales en San Juan de Bigote , una localidad de la provincia de Morropón que se convirtió en escenario de reclamos ciudadanos. De acuerdo con la información difundida, el caso llegó a esta instancia electoral después de que se cuestionara la resolución que había dispuesto anular las elecciones en el distrito. Frente a esa situación, se presentó una apelación para que el organismo electoral revisara la decisión. Para conocer la información institucional, los ciudadanos pueden consultar el portal del Jurado Nacional de Elecciones , donde se publican documentos y pronunciamientos vinculados con sus competencias. Santiago Paz celebra la decisión del organismo electoral Tras conocerse el pronunciamiento, el candidato Santiago Paz expresó su satisfacción y sostuvo que la decisión representa una victoria para los ciudadanos de Piura, más allá de las diferencias partidarias. “Este es el resultado de la lucha de todos los piuranos. San Juan de Bigote podrá ver el resultado de sus elecciones. Hemos logrado que la voluntad popular se respete. Que oigan nuestra voz”, manifestó en su publicación. El representante de Somos Perú también remarcó que, desde su perspectiva, el resultado no debe atribuirse exclusivamente a una organización política o a una candidatura, sino al reclamo de quienes participaron en las movilizaciones. “Este logro no es por Somos Perú, ni por Santiago Paz, este logro es por la democracia de nuestra región y de nuestro país”, señaló. Sus declaraciones reflejan la posición del candidato frente a la controversia electoral. Sin embargo, el alcance jurídico de la decisión deberá determinarse a partir de los fundamentos y disposiciones que figuren en el documento oficial del JNE. Las protestas ciudadanas por el proceso electoral en Piura La controversia en San Juan de Bigote generó expresiones de rechazo entre ciudadanos que exigían una respuesta de las autoridades electorales. Según lo expresado por Santiago Paz, las movilizaciones fueron parte de una protesta que buscaba defender la voluntad de los electores y cuestionar la anulación de los comicios. El candidato afirmó que las manifestaciones trascendieron los intereses de una agrupación política y que tuvieron como principal objetivo exigir que las instituciones del Estado atendieran el reclamo de la población. “Independientemente del partido político, esta es una voz de protesta que fue escuchada”, expresó en redes sociales. Asimismo, sostuvo que los ciudadanos estaban cansados de determinadas prácticas políticas y consideró que las movilizaciones debían quedar registradas como una muestra de participación democrática en la región. “Que estas marchas marquen una historia, que cuenten que el día que se quiso torcer la voluntad, hubo piuranos y piuranas que salimos, caminamos, protestamos y luchamos en las calles por el respeto a la democracia de nuestra región”, indicó. Estas afirmaciones corresponden a la valoración política de Santiago Paz sobre el conflicto. Para determinar las razones que motivaron la anulación inicial y los argumentos aceptados por el organismo electoral, será necesario revisar los documentos oficiales del expediente. ¿Qué pasará ahora con las elecciones en San Juan de Bigote? El siguiente paso dependerá de lo establecido en la resolución del Jurado Nacional de Elecciones. El documento permitirá conocer qué efectos tendrá la decisión sobre el proceso electoral y qué acciones deberán ejecutar las autoridades competentes. En particular, será importante determinar si corresponde restablecer los resultados electorales, realizar alguna actuación complementaria o cumplir con otras disposiciones. Por ahora, no es posible confirmar cuál de esos escenarios corresponde al caso sin contar con el contenido íntegro del fallo. Los ciudadanos pueden seguir las actualizaciones mediante el portal oficial del JNE y las publicaciones institucionales relacionadas con el proceso. También pueden consultar la información de la Oficina Nacional de Procesos Electorales (ONPE) , entidad encargada de organizar y ejecutar los procesos electorales dentro de sus competencias.</t>
+          <t>Indicó que la pesca en Piura es un sector vital para su economía local y además, representa el 20% del Producto Bruto Interno (PBI) pesquero marino del Perú y sostiene cerca de 49,000 empleos directos e indirectos.
+Refirió que la pandemia del Covid-19 dejó aprendizajes invaluables sobre la capacidad de respuesta de la pesca artesanal, hoy sistematizados en un estudio y publicados en la prestigiosa revista científica Journal of Rural Studies.
+En ese sentido, subrayó que los resultados del estudio demuestran que la flexibilidad, la solidaridad colectiva y el trabajo doméstico de las familias fueron las verdaderas fuerzas que mantuvieron la seguridad alimentaria y la operatividad del sector en el norte peruano.
+"Las respuestas comunitarias no fueron meras reacciones de supervivencia, sino muestras de una profunda capacidad de gobernanza local" , destacó Liza Meza, autora principal del referido estudio.
+"Estas capacidades no deben ser ignoradas.
+El diseño de cualquier hoja de ruta para enfrentar los inminentes choques climáticos globales, como El Niño, debe partir del reconocimiento de la autogestión comunitaria y transitar hacia políticas de auténtica co-producción y respaldo estatal" , enfatizó.
+El estudio titulado: “ Illuminating small-scale fishers’ adaptation strategies to COVID-19: Navigating the challenges in Peruvian coastal communities ” (Iluminando las estrategias de adaptación de los pescadores artesanales al COVID-19: navegando los desafíos en las comunidades costeras del Perú) muestra cómo 12 comunidades pesqueras artesanales de la región Piura desarrollaron respuestas inmediatas antes una situación crítica a nivel sanitario, social y económico.
+Pilares de resiliencia comunitaria El estudio identificó cuatro grandes bloques de estrategias adaptativas aplicadas en la costa norte: 1) la reinvención de las ventas y aseguramiento del sustento familiar, 2) la adaptación de los trabajos de pesca y protección a los adultos mayores, 3) la autogestión para la protección comunitaria, cooperación y solidaridad y 4) la agregación de valor a nivel doméstico y salud local Según el último reporte de la Organización Meteorológica Mundial (OMM) advierte que el próximo Fenómeno de El Niño generará condiciones climáticas extremas y graves impactos sobre los medios de vida de las poblaciones más vulnerables del litoral.
+Más en Andina: ???? La inversión minera en el Perú alcanzó los US$ 4,117 millones entre enero y julio de 2026, un crecimiento de 45% frente al mismo periodo de 2025, cuando sumó US$ 2,389 millones, según el Ministerio de Energía y Minas (Minem).
+?? https://t.co/PyWQ1EnO3w https://t.co/fMfSzTufGV (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 13, 2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/jne-declara-fundado-pedido-de-nulidad-de-elecciones-en-san-juan-de-bigote/</t>
+          <t>https://andina.pe/agencia/noticia-la-solidaridad-e-innovacion-seran-claves-pescadores-artesanales-para-enfrentar-nino-1096431.aspx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sismo en Piura de 4.1: ¿dónde se registró el epicentro de esta madrugada?</t>
+          <t>Mindef: Ejército fortalece sus comunicaciones para respuesta rápida ante fenómeno El Niño</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Un sismo de magnitud 4.1 remeció la región Piura durante la mañana de este día, según el reporte del Instituto Geofísico del Perú (IGP). El movimiento telúrico se registró a las 5:53 a. m. y tuvo su epicentro en territorio ecuatoriano, a 104 kilómetros al noreste de Ayabaca, de acuerdo con la información difundida por la institución. El evento sísmico tuvo una profundidad de 100 kilómetros, un factor que permite caracterizar el movimiento registrado en la zona fronteriza entre Perú y Ecuador. Hasta el momento de la información proporcionada, las autoridades locales no habían reportado daños materiales ni víctimas como consecuencia del temblor. El movimiento volvió a poner en atención la actividad sísmica que caracteriza al norte del país. Aunque no se informaron consecuencias graves, los especialistas recuerdan que los sismos pueden presentarse en cualquier momento y que la preparación de las familias resulta importante para reducir los riesgos ante una emergencia. Sismo en Piura: ¿dónde se registró el epicentro? Según el reporte del Instituto Geofísico del Perú, el epicentro del sismo de magnitud 4.1 se localizó en territorio ecuatoriano, a 104 kilómetros al noreste de Ayabaca, provincia ubicada en la sierra de la región Piura. El movimiento ocurrió a las 5:53 a. m., con una profundidad de 100 kilómetros. Estos datos permiten identificar la ubicación y las características principales del evento sísmico, aunque la percepción del temblor puede variar dependiendo de la distancia al epicentro, la profundidad y las condiciones del terreno. La cercanía geográfica entre el norte peruano y el sur de Ecuador hace que los movimientos telúricos registrados en uno de estos territorios puedan sentirse en el otro. Por ello, los reportes sísmicos de ambos países son relevantes para las poblaciones que viven en las zonas fronterizas. Para conocer los detalles de un evento, la población puede consultar la información oficial del Instituto Geofísico del Perú (IGP) , entidad encargada de estudiar la actividad sísmica en el territorio nacional. ¿Se reportaron daños por el temblor en Piura? De acuerdo con la información disponible, las autoridades locales no habían comunicado daños materiales ni víctimas relacionados con el sismo de magnitud 4.1. Sin embargo, la ausencia de reportes de daños no significa que la población deba dejar de lado las medidas de prevención. Ante un movimiento telúrico, se recomienda mantener la calma, alejarse de ventanas y objetos que puedan caer y ubicarse en una zona segura previamente identificada. Después del temblor, es importante revisar las condiciones de la vivienda sin exponerse a estructuras que presenten daños visibles. También se debe prestar atención a las indicaciones de las autoridades y evitar difundir información no confirmada sobre posibles consecuencias. En Perú, el Instituto Nacional de Defensa Civil (Indeci) ofrece recomendaciones para que las familias sepan cómo actuar antes, durante y después de una emergencia. Estas medidas incluyen preparar una mochila de emergencia, identificar rutas de evacuación y establecer un punto de encuentro familiar. La información preventiva puede consultarse en el portal oficial del Instituto Nacional de Defensa Civil . Preocupación por la energía sísmica acumulada en la costa central del Perú Mientras el norte del país registraba este movimiento telúrico, la actividad sísmica en la costa central peruana volvió a ser motivo de atención por las advertencias de especialistas sobre la energía acumulada en esa parte del territorio nacional. En declaraciones a RPP, el sismólogo César Jiménez Tintaya, profesor de la Universidad Nacional Mayor de San Marcos (UNMSM), advirtió que la costa central mantiene una importante acumulación de energía sísmica asociada al último gran terremoto ocurrido en Lima en 1746. El especialista explicó que, desde aquel evento, se han registrado otros terremotos importantes en el siglo XX y comienzos del XXI. Entre ellos mencionó los ocurridos en 1940, en la zona de Huacho; en 1966, cerca de Barranca; en 1974, en el sector de Chilca-Lima; y en 2007, en Pisco, región Ica. Según la explicación recogida por RPP, estos terremotos habrían liberado solo una parte de la energía sísmica acumulada en la región central. El especialista señaló que la cantidad restante constituye un motivo para reforzar la prevención y la preparación ante posibles terremotos de gran magnitud. Las estimaciones mencionadas por el experto contemplan la posibilidad de un terremoto de magnitud superior a 8.0, e incluso de entre 8.5 y 8.8, en la costa central. No obstante, estas declaraciones no representan una predicción de fecha u hora: actualmente, no es posible determinar con precisión cuándo ocurrirá un terremoto ni cuál será su magnitud exacta. ¿El sismo de Piura está relacionado con un posible terremoto en Lima? El sismo de magnitud 4.1 registrado al noreste de Ayabaca y las advertencias sobre la energía acumulada en la costa central corresponden a contextos sísmicos distintos. Con la información disponible, no existe evidencia presentada que permita afirmar que ambos fenómenos estén directamente relacionados. Los movimientos telúricos se producen por procesos geológicos que pueden variar según la ubicación, la profundidad y las características de las fallas involucradas. Por eso, un temblor registrado en la frontera entre Perú y Ecuador no debe interpretarse automáticamente como una señal de que ocurrirá un terremoto de gran magnitud en Lima. Las declaraciones de los especialistas sobre la costa central deben entenderse dentro del análisis del riesgo sísmico de largo plazo. La acumulación de energía tectónica es un aspecto relevante para la evaluación de amenazas, pero no permite establecer una fecha específica para un futuro evento. Para conocer los reportes sísmicos y las recomendaciones oficiales, se puede revisar la página del Instituto Geofísico del Perú y la información de prevención publicada por el Indeci . ¿Qué hacer ante un sismo en la región Piura? Ante un movimiento telúrico, las autoridades recomiendan priorizar la seguridad personal y evitar desplazamientos apresurados que puedan provocar accidentes. Si el temblor ocurre dentro de una vivienda, es importante protegerse y mantenerse alejado de vidrios, muebles altos y objetos que puedan desprenderse. Las familias también deben identificar las zonas seguras de sus viviendas, conocer las rutas de evacuación y mantener disponibles artículos esenciales, como agua, alimentos no perecibles, una linterna, una radio portátil, medicamentos necesarios y documentos importantes protegidos. En las zonas rurales y urbanas de Piura, la preparación debe considerar las características de cada vivienda y las condiciones del entorno. Los integrantes de una familia deben saber cómo comunicarse si quedan separados y qué lugares pueden utilizar como puntos de encuentro después de una emergencia. La información sobre la magnitud, el epicentro y la profundidad de un sismo debe verificarse mediante fuentes oficiales. Compartir datos confirmados ayuda a evitar la propagación de rumores y permite que la población tome decisiones con mayor tranquilidad. ¿Dónde consultar información oficial sobre los sismos en Perú? El Instituto Geofísico del Perú publica información relacionada con los movimientos sísmicos registrados en el país. Por su parte, el Indeci difunde orientaciones para la preparación y respuesta ante emergencias. La población también puede revisar los comunicados de las autoridades locales y regionales para conocer posibles evaluaciones de daños o recomendaciones específicas para su zona. En situaciones de emergencia, es importante seguir las instrucciones de los organismos competentes y no basarse únicamente en publicaciones difundidas por redes sociales. El sismo de magnitud 4.1 registrado a las 5:53 a. m., con epicentro en Ecuador y a 104 kilómetros al noreste de Ayabaca, volvió a recordar la importancia de mantener una cultura de prevención en Piura y en el resto del país.</t>
+          <t>Estas comunicaciones permitirán mantener el contacto con las Compañías de Intervención Rápida para Desastres (CIRD), especialmente en comunidades que podrían quedar aisladas.
+Así, se busca agilizar la toma de decisiones y facilitar el desplazamiento de personal, equipos y ayuda humanitaria hacia las zonas afectadas.
+Lea también: Enfen: lluvias aumentarán más de lo normal en la costa y la sierra hasta fines de 2026 Las pruebas estuvieron a cargo de la I División de Ejército y el Batallón de Comunicaciones N° 111, que estableció enlaces con cuatro organizaciones militares: el Cuartel General de la I División de Ejército y el Agrupamiento de Artillería Inclán, en Piura; la 9ª Brigada Blindada, en Tumbes; y la 1ª Brigada de Protección de la Amazonía, en Amazonas.
+Para ello, se emplearon equipos de radiocomunicación Hytera y plataformas tecnológicas que permiten intercambiar información entre las unidades militares.
+Los ejercicios sirvieron para comprobar su funcionamiento y evaluar la continuidad y confiabilidad de las comunicaciones ante situaciones de emergencia.
+También se evaluó la coordinación entre los mandos militares y las unidades encargadas de intervenir ante desastres , a fin de detectar posibles dificultades y optimizar el uso de los equipos disponibles en escenarios de riesgo.
+Lea también: Ministerio de Defensa presenta despliegue a gran escala del Ejército ante fenómeno El Niño Estas acciones forman parte de las medidas impulsadas por el Ministerio de Defensa para fortalecer la capacidad operativa de las Fuerzas Armadas ante el FEN , mediante sistemas de comunicación que permitan coordinar intervenciones oportunas y facilitar el despliegue de recursos en las zonas afectadas.
+Dato El Gobierno informó que las regiones de Piura y Tumbes estarán bajo la responsabilidad del ministro de Defensa, Rafael Belaunde.
+Más en Andina: El papa León XIV saludó a miles de personas congregadas en la plaza de San Pedro del Vaticano este domingo, sonriendo, y afirmó que retomará el trabajo "progresivamente" después de su operación por un cáncer de pulmón.??https://t.co/PG9GTIpJkO https://t.co/4WYK89RM0N (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 18, 2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/sismo-en-piura-de-4-1-donde-se-registro-el-epicentro-de-esta-madrugada/</t>
+          <t>https://andina.pe/agencia/noticia-mindef-ejercito-fortalece-sus-comunicaciones-para-respuesta-rapida-ante-fenomeno-nino-1096387.aspx</t>
         </is>
       </c>
     </row>
@@ -841,105 +874,139 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Temperaturas de hasta 38 °C en Piura y Tumbes será hasta fin de octubre, prevé Senamhi</t>
+          <t>Otro ataque en colegio de Piura: escolar queda desfigurada</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Las temperaturas máximas de hasta 38 °C continuarán en Piura y Tumbes durante la segunda quincena de octubre, según el pronóstico del Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi). Las condiciones cálidas se mantendrán tanto durante el día como en la noche, en un escenario asociado al actual evento El Niño costero. De acuerdo con el organismo, adscrito al Ministerio del Ambiente (Minam), las altas temperaturas se presentarán entre el sábado 17 y el sábado 31 de octubre. Durante este periodo, los valores máximos en ambas regiones oscilarán entre 32 °C y 38 °C, mientras que las temperaturas mínimas se situarán entre 22 °C y 25 °C. El pronóstico también contempla lluvias dispersas en algunos sectores de la costa norte, además de variaciones en la cobertura nubosa y ráfagas de viento en determinadas zonas del litoral peruano. Senamhi pronostica temperaturas de hasta 38 °C en Piura En Piura, el calor continuará siendo una de las principales características de las condiciones meteorológicas previstas para lo que resta de octubre. Las temperaturas máximas podrían alcanzar los 38 °C, mientras que durante la noche los termómetros registrarían valores de entre 22 °C y 25 °C. Estas condiciones implican que el descenso de la temperatura durante las horas nocturnas no será suficiente para eliminar la sensación de calor. Por ello, los habitantes de las zonas urbanas y rurales deberán prestar atención a los cambios meteorológicos y a los avisos emitidos por las autoridades. El Senamhi señaló que el comportamiento del tiempo estará relacionado con las condiciones atmosféricas y oceánicas vinculadas al actual episodio de El Niño costero. El calentamiento de la superficie del mar y el ingreso de vientos del norte figuran entre los factores que favorecen el incremento de las temperaturas en la franja costera. ¿Qué temperaturas se esperan en Tumbes hasta el 31 de octubre? En Tumbes se prevé un escenario similar al de Piura, con temperaturas máximas de entre 32 °C y 38 °C y mínimas que oscilarán entre 22 °C y 25 °C. El pronóstico comprende el periodo del 17 al 31 de octubre, durante el cual persistirán las condiciones cálidas en la costa norte. El comportamiento de la nubosidad también variará a lo largo del día. Según la información meteorológica difundida, se espera cielo nublado durante las primeras horas de la mañana, seguido de una disminución de la nubosidad hacia el mediodía y la tarde. Posteriormente, la cobertura nubosa podría incrementarse nuevamente. Además de las altas temperaturas, el pronóstico contempla lluvias dispersas en algunos sectores de la costa norte. Estas precipitaciones no necesariamente se presentarán con la misma intensidad ni en todas las localidades, por lo que resulta importante consultar los reportes oficiales correspondientes a cada zona. ¿Por qué aumentan las temperaturas en la costa norte? El Senamhi explicó que el incremento del calor está relacionado principalmente con el calentamiento de la superficie marina y el ingreso de vientos provenientes del norte. Ambos factores influyen en las condiciones atmosféricas de la costa y favorecen la persistencia de temperaturas elevadas. Otro elemento que podría contribuir a mantener el calor se presentaría entre el 27 y el 31 de octubre. Durante esos días, el ingreso de aire seco en los niveles medios de la atmósfera favorecería las altas temperaturas. Este proceso está relacionado con la subsidencia, fenómeno que consiste en el descenso de masas de aire hacia niveles inferiores de la atmósfera. Estas condiciones pueden limitar determinados procesos de formación de nubes y contribuir a mantener un ambiente cálido. La evolución de estos factores dependerá de las condiciones atmosféricas y oceánicas. Por ese motivo, los pronósticos deben revisarse periódicamente, especialmente cuando se anuncian cambios en las temperaturas, lluvias o vientos. Temperaturas previstas en otras regiones de la costa peruana Las altas temperaturas no se limitarán a Piura y Tumbes. El pronóstico del Senamhi también contempla valores elevados en otras regiones de la costa peruana durante la segunda mitad de octubre. En Lambayeque e Ica, las temperaturas máximas se situarían entre 30 °C y 38 °C. En La Libertad, los registros oscilarían entre 28 °C y 32 °C, mientras que en Lima y Áncash se esperan máximas de entre 27 °C y 34 °C. En la costa sur, las temperaturas máximas variarían entre 26 °C y 33 °C. Los valores previstos muestran diferencias entre las regiones, debido a las características geográficas y a las condiciones meteorológicas de cada sector del litoral. En cuanto a las temperaturas mínimas, Lambayeque registraría valores de entre 22 °C y 24 °C, mientras que en La Libertad se esperan registros de entre 21 °C y 24 °C. Para Lima y Áncash, las mínimas oscilarían entre 18 °C y 23 °C. ¿Cuánto calor hará en Lima Metropolitana? En Lima Metropolitana, las temperaturas máximas alcanzarían aproximadamente los 26 °C en los distritos de Lima oeste y los 29 °C en Lima norte y este. Durante la noche, las temperaturas mínimas se ubicarían entre 22 °C y 23 °C. Estas condiciones también estarán acompañadas por variaciones en la nubosidad. En algunos sectores de la costa central podrían presentarse niebla, neblina y lloviznas, principalmente durante la noche y las primeras horas de la mañana. Senamhi advierte sobre ráfagas de viento, niebla y lloviznas Además del calor, el pronóstico meteorológico contempla ráfagas de viento en algunos sectores de la costa peruana entre el 20 y el 26 de octubre. Estas condiciones podrían favorecer la aparición de niebla y neblina durante la noche y al amanecer, así como la ocurrencia de lloviznas dispersas. Estos fenómenos pueden reducir la visibilidad en determinados lugares y modificar las condiciones habituales del tiempo, especialmente durante las primeras horas del día. Su presencia dependerá de las características meteorológicas locales. Ante este escenario, el Ministerio del Ambiente y el Senamhi recomendaron a la población mantenerse informada mediante los avisos y pronósticos oficiales. Consultar las actualizaciones permite conocer la evolución de las temperaturas y otros fenómenos previstos para cada región.</t>
+          <t>Un nuevo caso de violencia escolar causa preocupación en la provincia de Sullana. Una estudiante de quinto año de secundaria de un conocido colegio de Querecotillo resultó con el rostro seriamente herido luego de ser atacada con un cúter por una compañera durante el recreo el último viernes. PUEDES LEER ► Defensoría exige esclarecer presunta agresión entre dos escolares en Querecotillo Tras la difusión de la denuncia de los familiares de la agraviada a través de las redes sociales, el Módulo Defensorial de Sullana adscrita a la Oficina Defensorial de Piura solicitó a la Comisaría de Querecotillo realizar las diligencias necesarias para esclarecer los hechos denunciados. EL CASO Según denunciaron los familiares de la víctima, identificada con las iniciales H. T. N. , la agresión habría sido una represalia porque un día antes la menor exigió a la dirección del plantel y al tutor que intervinieran ante otro episodio de violencia en el que presuntamente también habría participado la misma estudiante. El padre de la agraviada relató que, tras reclamar medidas correctivas y solicitar que el caso fuera denunciado ante la UGEL, la presunta agresora, identificada como D. A. R., habría llegado a su vivienda acompañada de su madre para amenazar a su hija. La mañana del viernes, cuando la víctima bajaba las escaleras durante el recreo, habría sido interceptada por su compañera, quien sacó un cúter y le cortó el rostro. La intervención de otra estudiante habría evitado que la agresión alcanzara el cuello de la menor.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/temperaturas-de-hasta-38-c-en-piura-y-tumbes-sera-hasta-fin-de-octubre-preve-senamhi/</t>
+          <t>https://eltiempo.pe/local/otro-ataque-en-colegio-de-piura-escolar-queda-desfigurada/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Presidenta Fujimori sostuvo reuniones de trabajo con ministro de Educación y el canciller</t>
+          <t>Agricultores de Sechura se cansaron e irán al paro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>En el encuentro con el titular del Minedu, dialogaron sobre las políticas del sector, las próximas medidas a implementar y los nuevos Lineamientos para la Gestión de la Disciplina Escolar , los cuales establecen reglas y procedimientos para fortalecer el respeto en las instituciones educativas públicas y privadas, recuperar el orden y restituir la autoridad de los docentes.
-Lee también: [ Minsa instala mesa de alto nivel para fortalecer la atención de la salud mental ] Asimismo, en la reunión entre la mandataria y el titular de Educación se abordaron las acciones anticipadas que viene desarrollando el sector ante el fenómeno El Niño, entre ellas la entrega oportuna de los recursos educativos para el Año Escolar 2027 , entre otros.
-Por otro lado y como parte de su agenda de trabajo, la mandataria también se reunió con el ministro de Relaciones Exteriores, Carlos Espá, a fin de revisar la agenda de política exterior que promueve el Gobierno .
-En la víspera, la jefa de Estado visitó las regiones Piura y La Libertad , donde afirmó que su Gobierno viene ejecutando trabajos de prevención desde el inicio de su gestión en las regiones donde se esperan lluvias intensas por el fenómeno El Niño.
-FIN) NDP/HTC Más en Andina: ??????? ¡Desde el espacio se combate la minería ilegal en el Perú! La Fuerza Aérea del Perú (FAP) utiliza tecnología satelital para detectar actividades ilegales en la Amazonía.
-???? En Madre de Dios, el análisis de imágenes satelitales permitió identificar 236 dragas, 118 canaletas de lavado de mineral, 242 instalaciones operativas y cinco campamentos clandestinos.?? Además, se evidenció la degradación de más de 4 000 hectáreas de bosque amazónico.??? Esta tecnología permite a las fuerzas del orden planificar operativos contra la minería ilegal.?? Conoce más en la Agencia Andina:https://t.co/5njNTuwbAY#MineríaIlegal #FAP #MadreDeDios #Amazonía #Perú (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 17, 2026 Publicado: 17/10/2026 (function(){ window.addEventListener('message', function(e){ if (e.data &amp;&amp; e.data.tipo === 'andina-alto' &amp;&amp; e.data.alto) { var f = document.getElementsByTagName('iframe'); for (var i = 0; i &lt; f.length; i++) { if (f[i].contentWindow === e.source) { f[i].style.height = e.data.alto + 'px'; } } } }); })(); googletag.cmd.push(function () { googletag.display('top3_ad'); }); PUBLICIDAD MGID - UNDER ARTICLE (29/09/2026), tag entregado por Comercial (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); /////////////////// CARRUSEL DE VIDEOS EN STOP //////////////////// /////////// CARRUSEL DE VIDEOS /////////// Videos Andina Presidenta Keiko Fujimori recibe al Señor de los Milagros en Palacio de Gobierno access_time 2:02 Federico Kauffmann: el legado de un arqueológo construido en familia access_time 3:26 Illariywan Yacahriy: economía peruana crece impulsada por construcción access_time 3:13 Pensionistas usan IA para enviar mensajes de apoyo al papa León XIV access_time 2:42 Del culto ancestral a la ciencia: ingenieros peruanos transforman la humedad en agua potable access_time 2:43 Salsa criolla: un encuentro de ritmos con identidad peruana access_time 3:30 Caral nos presenta nuevos hallazgos en 32 años de investigación access_time 2:35 Cuidados paliativos: alivio y acompañamiento en los momentos más difíciles access_time 2:56 Presidenta: Tenemos que ponernos la camiseta blanca y roja para enfrentar a El Niño access_time 1:25 ERM 2026: audiencias de recuento de votos inicia 12 de octubre access_time 1:40 El coro para León XIV: dos generaciones y un mismo sentimiento access_time 3:24 Presidenta Fujimori: No vamos a parar hasta recuperar la paz y el orden en nuestro país access_time 2.30 PUBLICIDAD PROGRAMATICA LEADER1 (SOLO MOBILE) ////////////////////////////// ASIDE ////////////////////////////// // VIDEO /////////// Video más visto ////////////////////////// LAS MAS LEIDAS ///////////////////////// ////////////////////////// LAS MAS LEIDAS LATERAL///////////////////////// Las más leídas Metropolitano y Línea 1: conexión en Grau estará lista en la primera semana de diciembre Examen de Admisión UNMSM 2027-I: conoce aquí los resultados de las dos primeras fechas ¡Atención! Pronabec amplía hasta hoy domingo 18 la inscripción para postular a Beca 18 Presidenta Keiko Fujimori recibe al Señor de los Milagros en Palacio de Gobierno Puente Piedra: incendio de grandes proporciones consume una fábrica de plásticos [video] Minsa ofrecerá chequeos gratuitos de cáncer de mama en dos centros comerciales de Lima Cumbre Infracon Perú 2026 destacó potencial del país para inversiones en infraestructura Fenómeno El Niño: Sector Vivienda coordina estrategia multisectorial en Ica y Arequipa Fiscalía contra el terrorismo pide cadena perpetua para hermanos Quispe Palomino Superávit comercial anual del Perú ascendió a los US$ 47,723 millones a agosto 2026 ////////////////////////// FIN LAS MAS LEIDAS ///////////////////////// //////// PUBLICIDAD INTERNA ////// //////// PUBLICIDAD PROGRAMATICA CENTER1 ////// $(document).ready(function () { $('.materialboxed').materialbox(); }); (function () { var path = window.location.pathname; // ej: "///////noticia-peru-..." // Si path comienza con más de una barra if (/^\/{2,}/.test(path)) { // Reemplazar múltiples '/' por uno solo al inicio var nuevaPath = path.replace(/^\/+/, '/'); // Reconstruir la URL completa var nuevaUrl = window.location.protocol + '//' + window.location.host + nuevaPath + window.location.search + window.location.hash; // Redirigir a la URL limpia window.location.replace(nuevaUrl); console.log(nuevaUrl); } })(); /////////////// FOOTER /////////////// LOGOS CONVENIOS Director(e): Félix Paz Quiroz Gerente General(e): Félix Paz Quiroz Av.
-Alfonso Ugarte 873 Lima 1 Teléfono: (51-1) 315 0400 Fax: 431 2849 ENGLISH VERSION Inicio Lo último Política Economía Locales Regionales Internacional Cultural Ánfora 2026 Deportes Clic Perfiles y Crónicas Ciencia y Tecnología Cambio Climático Canal Online Videos Especiales Interactivos Podcast Newsletter Nosotros Especiales Elecciones 2026 Enfermedades raras en Perú Joyas religiosas en Lima Foro de Cooperación Económica Asia-Pacífico Embarazo adolescente: el costo de la maternidad temprana Perú y Corea hermanados por la gastronomía Inti Raymi: el Sol sale para todos Editora Perú | Acerca de Andina | Términos | Privacidad © 2025 Agencia Peruana de Noticias.
-Todos los derechos reservados.
-(function () { 'use strict'; function fechaConsulta() { var meses = ['enero', 'febrero', 'marzo', 'abril', 'mayo', 'junio', 'julio', 'agosto', 'septiembre', 'octubre', 'noviembre', 'diciembre']; var d = new Date(); return d.getDate() + ' de ' + meses[d.getMonth()] + ' de ' + d.getFullYear(); } function tituloLimpio() { var t = (document.title || '').replace(/\s*\|\s*ANDINA.*$/i, '') .replace(/^Agencia Peruana de Noticias\s*\|\s*/i, '') .trim(); return t || 'Agencia Peruana de Noticias Andina'; } document.addEventListener('copy', function (e) { var seleccion = (window.getSelection ? window.getSelection().toString() : ''); if (!seleccion || seleccion.length &lt; 50) return; var url = window.location.href; var titulo = tituloLimpio(); var fecha = fechaConsulta(); var encabezado = 'Este contenido puede reproducirse citando a la Agencia Andina ©️ Editora Perú\n\n'; var cierre = '\n\nLea más en: ' + url; var textoFinal = encabezado + seleccion + cierre; if (e.clipboardData &amp;&amp; e.clipboardData.setData) { e.clipboardData.setData('text/plain', textoFinal); e.preventDefault(); } else if (window.clipboardData &amp;&amp; window.clipboardData.setData) { window.clipboardData.setData('Text', textoFinal); e.returnValue = false; } }); function copiarTexto(texto) { if (navigator.clipboard &amp;&amp; navigator.clipboard.writeText) { navigator.clipboard.writeText(texto); } else { var ta = document.createElement('textarea'); ta.value = texto; ta.style.position = 'fixed'; ta.style.opacity = '0'; document.body.appendChild(ta); ta.select(); try { document.execCommand('copy'); } catch (e) { } ta.remove(); } } function mostrarMenuPersonalizado(x, y, img) { var anterior = document.getElementById('andina-img-menu'); if (anterior) anterior.parentNode.removeChild(anterior); var menu = document.createElement('div'); menu.id = 'andina-img-menu'; menu.style.cssText = 'position:fixed;top:' + y + 'px;left:' + x + 'px;' + 'background:#fff;border:1px solid #d0d0d0;border-radius:5px;' + 'box-shadow:0 6px 20px rgba(0,0,0,.18);padding:5px 0;' + 'font-family:Arial,sans-serif;font-size:13px;min-width:240px;' + 'z-index:1;'; var opciones = [ { txt: 'Abrir imagen en nueva pestaña', fn: function () { window.open(img.src, '_blank'); } }, { txt: 'Copiar dirección de la imagen', fn: function () { copiarTexto(img.src); } } ]; opciones.forEach(function (opt) { var item = document.createElement('div'); item.textContent = opt.txt; item.style.cssText = 'padding:9px 18px;cursor:pointer;color:#222;user-select:none;'; item.addEventListener('mouseenter', function () { item.style.background = '#eef3f9'; }); item.addEventListener('mouseleave', function () { item.style.background = 'transparent'; }); item.addEventListener('click', function () { opt.fn(); if (menu.parentNode) menu.parentNode.removeChild(menu); }); menu.appendChild(item); }); var sep = document.createElement('div'); sep.style.cssText = 'border-top:1px solid #eee;margin:4px 0;'; menu.appendChild(sep); var pie = document.createElement('div'); pie.textContent = 'Foto: ANDINA / Editora Perú'; pie.style.cssText = 'padding:6px 18px;font-size:11px;color:#888;font-style:italic;'; menu.appendChild(pie); document.body.appendChild(menu); var rect = menu.getBoundingClientRect(); if (rect.right &gt; window.innerWidth) menu.style.left = (window.innerWidth - rect.width - 10) + 'px'; if (rect.bottom &gt; window.innerHeight) menu.style.top = (window.innerHeight - rect.height - 10) + 'px'; setTimeout(function () { document.addEventListener('click', function cerrar(ev) { if (!menu.contains(ev.target)) { if (menu.parentNode) menu.parentNode.removeChild(menu); document.removeEventListener('click', cerrar); } }); document.addEventListener('contextmenu', function cerrarCtx(ev) { if (!menu.contains(ev.target)) { if (menu.parentNode) menu.parentNode.removeChild(menu); document.removeEventListener('contextmenu', cerrarCtx); } }); }, 0); } function mostrarModalImagen(img, callback) { var anterior = document.getElementById('andina-img-modal'); if (anterior) anterior.parentNode.removeChild(anterior); var rect = img.getBoundingClientRect(); var scrollY = window.pageYOffset || document.documentElement.scrollTop; var scrollX = window.pageXOffset || document.documentElement.scrollLeft; // Overlay sobre el área de la imagen, con flexbox para centrar el modal var overlay = document.createElement('div'); overlay.id = 'andina-img-modal'; overlay.style.cssText = 'position:absolute;' + 'top:' + (rect.top + scrollY) + 'px;' + 'left:' + (rect.left + scrollX) + 'px;' + 'width:' + rect.width + 'px;' + 'height:' + rect.height + 'px;' + 'background:rgba(0,0,0,.7);z-index:1;' + 'display:flex;align-items:center;justify-content:center;' + 'font-family:Arial,sans-serif;opacity:0;transition:opacity .2s ease-in;' + 'overflow:hidden;cursor:pointer;'; // Modal con tamaño "natural" (referencia en imagen grande) var anchoNatural = 320; var altoNatural = 170; // Escala proporcional para que quepa con margen del 10% en cualquier imagen var escalaX = (rect.width * 0.90) / anchoNatural; var escalaY = (rect.height * 0.90) / altoNatural; var escala = Math.min(escalaX, escalaY, 1); // máx 1 (no se agranda) var caja = document.createElement('div'); caja.style.cssText = 'background:#fff;border-radius:6px;padding:18px 22px;' + 'width:' + anchoNatural + 'px;' + 'box-shadow:0 12px 40px rgba(0,0,0,.55);' + 'border-top:4px solid #c62828;' + 'text-align:center;box-sizing:border-box;' + 'transform:scale(' + escala + ');' + 'transform-origin:center center;' + 'cursor:auto;'; caja.innerHTML = '&lt;h3 style="margin:0 0 12px 0;color:#c62828;font-size:17px;font-weight:bold;"&gt;Derechos de imagen&lt;/h3&gt;' + '&lt;p style="margin:0 0 16px 0;color:#333;font-size:13px;line-height:1.5;"&gt;' + '&lt;strong&gt;© ANDINA / Editora Perú&lt;/strong&gt;.&lt;br&gt;' + 'Reproducción permitida colocando el crédito de manera obligatoria.' + '&lt;/p&gt;' + '&lt;button id="andina-img-modal-ok" type="button" ' + 'style="background:#c62828;color:#fff;border:none;padding:10px 26px;' + 'border-radius:4px;font-size:13px;cursor:pointer;font-weight:bold;' + 'letter-spacing:.3px;"&gt;Acepta y continúa.&lt;/button&gt;'; // Evita que el clic dentro de la caja cierre el overlay caja.addEventListener('click', function (ev) { ev.stopPropagation(); }); overlay.appendChild(caja); document.body.appendChild(overlay); requestAnimationFrame(function () { overlay.style.opacity = '1'; }); var btn = document.getElementById('andina-img-modal-ok'); btn.focus(); // Si el usuario hace scroll, cerramos el modal (evita que pase bajo el header sticky) function onScrollClose() { cerrar(false); } window.addEventListener('scroll', onScrollClose, { passive: true, once: true }); function cerrar(aceptado) { window.removeEventListener('scroll', onScrollClose); overlay.style.opacity = '0'; setTimeout(function () { if (overlay.parentNode) overlay.parentNode.removeChild(overlay); if (aceptado &amp;&amp; callback) callback(); }, 200); } btn.addEventListener('click', function () { cerrar(true); }); overlay.addEventListener('click', function () { cerrar(false); }); document.addEventListener('keydown', function escListener(ev) { if (ev.key === 'Escape') { document.removeEventListener('keydown', escListener); cerrar(false); } }); } function esImagenDeContenido(img) { var src = (img.getAttribute('src') || '').toLowerCase(); // Patrón CMS Andina: nnnnnnW|M|T.ext (W=wide, M=medium, T=thumbnail) // Mostrar aviso solo en W y M; T es miniatura.
-var match = src.match(/(\d+)([wmt])\.(jpe?g|png|webp|gif)(\?|$)/i); if (match) { var sufijo = match[2].toLowerCase(); return (sufijo === 'w' || sufijo === 'm'); } // Para imágenes que NO siguen el patrón del CMS, aplicar filtros generales: // SVG = ícono/logo if (src.indexOf('.svg') !== -1) return false; var rect = img.getBoundingClientRect(); var anchoNatural = img.naturalWidth || rect.width; var altoNatural = img.naturalHeight || rect.height; if (rect.width &lt; 200 &amp;&amp; rect.height &lt; 200) return false; if (anchoNatural &lt; 250 &amp;&amp; altoNatural &lt; 250) return false; // Contenedores estructurales if (img.closest('header, footer, nav, .sidebar, .menu-sidebar, .floating-btn, ' + '.descargueapp, .convewidth, .logoeditora, .buscador, .cinta')) { return false; } // Clases de logo/ícono if (img.classList.contains('logo') || img.classList.contains('no-watermark')) return false; var cls = img.className || ''; if (/\b(width(\d+)|icon|btn-floating)\b/.test(cls) &amp;&amp; (anchoNatural &lt; 300)) return false; // Nombres de logos/íconos conocidos var skip = ['andina.svg', 'editora_logo', 'appstore', 'googleplay', 'menu.svg', 'search.svg', 'facebook', 'twitter', 'linkedin', 'youtube', 'instagram', 'soundcloud', 'spotify', 'tik-tok', 'more_vert', 'i_class-fecha', 'icono.ico', 'radio_nacional', 'tv_peru', 'ansa.svg', 'centro_de_informacion', 'editora_peru']; for (var i = 0; i &lt; skip.length; i++) { if (src.indexOf(skip[i]) !== -1) return false; } return true; } document.addEventListener('contextmenu', function (e) { var t = e.target; var img = (t &amp;&amp; t.tagName === 'IMG') ? t : (t &amp;&amp; t.closest ? t.closest('img') : null); if (!img) return; // Si el clic está dentro de nuestro menú personalizado, no hacer nada if (t.closest &amp;&amp; t.closest('#andina-img-menu')) return; // Solo bloquear el menú nativo en fotos de contenido if (!esImagenDeContenido(img)) return; e.preventDefault(); var posX = e.clientX, posY = e.clientY; mostrarModalImagen(img, function () { mostrarMenuPersonalizado(posX, posY, img); }); }); })(); /////////////// LLAMADA SCRIPTS/////////////// $('.button-collapse').sideNav({ menuWidth: 300, edge: 'right', closeOnClick: true, draggable: true, onOpen: function (el) { } } ); &lt;!-- Marquee pestaña --&gt; var scrl = " Agencia Andina "; function scrlsts() { scrl = scrl.substring(1, scrl.length) + scrl.substring(0, 1); document.title = scrl; setTimeout("scrlsts()", 280); } $(document).ready(function () { $('.parallax').parallax(); }); $(document).ready(function () { $('.slider').slider(); //Registro de Datalayer en Push }); $(".button-collapse").sideNav(); $(window).scroll(function () { if ($(this).scrollTop() &gt; 265) { $('nav').addClass("fixed").fadeIn(); $('#logomin').empty(); $('#logomin').prepend('&lt;a href="https://andina.pe"&gt;&lt;img src="img/logoandina2.png" loading="lazy" style="margin: 4px 8px; width:110px; margin-right:10px;" alt="#" &gt;&lt;/a&gt;'); } else { $('#logomin').empty(); $('nav').removeClass("fixed"); } }); //Funcion Registro Evento para GTAG Manager RL function registerEventTarget(nombreSeccion) { //Modificacion envio de evento para GTAG Manager Ricardo Lazarte const urlActual = window.location.href; let now = new Date(); window.dataLayer = window.dataLayer || []; window.dataLayer.push({ 'event': 'interaction', //Interaction 'eventAction': 'click', 'eventLabel': nombreSeccion, 'secction': 'Portada', 'eventCategory': 'Header', 'newurl': urlActual }); } //Funcion Registro Evento para GTAG Manager RL BANNERS function registerEventTargetBanner(nombreElemento) { //Modificacion envio de evento para GTAG Manager Ricardo Lazarte const urlActual = window.location.href; let now = new Date(); window.dataLayer = window.dataLayer || []; window.dataLayer.push({ 'event': 'interaction', 'eventAction': 'click', 'eventLabel': nombreElemento, 'secction': 'Portada', 'eventCategory': 'BANN LATERAL', 'newurl': urlActual }); // alert(nombreElemento); } const delay = 7000; //ms const slides = document.querySelector(".slides"); const slidesCount = slides.childElementCount; const maxLeft = (slidesCount - 1) * 100 * -1; let current = 0; function changeSlide(next = true) { if (next) { current += current &gt; maxLeft ? -100 : current * -1; } else { current = current &lt; 0 ? current + 100 : maxLeft; } slides.style.left = current + "%"; } let autoChange = setInterval(changeSlide, delay); const restart = function () { clearInterval(autoChange); autoChange = setInterval(changeSlide, delay); }; // Controls document.querySelector(".next-slide").addEventListener("click", function () { changeSlide(); restart(); }); document.querySelector(".prev-slide").addEventListener("click", function () { changeSlide(false); restart(); }); $(window).scroll(function () { if ($(this).scrollTop() &gt; 265) { $('nav').addClass("fixed").fadeIn(); $('#logomin').empty(); $('#logomin').prepend('&lt;a href="https://andina.pe"&gt;&lt;img src="img/logoandina2.png" style="margin: 4px 8px; width:110px; margin-right:10px;" alt="#" &gt;&lt;/a&gt;'); } else { $('#logomin').empty(); $('nav').removeClass("fixed"); } }); $(window).scroll(function () { if ($(window).width() &lt;= 992) { if ($(this).scrollTop() &gt; 100) { $('#sticky-header2').addClass("fixed").fadeIn(); } else { $('#sticky-header2').removeClass("fixed"); } } else { // Por si el usuario redimensiona la pantalla $('#sticky-header2').removeClass("fixed"); } }); //// Detecta el clic en la clase .floating-btn //document.querySelector('#headers .floating-btn').addEventListener('click', function () { // // Verifica si estamos en un dispositivo móvil (opcional, en base a la resolución) // if (window.innerWidth &lt;= 600) { // this.classList.toggle('hover-active'); // Alterna la clase que activa el hover // } //});</t>
+          <t>Una grave crisis golpea a los pequeños agricultores del Bajo Piura y Sechura. La falta de financiamiento estatal, las dificultades para comercializar sus cosechas y el escaso avance de las obras de prevención ante el Fenómeno El Niño mantienen en incertidumbre a más de 30 mil productores, denunció Máximo Valdiviezo , presidente de la Asociación de Productores Agrarios del Valle de Sechura. El dirigente cuestionó el programa de compra estatal de arroz, al que calificó de “ engaño ”, debido a que, según indicó, los recursos necesarios aún no habrían sido transferidos por el Ministerio de Economía y Finanzas (MEF). Valdiviezo señaló que, de los S/ 15 millones anunciados inicialmente para Piura, se habría reducido el presupuesto a aproximadamente S/ 8,8 millones para adquirir 57 mil sacos de arroz. “En el valle de Sechura ningún agricultor le ha vendido un solo saco de arroz al Estado” , afirmó, reclamando respuestas concretas del Gobierno. Asimismo, informó que los gremios agrarios impulsan un proyecto de ley para proteger la producción nacional de arroz, algodón, maíz y menestras, además de exigir el fortalecimiento de la franja de precios frente a las importaciones. La preocupación también alcanza las obras de prevención. Según el dirigente, de los 77 kilómetros proyectados para intervenir en el río Piura, solo se habría avanzado entre dos y tres kilómetros. A ello se suman los drenes colmatados, la falta de combustible para su mantenimiento y el deterioro de las trochas carrozables. “Soy sincero, no estamos preparados”, advirtió.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-presidenta-fujimori-sostuvo-reuniones-trabajo-ministro-educacion-y-canciller-1096370.aspx</t>
+          <t>https://eltiempo.pe/local/agricultores-de-sechura-se-cansaron-e-iran-al-paro/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ministerio de Defensa presenta despliegue a gran escala del Ejército ante fenómeno El Niño</t>
+          <t>Defensoría exige esclarecer presunta agresión entre dos escolares en Querecotillo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>???? ¡Preparados para llegar a donde más nos necesitan!?? Nuestro glorioso @EjercitoPeru demostró sus capacidades de rescate, evacuación y respuesta ante emergencias frente al fenómeno El Niño.¡#ElPerúResponde para proteger a la población!?? https://t.co/fHnSHXKo01 https://t.co/zKOQGWsjwJ — Mindef Perú (@MindefPeru) October 17, 2026 La actividad formó parte de la Reunión de Coordinación Multisectorial organizada por el Comando de Operaciones Terrestres junto a representantes del Sistema Nacional de Gestión del Riesgo de Desastres (Sinagerd).
-Durante la jornada, se realizaron maniobras operativas que incluyeron descensos con cuerdas desde helicópteros MI-17 para zonas de difícil acceso, el empleo de electrobombas y motobombas para drenar áreas anegadas , y el uso de caballos para el traslado en terrenos de difícil tránsito.
-Asimismo, vehículos lanza puentes diseñados para restablecer la circulación en vías interrumpidas.
-Lea también: Ministro de Defensa liderará acciones de emergencia en Piura y Tumbes ante El Niño Por su parte, las unidades especializadas USAR PER-13 y PER-14 ejecutaron ejercicios de rescate acuático , búsqueda bajo el agua, trabajos de corte, rompimiento y evacuación de víctimas.
-A la par, presentó su infraestructura logística para la gestión de desastres, la cual contempla puestos de comando móvil, puestos de atención de salud, bases para grupos de búsqueda y la instalación de albergues temporales con soporte tecnológico.
-Capacidad de respuesta ante emergencias En el plano operativo, el Ejército cuenta con 22 batallones de Ingeniería distribuidos en 15 regiones , equipados con 441 maquinarias pesadas y vehículos de ingeniería destinados a la remoción de escombros, limpieza de cauces y atención directa de emergencias.
-Este despliegue se enmarca en un proceso de preparación iniciado en julio de 2026 , que comprendió cuatro etapas de planeamiento, revisión de experiencias anteriores, simulaciones y coordinación interinstitucional.
-Más en Andina: Intervienen a más de 1,800 extranjeros en megaoperativo nacional https://t.co/KOT1jwbMHa https://t.co/ge3KjV77sN (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 17, 2026</t>
+          <t>La Defensoría del Pueblo solicitó al Ministerio Público realizar una investigación exhaustiva para esclarecer los hechos de violencia que involucrarían a dos estudiantes de la institución educativa José María Raygada Gallo, ubicada en el distrito de Querecotillo, provincia de Sullana, en Piura. A través de la Oficina Defensorial de Piura, en coordinación con el Módulo Defensorial de Sullana, la entidad viene efectuando acciones de seguimiento para garantizar la protección de los derechos de ambas adolescentes. Según informó la fiscal a cargo del caso, en las primeras diligencias se conoció que las dos escolares se habrían agredido mutuamente. La investigación cuenta con un certificado médico legal y está pendiente la revisión de videos que permitan esclarecer las circunstancias del incidente y determinar las responsabilidades correspondientes. Ante esta situación, la Defensoría pidió al Ministerio Público profundizar las investigaciones, respetando los derechos de ambas menores de edad y garantizando que el caso sea evaluado conforme a ley. Además, exhortó a la UGEL Sullana y a la dirección del colegio a activar los protocolos de atención frente a la violencia escolar, implementar las medidas de protección necesarias y asegurar que ambas estudiantes puedan continuar sus estudios en un ambiente seguro. La institución defensorial indicó que continuará supervisando las actuaciones de las entidades competentes para velar por la integridad de las adolescentes, su protección oportuna y la convivencia adecuada dentro de la comunidad educativa.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-ministerio-defensa-presenta-despliegue-a-gran-escala-del-ejercito-ante-fenomeno-nino-1096354.aspx</t>
+          <t>https://eltiempo.pe/local/defensoria-exige-esclarecer-presunta-agresion-entre-dos-escolares-en-querecotillo/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Evacuación preventiva para evitar desastres por El Niño</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>nuevo caso de violencia escolar causa preocupación en la provincia de Sullana. Una estudiante de quinto año de secundaria de un conocido colegio de Querecotillo resultó con el rostro seriamente herido luego de ser atacada con un cúter por una compañera durante el recreo el último viernes. Tras la difusión de la denuncia de los familiares de la agraviada a través de las redes sociales, el Módulo Defensorial de Sullana adscrita a la Oficina Defensorial de Piura solicitó a la Comisaría de Querecotillo realizar las diligencias necesarias para esclarecer los hechos denunciados. EL CASO Según denunciaron los familiares de la víctima, identificada con las iniciales H. T. N. , la agresión habría sido una represalia porque un día antes la menor exigió a la dirección del plantel y al tutor que intervinieran ante otro episodio de violencia en el que presuntamente también habría participado la misma estudiante. El padre de la agraviada relató que, tras reclamar medidas correctivas y solicitar que el caso fuera denunciado ante la UGEL, la presunta agresora, identificada como D. A. R., habría llegado a su vivienda acompañada de su madre para amenazar a su hija. La mañana del viernes, cuando la víctima bajaba las escaleras durante el recreo, habría sido interceptada por su compañera, quien sacó un cúter y le cortó el rostro. La intervención de otra estudiante habría evitado que la agresión alcanzara el cuello de la menor.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/evacuacion-preventiva-para-evitar-desastres-por-el-nino/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Alcalde electo de VDO, Percy Fiestas, denuncia extorsión en Piura y amenazas contra su familia</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>El virtual alcalde del distrito de Veintiséis de Octubre, Percy Fiestas Aquino , denunció haber recibido amenazas de muerte y mensajes extorsivos dirigidos contra él y sus familiares, días después de ser elegido como nueva autoridad municipal. Según su testimonio, los presuntos responsables le exigen dinero y buscan obligarlo a entablar una negociación bajo el argumento de brindarle seguridad. El caso ha generado preocupación en Piura , especialmente por los antecedentes de violencia contra autoridades municipales en el distrito. Las comunicaciones recibidas por Fiestas incluirían llamadas telefónicas, mensajes intimidatorios y un video en el que un sujeto exhibe un arma de fuego y exige una respuesta en un plazo de 24 horas. De acuerdo con lo informado por el virtual alcalde, los remitentes se identifican como presuntos integrantes de la organización criminal Nueva Generación del Norte. Sin embargo, la identidad de los autores y su posible vinculación con alguna banda delictiva deberán ser determinadas por las autoridades encargadas de la investigación. Percy Fiestas denuncia extorsión en Piura y amenazas contra su familia Las primeras comunicaciones llegaron el 15 de octubre, alrededor de las 10 de la mañana, según relató Fiestas. Los mensajes estuvieron acompañados de llamadas telefónicas y material audiovisual en el que un hombre, que asegura pertenecer a la mencionada organización, intenta presionarlo para que acepte una negociación. “Nos exigen pagos de dinero y, además, que entremos en comunicación con ellos para que, entre comillas, nos brinden seguridad. Envían amenazas y videos donde muestran armas de fuego y también amenazan a mi familia”, declaró el virtual alcalde. Según las capturas de pantalla difundidas, los presuntos extorsionadores afirman conocer la dirección de su vivienda, los nombres de sus familiares y sus movimientos. En uno de los mensajes, el remitente establece un plazo de 24 horas para recibir una respuesta y advierte que acudirá al domicilio si no obtiene contestación. El video enviado a Fiestas contiene nuevas advertencias. En la grabación, un sujeto le pide que dialogue y acepte negociar, al mismo tiempo que menciona a su esposa y a su hija. El contenido busca generar presión mediante referencias directas a sus seres queridos. “Mire doctor Percy, es mejor que dialogues con nosotros, entrar en una negociación y llevar la fiesta en paz, ya nosotros sabemos todos tus movimientos. Espero una respuesta tuya lo más antes posible, dentro de las 24 horas. Si ignoras, después no te quejes”, se escucha en el material difundido. Policía Nacional investiga las amenazas contra el virtual alcalde Percy Fiestas informó que presentó la denuncia correspondiente y entregó a la Policía Nacional del Perú (PNP) el teléfono celular en el que recibió los mensajes y las llamadas. El caso quedó a cargo de la División de Investigación Criminal (Divincri), que deberá realizar las diligencias para establecer el origen de las comunicaciones e identificar a los responsables. El virtual alcalde señaló que no tenía identificado a ningún sospechoso y que, hasta el momento de sus declaraciones, no había recibido nuevas amenazas durante ese día. No obstante, explicó que las llamadas y los mensajes se prolongaron durante varias horas, y que una de las comunicaciones fue contestada por su esposa. “Las amenazas mencionan la dirección exacta de mi casa y los nombres de los miembros de mi familia. Como entenderán, esto nos genera temor, por eso hacemos un llamado a las autoridades para que se investigue el caso y se pueda sancionar a los responsables”, manifestó. Tras conocerse la denuncia, se dispusieron patrullajes en los alrededores de su vivienda. Además, se cursaron oficios a las comisarías de San Martín y Veintiséis de Octubre para solicitar acciones de seguridad, según la información proporcionada sobre el caso. Fiestas también indicó que tuvo que asumir el costo de su seguridad personal ante el temor generado por las amenazas. Su principal preocupación, sostuvo, es la integridad de sus familiares, quienes también habrían sido mencionados en las comunicaciones intimidatorias. Otro aspecto que le preocupa es la falta de cámaras de vigilancia en su vivienda y en los alrededores. Según explicó, el sector no cuenta con equipos de videovigilancia que permitan registrar posibles movimientos sospechosos y que podrían contribuir a las investigaciones. ¿Por qué las amenazas contra Percy Fiestas generan preocupación en Veintiséis de Octubre? La denuncia adquiere especial relevancia por el antecedente de violencia que afectó a la municipalidad del distrito. El 21 de mayo de 2026, el entonces alcalde de Veintiséis de Octubre, Víctor Hugo Febre , fue asesinado en un ataque armado atribuido a sicarios. Según Percy Fiestas, los remitentes de los mensajes hicieron referencia a ese crimen para incrementar el temor y presionarlo a responder a sus exigencias. La mención del asesinato de su antecesor habría intensificado la preocupación de su entorno familiar, debido a que el hecho ocurrió en la misma jurisdicción donde ejercerá funciones municipales. “Si estamos en un distrito en el cual un alcalde murió a manos de sicarios, entenderán que estamos pasando una situación familiar bastante preocupante. Los delincuentes hacen referencia a ese hecho como una herramienta para infundirnos mayor temor”, señaló. El antecedente pone nuevamente en discusión las condiciones de seguridad para las autoridades locales en Piura, donde las amenazas extorsivas representan un desafío para las familias afectadas y para las instituciones responsables de prevenir e investigar los delitos. En este caso, corresponde a la Policía y al Ministerio Público determinar si las comunicaciones proceden de una organización criminal, establecer la posible relación entre los mensajes y otros hechos delictivos y reunir las pruebas necesarias para identificar a los responsables. Hasta que concluyan las diligencias, las afirmaciones sobre la autoría de las amenazas deben considerarse parte de la denuncia y no hechos judicialmente acreditados. Percy Fiestas pide reforzar la seguridad frente a la extorsión en Piura Ante esta situación, el virtual alcalde pidió a las autoridades profundizar las investigaciones y sancionar a quienes resulten responsables. También hizo un llamado al Gobierno central para fortalecer la lucha contra la extorsión y mejorar la coordinación entre las instituciones nacionales y los gobiernos locales. Fiestas advirtió que las amenazas no solo afectan a quienes ocupan cargos públicos, sino también a sus familiares, especialmente cuando los mensajes incluyen información sobre sus domicilios y actividades cotidianas. Por ello, insistió en la necesidad de adoptar medidas que permitan proteger a las personas afectadas y evitar que las intimidaciones escalen a hechos de violencia. La denuncia se produce cuando el distrito de Veintiséis de Octubre se prepara para una nueva gestión municipal. Mientras avanzan las diligencias policiales, la identificación de los remitentes, la verificación del material audiovisual y el análisis de las llamadas serán elementos importantes para esclarecer lo ocurrido. ¿Dónde denunciar casos de extorsión en Piura? Las personas que reciban amenazas, mensajes extorsivos o llamadas en las que se les exija dinero pueden acudir a una dependencia policial para presentar una denuncia. Es importante conservar las conversaciones, los números telefónicos, las capturas de pantalla, los audios y los videos recibidos, evitando eliminar los archivos que podrían servir como evidencia. También se recomienda no negociar ni realizar pagos por presión sin comunicar previamente el caso a las autoridades. Si existen amenazas inmediatas contra la vida o la integridad de una persona, se debe solicitar ayuda policial de manera urgente y evitar exponerse a encuentros con los presuntos responsables. Para obtener orientación y conocer los canales oficiales de atención, se puede consultar el portal de la Ministerio del Interior y la página institucional de la Policía Nacional del Perú . Asimismo, el Ministerio Público ofrece información institucional sobre sus funciones y los servicios vinculados a la recepción e investigación de denuncias.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/alcalde-electo-de-vdo-percy-fiestas-denuncia-extorsion-en-piura-y-amenazas-contra-su-familia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
+      <c r="B20" s="2" t="n">
         <v>46312</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Reniec: conoce cómo reservar una cita para tramitar el DNI de tus hijos.</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Cabe resaltar que, esta atención con cita solo se brinda a los ciudadanos que desean realizar trámites de DNI.
 No se requiere una cita para los trámites de registros civiles, ni para el recojo del documento de identidad.
@@ -972,71 +1039,16 @@
 https://t.co/zFayQIeND9 https://t.co/9RbGIAiNaK (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 16, 2026</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-reniec-conoce-como-reservar-una-cita-para-tramitar-dni-tus-hijos-1096343.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>46312</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Temblor hoy en Perú: sismo de magnitud 4.1 en Piura eleva a 739 los reportados este año</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>El movimiento telúrico ocurrió a la 05:53 horas, y su epicentro fue localizado a 104 kilómetros al este del distrito de Ayabaca, provincia del mismo nombre.
-Las autoridades regionales y locales de Defensa Civil no han reportado hasta el momento daños personales o materiales a consecuencia de este sismo.
-Con este temblor, el Perú acumula 739 sismos reportados en el país por el Centro Sismológico Nacional en lo que va del año.
-Perú registra permanente actividad sísmica El territorio peruano presenta una elevada actividad sísmica debido principalmente al proceso de subducción de la placa de Nazca bajo la placa Sudamericana.
-Ante la ocurrencia de un sismo, el Instituto Nacional de Defensa Civil (Indeci) recomienda mantener la calma, ubicarse en una zona segura previamente identificada y alejarse de ventanas, objetos que puedan caer y estructuras que representen peligro.
-También aconseja contar con una mochila para emergencias y una caja de reserva con artículos básicos para afrontar las primeras horas posteriores a una emergencia.</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-temblor-hoy-peru-sismo-magnitud-41-piura-eleva-a-739-los-reportados-este-ano-1096310.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>46312</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Anuncian corte de servicio eléctrico por trabajos de reforzamiento de redes en VDO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Como parte de las acciones preventivas ante la llegada del FEN, Enosa realizará trabajos de reforzamiento de redes de media tensión en Veintiséis de Octubre, a fin de fortalecer la infraestructura eléctrica frente a las posibles condiciones que genere el periodo de lluvias. La intervención se realizará mañana domingo, de 7 a. m. a 3 p. m. Durante ese horario, el corte del servicio comprenderá las urbanizaciones Villas del Sol, Las Casuarinas IV y V Etapa, Las Colinas del Chipe I Etapa, manzanas B a F, Los Parques del Chipe II Etapa, Las Praderas del Chipe, Alameda del Chipe y Las Lomas del Chipe. Asimismo, los residenciales Condominio Club Parques del Chipe I y II Etapa, Alameda del Chipe y Condominio Parques del Chipe.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/anuncian-corte-de-servicio-electrico-por-trabajos-de-reforzamiento-de-redes-en-vdo/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1044,145 +1056,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ExpoAmazónica Ucayali 2026:conoce la oferta productiva y turística de la región anfitriona</t>
+          <t>Trabajadores del hospital de Sullana contra nuevos funcionarios</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Este gran encuentro, oficializado por la Mancomunidad Regional Amazónica , busca fortalecer la articulación entre las regiones amazónicas, generar oportunidades para productores y emprendedores, y promover el desarrollo económico de la Amazonía.
-Entre sus actividades más destacadas están la II Expo Indígena y el VII Congreso de Emprendedores Amazónicos .
-A continuación, veamos cuál es la oferta productiva, agroindustrial y turística que exhibirá la región Ucayali, anfitriona de la ExpoAmazónica 2026 .
-Lea también: [ ¿Qué atributos le valieron a Perú para consagrarse como Destino Líder de Sudamérica 2026? ] Oferta Productiva y Agroindustrial Palma aceitera y derivados: La región destacará su liderazgo como principal productora de palma aceitera en el Perú.
-El Comité Central de Palmicultores de Ucayali (Cocepu) y empresas como Olamsa y Aopsa presentarán aceite crudo, mantecas y, como gran novedad, una nueva línea de cosméticos y cuidado personal (jabones, cremas y champús a base de palma).
-Cacao y derivados: Como una de las principales regiones productoras de cacao del Perú, se exhibirán chocolates de fino aroma, derivados y productos transformados.
-Cadenas productivas agrícolas: Muestra de papaya (en la que Ucayali también lidera a nivel nacional), frutas tropicales, maderas tratadas e iniciativas de bioeconomía.
-Asociatividad y Ruedas de Negocios: Espacios de articulación comercial con compradores nacionales e internacionales provenientes de Norteamérica, Europa y Asia.
-Lea también: [ Perú es elegido Destino de Naturaleza líder de Sudamérica en los World Travel Awards 2026 ] Oferta turística Turismo en diversos atractivos de la región , turismo vivencial con comunidades nativas, turismo de aventura, de naturaleza y de bienestar en salud.
-Cultura y gastronomía: Exposición de artesanía típica regional, música y danzas ucayalinas, exhibiciones gastronómicas con platos tradicionales y demostraciones de cocina amazónica en vivo a cargo de chefs locales y nacionales.
-Eventos académicos: Desarrollo del II Expo Indígena y el VII Congreso de Emprendedores Amazónicos 2026 , enfocado en innovación, conservación y desarrollo sostenible.
-Lea también: [ ¿Cuáles son las claves para que Perú se corone como Destino Cultural de Sudamérica 2026? ] Atractivos turísticos de Ucayali Poseedora de una cautivante belleza paisajística, gran biodiversidad, rica herencia cultural y afectuosa hospitalidad, Ucayali es no solo el segundo departamento más grande del Perú y de su región amazónica , sino que reúne todos los atributos para ser un destino de obligada visita y vivir una experiencia que deleite los sentidos y se grabe para siempre en la memoria.
-A continuación, repasemos los principales atractivos turísticos que pueden apreciarse en la ciudad de Pucallpa y en la región durante la celebración del Carnaval de Ucayali.
-Ciudad de Pucallpa El viaje inolvidable comienza en la ciudad de Pucallpa , cuyo nombre significa Tierra colorada , fundada hace 130 años y actual capital de la provincia de Coronel Portillo y de la región Ucayali .
-En el corazón de la ciudad se encuentra la Plaza de Armas , de construcción moderna y donde destaca un obelisco de 25 metros de alto, una pileta ornamental ubicada en el centro, así como esculturas en granito, arena y cemento que representan las costumbres de los pobladores mestizos e indígenas.
-Allí también se encuentra un monumento en homenaje al coronel Pedro Portillo Silva , promotor del progreso en la Amazonía.
-Bulevar Tacna Cerca de la Plaza de Armas se encuentra el bulevar Tacna, donde hay restaurantes, hospedajes y centros comerciales donde se vende artesanías locales.
-En el recorrido por la ciudad se pueden encontrar murales de arte amazónico que expresan sentimientos compartidos y enaltecen el patrimonio natural y cultural de Ucayali.
-Catedral Otro lugar emblemático es la Catedral de Pucallpa, inaugurada en diciembre de 2006 y diseñada con estilo arquitectónico ojival neogótico, fue construida con madera y porcelanato de España.
-El campanario levantado en una torre de 34 metros de alto y cuenta con 3 campanas traídas de Italia.
-Lea también: [ Diez lugares de la Amazonía peruana que los peruanos deben conocer ] Plaza del Reloj Público También destaca la Plaza del Reloj Público, donde se encuentra el monumento al héroe naval peruano Miguel Grau Seminario y un gran reloj que corona una torre de 25 metros, con trazos geométricos, que representa al pueblo indígena Yine.
-Construida entre 1950 y 1951, es la primera plaza que tuvo la ciudad.
-La torre cuenta con un mirador desde donde se aprecia el majestuoso río Ucayali.
-Comunidad 11 de Agosto Es una isla que se encuentra a 20 minutos en transporte fluvial desde el puerto Callao, en un sector de la gran laguna de Yarinacocha.
-Fue fundada el 11 de agosto de 1980 y allí residen alrededor de 200 habitantes que se dedican a la artesanía, principalmente a base de fibras recolectadas con cuidado de los bosques, como caña brava, sinami, bombonaje y corteza de plátano.
-Con esta materia prima orgánica se elaboran sombreros, abanicos, carteras, bolsos, joyeros, posa vasos, individuales, entre otros artículos utilitarios.
-Desde las orillas de la isla se contempla una hermosa vista de la laguna Yarinacocha.
-Comunidad nativa San Francisco Centro poblado más antiguo y numeroso entre las comunidades nativas del pueblo indígena amazónico Shipibo.
-Sus habitantes se dedican a la agricultura, pesca y turismo.
-La comunidad mantiene sus costumbres ancestrales: idioma, danzas, música, pintura de la cosmovisión, vestimenta, gastronomía, medicina tradicional y viviendas típicas.
-Alrededor de la comunidad se puede visitar la Plaza de la Charapita , realizar caminatas, campamentos y observar flora y fauna de la zona.
-En las noches se puede participar de sesiones chamánicas y toma de la ayahuasca, planta alucinógena usada desde tiempos milenarios por los chamanes o sacerdotes indígenas para acceder a la sabiduría amazónica y sus poderes sobrenaturales.
-Comunidad nativa Santa Clara Otra notables comunidad del pueblo indígena Shipibo cuyos habitantes conservan sus costumbres ancestrales, idioma, vestimenta, artesanía y viviendas típicas.
-Sus pobladores se dedican a la agricultura, pesca, recolección, medicina tradicional y turismo.
-La comunidad es ideal para aprender de la cultura shipiba.
-Por las noches se puede participar en sesiones chamánicas y toma de la ayahuasca.
-Lea también: [ Junín, la región que lo tiene todo, te espera con sus tesoros turísticos ] Museo etnográfico y natural Antonio Reátegui Rengifo Es uno de los primeros museos en su género implementados en la Amazonía peruana.
-Se ubica en el cruce de la avenida San Juan con el jirón Alfonso Ugarte, en el caserío San Juan de Yarinacocha.
-Allí se puede apreciar muestras etnográficas, fotografías, taxidermia, vestimentas de pueblos indígenas, cerámicas antiguas, instrumentos de pesca, armas de caza y de guerra, entre otros artículos de las comunidades indígenas de Ucayali.
-Laguna de Cashibococha Ubicada a 25 kilómetros desde el centro de la ciudad de Pucallpa, es una gran laguna que por su riqueza ictiológica es ideal para la práctica de pesca deportiva y también se puede realizar paseos en bote.
-En sus orillas, se encuentran asentadas diversas comunidades del pueblo indígena Shipibo, como Santa Teresita y San Salvador, que destacan por su bella artesanía de telas pintadas.
-Cuenta con el canal Cashibococha, que se conecta con la Laguna Yarinacocha.
-Los establecimientos alrededor de la laguna ofrecen servicios para la práctica de deportes acuáticos y pesca artesanal.
-Lea también: [ Ucayali: Dulces tradicionales casi olvidados resurgen y deleitan paladares con éxito ] Laguna de Yarinacocha La visita a Pucallpa no puede finalizar sin apreciar la hermosa laguna de Yarinacocha .
-De aguas tibias y tranquilas, es un antiguo meandro del río Ucayali creado por el cambio de su curso.
-En temporada de lluvias, la laguna se une con el río Ucayali a través de canales.
-Esta unión le da una gran riqueza ictiológica y permite que sus aguas se renueven periódicamente.
-En la laguna se puede pescar, esquiar, nadar, remar, observar aves y delfines de agua dulce.
-Alrededor de la laguna existen hospedajes, albergues y restaurantes.
-Se puede disfrutar de la gastronomía típica, adquirir frutas de temporada y artesanía.
-En época de verano se puede visitar la playa “Restinga” de gran belleza paisajística.
-Lea también: [ ¿Conoces el paraíso? Visita Loreto y cautívate con sus fabulosos tesoros turísticos ] Parque Nacional Sierra del Divisor Creado oficialmente como área protegida por el Estado en noviembre de 2015, es el tercer parque nacional más grande del Perú y es el complejo montañoso más antiguo ubicado en pleno llano de la Amazonía peruana.
-El Parque Nacional Sierra del Divisor posee paisajes espectaculares en la zona fronteriza con Brasil, formando un corredor biológico de más de 3 millones de hectáreas.
-Abarca territorios de la provincia de Coronel Portillo, en el departamento de Ucayali , y de las provincias de Ucayali, Requena y Maynas , pertenecientes al departamento de Loreto .
-Tiene una extensión de 1 millón 354,485.10 hectáreas.
-Las montañas que conforman la Sierra del Divisor tienen una gran pendiente y originan una divisoria de aguas a más de 900 metros sobre el nivel del mar.
-El complejo de conos y colinas de origen volcánico presente en la región Contamana-Abujao-El Divisor constituye el origen de infinidad de pequeñas cuencas que drenan sus aguas hacia el río Ucayali en el Perú y el Yuruá en Brasil.
-En dicho país existe un complejo de áreas naturales protegidas contiguas al Parque, las cuales forman un corredor biológico de más de tres millones de hectáreas.
-Geológicamente, la Sierra del Divisor constituye una de las zonas más antiguas de la Amazonía y posee paisajes espectaculares e inaccesibles.
-El Parque Nacional Sierra del Divisor presenta zonas poco intervenidas con un alto grado de conservación que abarcan ecosistemas y comunidades biológicas de especies de flora y fauna endémicas y de distribución restringida, lo que la convierte en un área de gran importancia.
-Así también, posee numerosas caídas de agua, aguas termales y colpas de guacamayos, de gran belleza y atractivo.
-La singular situación geográfica del Parque Nacional Sierra del Divisor, con sus montañas aisladas ha generado muchos endemismos.
-Es decir, en la zona se encuentra especies que solo existen en ese lugar.
-Solo en la Sierra del Divisor habita el “ave del divisorius” ( Thamnophilus divisorius ), también conocida como hormiguero de Acre , en referencia a la vecina región brasilera donde se le registró por primera vez en 2004.
-Posteriormente esta ave fue encontrada en el Perú.
-Existe una alta diversidad biológica en el Parque Nacional Sierra del Divisor .
-Es así que allí se encuentra el mayor número de especies de primates en el Perú (16 especies).
-Si se toma en cuenta ambos lados de la frontera, es decir, también el lado brasileño, el número de primates se eleva a 18, lo que representa uno de los más altos registros en el mundo.
-Destacan el huapo colorado , el mono choro, el coto mono, el machín negro, el pichico, el maquisapa, el machín blanco y el leoncito.
-También se ha registrado la presencia de otros mamíferos como la sachavaca, la huangana, el sajino, el hormiguero gigante, el armadillo gigante, así como carnívoros tales como el otorongo , el perro de monte, la nutria de río y el zorro de orejas cortas.
-En lo que respecta a aves, existe a la fecha cuatro nuevos registros para la ciencia, de los cuales 3 de ellos se encuentran solo en las alturas de las montañas aisladas.
-Las especies más representativas son las pavas de monte, el ave del divisorius, guacamayos y otros loros grandes y las garzas.
-Entre los anfibios y reptiles destacan la taricaya, el motelo, el caimán o lagarto blanco; diversas ranitas dardo-venenosas, y la especie de gecko más grande de la Amazonía.
-En lo que respecta a la flora, existen dos asociaciones vegetales probablemente únicas.
-La primera incluye bosques enanos y manchales de bromelias terrestres que crece en las cumbres secas de las antiguas formaciones calizas en las sierras de Contamana, Contaya y Jaquerana, en la mitad norte del parque.
-La otra asociación crece en los precipicios y en las cumbres de granito antiguo de volcanes muertos, incluyendo el cerro San Lucas, en la mitad sur del Parque Nacional Sierra del Divisor .
-Ambos tipos de vegetación deben tener docenas de especies de plantas desconocidas para la ciencia, varias de ellas restringidas a Sierra del Divisor.
-Rutas turísticas El Parque Nacional Sierra del Divisor alberga la única región montañosa al este de Ucayali y Loreto que sobresale en la selva baja con elevaciones aisladas como el Cono o Cerro Aguja y San Lucas.
-No obstante, estos miradores naturales se encuentran en un lugar poco accesible, al sur del área natural protegida.
-Por el sector oeste, a 20 kilómetros por una trocha carrozable desde la ciudad de Contamana , se llega a las aguas termales sulfurosas de Aguas Calientes .
-Además, se puede apreciar una colpa de guacamayos ubicada a 40 kilómetros de Contamana, a la que se llega por un sendero pedestre rodeada de tramos de selva tupida, la cual está cerca de una bella catarata denominada “el llanto de la anaconda”.
-Lea también: [ ¡Orgullo peruano! El seco de cabrito vuelve a ser elegido el mejor guiso del mundo ] Gastronomía típica La región Ucayali ofrece una amplia gama de potajes amazónicos preparados con los ingentes recursos naturales que posee y los conocimientos culinarios heredados desde tiempos ancestrales y perfeccionados con innovadoras técnicas gastronómicas que le confieren un valor agregado sin perder la identidad ucayalina .
-A continuación, conoce y saborea los emblemáticos platos que son estandartes de la cocina de Ucayali.
-Juane Es el plato insignia de esta región y de toda la Amazonía peruana.
-Se trata de un sabroso potaje preparado con arroz, huevos sancochados, gallina y especias envueltas y cocidas en una hoja de bijao, la cual simboliza la cabeza de San Juan Bautista, el patrono de la selva peruana.
-Las amas de casa acostumbran acudir a tempranas horas, de preferencia un día antes de la festividad, al mercado en busca de los insumos para preparar el emblemático potaje amazónico.
-Además del típico juane a base de arroz, existen otras variedades según los ingredientes con los que se preparan.
-Juane de yuca: Lleva yuca molida en vez de arroz y se rellena con pescado, especialmente paiche.
-Avispa Juane: Se añade al arroz carne de cerdo molida y con ello se prepara la masa, rellenándose con una presa de gallina frita.
-Nina Juane: Es un juane que lleva trozos de gallina con huevo batido en vez de arroz.
-Sara juane: En vez de arroz lleva una mezcla de maní crudo molido, maíz molido y caldo de pollo.
-Juane de chonta: Se añade chonta picada a la mezcla de arroz.
-Lea también: [ ¿Por qué el chancho al palo es plato embajador de Huaral y cómo posicionó a este destino? ] Tacacho con cecina Es otro de los platos emblemáticos de la Amazonía peruana, no solo por su popularidad, sino también por su delicioso sabor.
-Está hecho a base de plátano verde cocido, triturado y bañado en manteca de cerdo, combinación que da lugar a unas esferas del tamaño de un puño pequeño, rellenas con trozos de cecina -carne ahumada tradicional de la Amazonía-.
-Se sirve junto a una buena porción de cecina frita y plátano maduro asado a la parrilla.
-Patarashca Es uno de los potajes tradicionales en los que el pescado cobra un gran protagonismo.
-Este plato está hecho a base de pescado fresco de río, sazonado por dentro con condimentos locales y asado a la parrilla envuelto en hoja de bijao.
-El resultado de este proceso culinario es un sabroso pescado ahumado, maridable con plátano o yuca sancochada, ají de cocona y un irresistible refresco de camu camu, el fruto considerado un superalimento por sus extraordinarias propiedades nutritivas.
-Inchicapi El nombre de este potaje proviene de los vocablos quechuas “inchik”, que significa maní, y “api”, que significa sopa.
-Al inchicapi se le considera la “sopa del poder” para los habitantes del oriente peruano, dado que otorga las energías necesarias para sobrellevar sin cansancio la jornada laboral diaria.
-Su receta incluye presas de gallina, maní, harina de maíz y sachaculantro, ingredientes con una gran cantidad de proteínas ideales para el eventual friaje amazónico o para cualquier ocasión especial.
-Se sirve acompañado de arroz graneado y una porción de yuca cocinada.
-Ensalada de chonta Se trata de un plato de entrada emblemático en el menú amazónico y es imposible de encontrar en otras partes del Perú, dado que el ingrediente principal es la chonta, una palmera que solamente crece en la selva y de la que se extraen unas finas tiras blancas que son las protagonistas de este potaje.
-Para quienes prefieren disfrutar de un plato ligero, pueden degustar esta entrada preparada también con lechuga, tomate, palta, limón y sal para obtener una deliciosa ensalada con un sabor único y muy agradable al paladar.
-Sudado de doncella Si bien el sudado es un guiso a base de pescado muy popular, sobre todo en la costa peruana, en la Amazonía adquiere una personalidad particular gracias a la amplia variedad de peces que existen en los ríos de la selva.
-De las diversas especies de peces destaca la doncella, un pez que se caracteriza por su deliciosa carne que, a diferencia de otros peces selváticos, carece de espinas por lo que se puede aprovechar en su casi totalidad.
-Los ingredientes utilizados para preparar este delicioso potaje son similares al del sudado tradicional: ajos, ají especial y cebolla para el aderezo base, así como caldo de pescado, chicha de jora, kion, sacha tomate, sacha culantro, sal y pimienta al gusto.
-Este plato se sirve acompañado de porciones de yuca y arroz blanco sancochado, así como rodajas de limón y ajíes amazónicos como decoración sobre el guiso.
-Timbuche de carachama Timbuche es el nombre con el que se conoce al chilcano en la gastronomía selvática.
-Y tiene como ingrediente estelar a la carachama, un pez prehistórico similar al bagre muy consumido por la población amazónica.
-Este suculento potaje es considerado un reparador de energías.
-Ello responde a su extraordinario valor nutricional, dado que contiene proteínas, vitaminas A, C, E y B12 , así como minerales como fósforo, hierro y yodo que lo convierten en un poderoso aliado en la lucha contra la anemia y la desnutrición.
-Para preparar el timbuche se utiliza un pescado entero por persona, y se utilizan ingredientes como ajos picados, cebolla cortada en cuadritos, sacha tomate, sal al gusto y la cantidad de agua necesaria para tener un caldo consistente.
-Antes de servir se añade huevos batidos y sacha culantro picado para decorar.
-Ceviche amazónico El plato embajador del Perú , que se sustenta en trozos de pescado fresco marinados, también se adaptó a la realidad amazónica, dada la existencia de una gran variedad de peces que facilitan la preparación de este potaje que seduce paladares en el mundo.
-Los ceviches amazónicos más tradicionales tienen como insumos protagonistas al paiche y la doncella , cuya carne tiene la consistencia y la abundancia necesarias para marinarse armoniosamente con el zumo de limón, camu camu y salsas a base de ajíes amazónicos que le confieren el seductor encanto a este plato embajador de la cocina peruana.
-Chapo Popular bebida que se prepara con plátanos maduros que luego son hervidos y licuados con leche y azúcar al gusto.
-Aguajina Refresco tradicional a base de la pulpa del aguaje, fruto de la palmera del mismo nombre, el cual se diluye en agua y posteriormente se le agrega azúcar.
-Masato Bebida elaborada con agua y pulpa de yuca fermentada, la cual se deja reposar con el objetivo de que el almidón del tubérculo se vuelva azúcar y con ello no es necesario endulzarla.
-¿Cómo llegar a Ucayali? La manera más sencilla de llegar a Ucayali es por vía aérea.
-El vuelo desde la ciudad de Lima hasta la ciudad de Pucallpa dura unos cincuenta minutos, lo mismo que desde la ciudad de Iquitos.
-Otra opción es llegar por vía terrestre, atravesando el centro del Perú por la Carretera Central en un viaje cuya duración es de aproximadamente 16 horas.</t>
+          <t>A 70 días de culminar la actual gestión regional, los trabajadores del Hospital de Especialidades de Sullana alzaron su voz de protesta contra las últimas designaciones de funcionarios dispuestas por el gobernador regional Luis Neyra, al cuestionar que algunos de los nuevos responsables no contarían con el perfil técnico ni la experiencia requerida para asumir sus cargos. Mediante un pronunciamiento conjunto, los gremios expresaron su rechazo a estos cambios, entre ellos el del nuevo administrador del establecimiento, y advirtieron que las designaciones realizadas a lo largo de 2026 vienen generando inestabilidad laboral y preocupación entre el personal del nosocomio. Los trabajadores señalaron que esta situación resulta especialmente preocupante debido a que el hospital se encuentra inmerso en el proceso de recategorización para alcanzar el nivel de complejidad III-1. A ello se suma el riesgo que afronta la región ante un eventual fenómeno de El Niño, escenario que exige una adecuada capacidad de respuesta del sistema sanitario. En el documento, los firmantes remarcaron que estas circunstancias demandan estabilidad institucional, continuidad operativa y decisiones responsables, sustentadas en criterios técnicos que permitan garantizar la adecuada prestación de los servicios de salud a la población. Por ello, solicitaron a las autoridades regionales que respeten la estabilidad de los equipos de gestión.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-expoamazonica-ucayali-2026conoce-oferta-productiva-y-turistica-de-region-anfitriona-1096213.aspx</t>
+          <t>https://eltiempo.pe/local/trabajadores-del-hospital-de-sullana-contra-nuevos-funcionarios/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -1190,24 +1081,24 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Sullana (Piura)</t>
+          <t>Sismo en Piura de 4.1: ¿dónde se registró el epicentro de esta madrugada?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Sullana, según el conteo oficial de la ONPE al 98.088% , arroja el siguiente resultado (actualizado el 17/10/2026, a las 18:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Un sismo de magnitud 4.1 remeció la región Piura durante la mañana de este día, según el reporte del Instituto Geofísico del Perú (IGP). El movimiento telúrico se registró a las 5:53 a. m. y tuvo su epicentro en territorio ecuatoriano, a 104 kilómetros al noreste de Ayabaca, de acuerdo con la información difundida por la institución. El evento sísmico tuvo una profundidad de 100 kilómetros, un factor que permite caracterizar el movimiento registrado en la zona fronteriza entre Perú y Ecuador. Hasta el momento de la información proporcionada, las autoridades locales no habían reportado daños materiales ni víctimas como consecuencia del temblor. El movimiento volvió a poner en atención la actividad sísmica que caracteriza al norte del país. Aunque no se informaron consecuencias graves, los especialistas recuerdan que los sismos pueden presentarse en cualquier momento y que la preparación de las familias resulta importante para reducir los riesgos ante una emergencia. Sismo en Piura: ¿dónde se registró el epicentro? Según el reporte del Instituto Geofísico del Perú, el epicentro del sismo de magnitud 4.1 se localizó en territorio ecuatoriano, a 104 kilómetros al noreste de Ayabaca, provincia ubicada en la sierra de la región Piura. El movimiento ocurrió a las 5:53 a. m., con una profundidad de 100 kilómetros. Estos datos permiten identificar la ubicación y las características principales del evento sísmico, aunque la percepción del temblor puede variar dependiendo de la distancia al epicentro, la profundidad y las condiciones del terreno. La cercanía geográfica entre el norte peruano y el sur de Ecuador hace que los movimientos telúricos registrados en uno de estos territorios puedan sentirse en el otro. Por ello, los reportes sísmicos de ambos países son relevantes para las poblaciones que viven en las zonas fronterizas. Para conocer los detalles de un evento, la población puede consultar la información oficial del Instituto Geofísico del Perú (IGP) , entidad encargada de estudiar la actividad sísmica en el territorio nacional. ¿Se reportaron daños por el temblor en Piura? De acuerdo con la información disponible, las autoridades locales no habían comunicado daños materiales ni víctimas relacionados con el sismo de magnitud 4.1. Sin embargo, la ausencia de reportes de daños no significa que la población deba dejar de lado las medidas de prevención. Ante un movimiento telúrico, se recomienda mantener la calma, alejarse de ventanas y objetos que puedan caer y ubicarse en una zona segura previamente identificada. Después del temblor, es importante revisar las condiciones de la vivienda sin exponerse a estructuras que presenten daños visibles. También se debe prestar atención a las indicaciones de las autoridades y evitar difundir información no confirmada sobre posibles consecuencias. En Perú, el Instituto Nacional de Defensa Civil (Indeci) ofrece recomendaciones para que las familias sepan cómo actuar antes, durante y después de una emergencia. Estas medidas incluyen preparar una mochila de emergencia, identificar rutas de evacuación y establecer un punto de encuentro familiar. La información preventiva puede consultarse en el portal oficial del Instituto Nacional de Defensa Civil . Preocupación por la energía sísmica acumulada en la costa central del Perú Mientras el norte del país registraba este movimiento telúrico, la actividad sísmica en la costa central peruana volvió a ser motivo de atención por las advertencias de especialistas sobre la energía acumulada en esa parte del territorio nacional. En declaraciones a RPP, el sismólogo César Jiménez Tintaya, profesor de la Universidad Nacional Mayor de San Marcos (UNMSM), advirtió que la costa central mantiene una importante acumulación de energía sísmica asociada al último gran terremoto ocurrido en Lima en 1746. El especialista explicó que, desde aquel evento, se han registrado otros terremotos importantes en el siglo XX y comienzos del XXI. Entre ellos mencionó los ocurridos en 1940, en la zona de Huacho; en 1966, cerca de Barranca; en 1974, en el sector de Chilca-Lima; y en 2007, en Pisco, región Ica. Según la explicación recogida por RPP, estos terremotos habrían liberado solo una parte de la energía sísmica acumulada en la región central. El especialista señaló que la cantidad restante constituye un motivo para reforzar la prevención y la preparación ante posibles terremotos de gran magnitud. Las estimaciones mencionadas por el experto contemplan la posibilidad de un terremoto de magnitud superior a 8.0, e incluso de entre 8.5 y 8.8, en la costa central. No obstante, estas declaraciones no representan una predicción de fecha u hora: actualmente, no es posible determinar con precisión cuándo ocurrirá un terremoto ni cuál será su magnitud exacta. ¿El sismo de Piura está relacionado con un posible terremoto en Lima? El sismo de magnitud 4.1 registrado al noreste de Ayabaca y las advertencias sobre la energía acumulada en la costa central corresponden a contextos sísmicos distintos. Con la información disponible, no existe evidencia presentada que permita afirmar que ambos fenómenos estén directamente relacionados. Los movimientos telúricos se producen por procesos geológicos que pueden variar según la ubicación, la profundidad y las características de las fallas involucradas. Por eso, un temblor registrado en la frontera entre Perú y Ecuador no debe interpretarse automáticamente como una señal de que ocurrirá un terremoto de gran magnitud en Lima. Las declaraciones de los especialistas sobre la costa central deben entenderse dentro del análisis del riesgo sísmico de largo plazo. La acumulación de energía tectónica es un aspecto relevante para la evaluación de amenazas, pero no permite establecer una fecha específica para un futuro evento. Para conocer los reportes sísmicos y las recomendaciones oficiales, se puede revisar la página del Instituto Geofísico del Perú y la información de prevención publicada por el Indeci . ¿Qué hacer ante un sismo en la región Piura? Ante un movimiento telúrico, las autoridades recomiendan priorizar la seguridad personal y evitar desplazamientos apresurados que puedan provocar accidentes. Si el temblor ocurre dentro de una vivienda, es importante protegerse y mantenerse alejado de vidrios, muebles altos y objetos que puedan desprenderse. Las familias también deben identificar las zonas seguras de sus viviendas, conocer las rutas de evacuación y mantener disponibles artículos esenciales, como agua, alimentos no perecibles, una linterna, una radio portátil, medicamentos necesarios y documentos importantes protegidos. En las zonas rurales y urbanas de Piura, la preparación debe considerar las características de cada vivienda y las condiciones del entorno. Los integrantes de una familia deben saber cómo comunicarse si quedan separados y qué lugares pueden utilizar como puntos de encuentro después de una emergencia. La información sobre la magnitud, el epicentro y la profundidad de un sismo debe verificarse mediante fuentes oficiales. Compartir datos confirmados ayuda a evitar la propagación de rumores y permite que la población tome decisiones con mayor tranquilidad. ¿Dónde consultar información oficial sobre los sismos en Perú? El Instituto Geofísico del Perú publica información relacionada con los movimientos sísmicos registrados en el país. Por su parte, el Indeci difunde orientaciones para la preparación y respuesta ante emergencias. La población también puede revisar los comunicados de las autoridades locales y regionales para conocer posibles evaluaciones de daños o recomendaciones específicas para su zona. En situaciones de emergencia, es importante seguir las instrucciones de los organismos competentes y no basarse únicamente en publicaciones difundidas por redes sociales. El sismo de magnitud 4.1 registrado a las 5:53 a. m., con epicentro en Ecuador y a 104 kilómetros al noreste de Ayabaca, volvió a recordar la importancia de mantener una cultura de prevención en Piura y en el resto del país.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-sullana-piura-noticia/</t>
+          <t>https://eltiempo.pe/local/sismo-en-piura-de-4-1-donde-se-registro-el-epicentro-de-esta-madrugada/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -1215,24 +1106,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Talara (Piura)</t>
+          <t>Temperaturas de hasta 38 °C en Piura y Tumbes será hasta fin de octubre, prevé Senamhi</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Talara, según el conteo oficial de la ONPE al 98.177% , arroja el siguiente resultado (actualizado el 17/10/2026, a las 18:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>Las temperaturas máximas de hasta 38 °C continuarán en Piura y Tumbes durante la segunda quincena de octubre, según el pronóstico del Servicio Nacional de Meteorología e Hidrología del Perú (Senamhi). Las condiciones cálidas se mantendrán tanto durante el día como en la noche, en un escenario asociado al actual evento El Niño costero. De acuerdo con el organismo, adscrito al Ministerio del Ambiente (Minam), las altas temperaturas se presentarán entre el sábado 17 y el sábado 31 de octubre. Durante este periodo, los valores máximos en ambas regiones oscilarán entre 32 °C y 38 °C, mientras que las temperaturas mínimas se situarán entre 22 °C y 25 °C. El pronóstico también contempla lluvias dispersas en algunos sectores de la costa norte, además de variaciones en la cobertura nubosa y ráfagas de viento en determinadas zonas del litoral peruano. Senamhi pronostica temperaturas de hasta 38 °C en Piura En Piura, el calor continuará siendo una de las principales características de las condiciones meteorológicas previstas para lo que resta de octubre. Las temperaturas máximas podrían alcanzar los 38 °C, mientras que durante la noche los termómetros registrarían valores de entre 22 °C y 25 °C. Estas condiciones implican que el descenso de la temperatura durante las horas nocturnas no será suficiente para eliminar la sensación de calor. Por ello, los habitantes de las zonas urbanas y rurales deberán prestar atención a los cambios meteorológicos y a los avisos emitidos por las autoridades. El Senamhi señaló que el comportamiento del tiempo estará relacionado con las condiciones atmosféricas y oceánicas vinculadas al actual episodio de El Niño costero. El calentamiento de la superficie del mar y el ingreso de vientos del norte figuran entre los factores que favorecen el incremento de las temperaturas en la franja costera. ¿Qué temperaturas se esperan en Tumbes hasta el 31 de octubre? En Tumbes se prevé un escenario similar al de Piura, con temperaturas máximas de entre 32 °C y 38 °C y mínimas que oscilarán entre 22 °C y 25 °C. El pronóstico comprende el periodo del 17 al 31 de octubre, durante el cual persistirán las condiciones cálidas en la costa norte. El comportamiento de la nubosidad también variará a lo largo del día. Según la información meteorológica difundida, se espera cielo nublado durante las primeras horas de la mañana, seguido de una disminución de la nubosidad hacia el mediodía y la tarde. Posteriormente, la cobertura nubosa podría incrementarse nuevamente. Además de las altas temperaturas, el pronóstico contempla lluvias dispersas en algunos sectores de la costa norte. Estas precipitaciones no necesariamente se presentarán con la misma intensidad ni en todas las localidades, por lo que resulta importante consultar los reportes oficiales correspondientes a cada zona. ¿Por qué aumentan las temperaturas en la costa norte? El Senamhi explicó que el incremento del calor está relacionado principalmente con el calentamiento de la superficie marina y el ingreso de vientos provenientes del norte. Ambos factores influyen en las condiciones atmosféricas de la costa y favorecen la persistencia de temperaturas elevadas. Otro elemento que podría contribuir a mantener el calor se presentaría entre el 27 y el 31 de octubre. Durante esos días, el ingreso de aire seco en los niveles medios de la atmósfera favorecería las altas temperaturas. Este proceso está relacionado con la subsidencia, fenómeno que consiste en el descenso de masas de aire hacia niveles inferiores de la atmósfera. Estas condiciones pueden limitar determinados procesos de formación de nubes y contribuir a mantener un ambiente cálido. La evolución de estos factores dependerá de las condiciones atmosféricas y oceánicas. Por ese motivo, los pronósticos deben revisarse periódicamente, especialmente cuando se anuncian cambios en las temperaturas, lluvias o vientos. Temperaturas previstas en otras regiones de la costa peruana Las altas temperaturas no se limitarán a Piura y Tumbes. El pronóstico del Senamhi también contempla valores elevados en otras regiones de la costa peruana durante la segunda mitad de octubre. En Lambayeque e Ica, las temperaturas máximas se situarían entre 30 °C y 38 °C. En La Libertad, los registros oscilarían entre 28 °C y 32 °C, mientras que en Lima y Áncash se esperan máximas de entre 27 °C y 34 °C. En la costa sur, las temperaturas máximas variarían entre 26 °C y 33 °C. Los valores previstos muestran diferencias entre las regiones, debido a las características geográficas y a las condiciones meteorológicas de cada sector del litoral. En cuanto a las temperaturas mínimas, Lambayeque registraría valores de entre 22 °C y 24 °C, mientras que en La Libertad se esperan registros de entre 21 °C y 24 °C. Para Lima y Áncash, las mínimas oscilarían entre 18 °C y 23 °C. ¿Cuánto calor hará en Lima Metropolitana? En Lima Metropolitana, las temperaturas máximas alcanzarían aproximadamente los 26 °C en los distritos de Lima oeste y los 29 °C en Lima norte y este. Durante la noche, las temperaturas mínimas se ubicarían entre 22 °C y 23 °C. Estas condiciones también estarán acompañadas por variaciones en la nubosidad. En algunos sectores de la costa central podrían presentarse niebla, neblina y lloviznas, principalmente durante la noche y las primeras horas de la mañana. Senamhi advierte sobre ráfagas de viento, niebla y lloviznas Además del calor, el pronóstico meteorológico contempla ráfagas de viento en algunos sectores de la costa peruana entre el 20 y el 26 de octubre. Estas condiciones podrían favorecer la aparición de niebla y neblina durante la noche y al amanecer, así como la ocurrencia de lloviznas dispersas. Estos fenómenos pueden reducir la visibilidad en determinados lugares y modificar las condiciones habituales del tiempo, especialmente durante las primeras horas del día. Su presencia dependerá de las características meteorológicas locales. Ante este escenario, el Ministerio del Ambiente y el Senamhi recomendaron a la población mantenerse informada mediante los avisos y pronósticos oficiales. Consultar las actualizaciones permite conocer la evolución de las temperaturas y otros fenómenos previstos para cada región.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-talara-piura-noticia/</t>
+          <t>https://eltiempo.pe/local/temperaturas-de-hasta-38-c-en-piura-y-tumbes-sera-hasta-fin-de-octubre-preve-senamhi/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -1240,24 +1131,33 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la región de Piura</t>
+          <t>Presidenta Fujimori sostuvo reuniones de trabajo con ministro de Educación y el canciller</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Piura, según el conteo oficial de la ONPE al 98.347% , arroja el siguiente resultado (actualizado el 17/10/2026, a las 18:06.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>En el encuentro con el titular del Minedu, dialogaron sobre las políticas del sector, las próximas medidas a implementar y los nuevos Lineamientos para la Gestión de la Disciplina Escolar , los cuales establecen reglas y procedimientos para fortalecer el respeto en las instituciones educativas públicas y privadas, recuperar el orden y restituir la autoridad de los docentes.
+Lee también: [ Minsa instala mesa de alto nivel para fortalecer la atención de la salud mental ] Asimismo, en la reunión entre la mandataria y el titular de Educación se abordaron las acciones anticipadas que viene desarrollando el sector ante el fenómeno El Niño, entre ellas la entrega oportuna de los recursos educativos para el Año Escolar 2027 , entre otros.
+Por otro lado y como parte de su agenda de trabajo, la mandataria también se reunió con el ministro de Relaciones Exteriores, Carlos Espá, a fin de revisar la agenda de política exterior que promueve el Gobierno .
+En la víspera, la jefa de Estado visitó las regiones Piura y La Libertad , donde afirmó que su Gobierno viene ejecutando trabajos de prevención desde el inicio de su gestión en las regiones donde se esperan lluvias intensas por el fenómeno El Niño.
+FIN) NDP/HTC Más en Andina: ??????? ¡Desde el espacio se combate la minería ilegal en el Perú! La Fuerza Aérea del Perú (FAP) utiliza tecnología satelital para detectar actividades ilegales en la Amazonía.
+???? En Madre de Dios, el análisis de imágenes satelitales permitió identificar 236 dragas, 118 canaletas de lavado de mineral, 242 instalaciones operativas y cinco campamentos clandestinos.?? Además, se evidenció la degradación de más de 4 000 hectáreas de bosque amazónico.??? Esta tecnología permite a las fuerzas del orden planificar operativos contra la minería ilegal.?? Conoce más en la Agencia Andina:https://t.co/5njNTuwbAY#MineríaIlegal #FAP #MadreDeDios #Amazonía #Perú (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 17, 2026 Publicado: 17/10/2026 (function(){ window.addEventListener('message', function(e){ if (e.data &amp;&amp; e.data.tipo === 'andina-alto' &amp;&amp; e.data.alto) { var f = document.getElementsByTagName('iframe'); for (var i = 0; i &lt; f.length; i++) { if (f[i].contentWindow === e.source) { f[i].style.height = e.data.alto + 'px'; } } } }); })(); googletag.cmd.push(function () { googletag.display('top3_ad'); }); PUBLICIDAD MGID - UNDER ARTICLE (29/09/2026), tag entregado por Comercial (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); /////////////////// CARRUSEL DE VIDEOS EN STOP //////////////////// /////////// CARRUSEL DE VIDEOS /////////// Videos Andina Población confinada y rescates en helicóptero por graves inundaciones en el este de España access_time 1:15 Presidenta Keiko Fujimori recibe al Señor de los Milagros en Palacio de Gobierno access_time 2:02 Federico Kauffmann: el legado de un arqueológo construido en familia access_time 3:26 Pensionistas usan IA para enviar mensajes de apoyo al papa León XIV access_time 2:42 Del culto ancestral a la ciencia: ingenieros peruanos transforman la humedad en agua potable access_time 2:43 Salsa criolla: un encuentro de ritmos con identidad peruana access_time 3:30 Caral nos presenta nuevos hallazgos en 32 años de investigación access_time 2:35 Cuidados paliativos: alivio y acompañamiento en los momentos más difíciles access_time 2:56 Presidenta: Tenemos que ponernos la camiseta blanca y roja para enfrentar a El Niño access_time 1:25 ERM 2026: audiencias de recuento de votos inicia 12 de octubre access_time 1:40 El coro para León XIV: dos generaciones y un mismo sentimiento access_time 3:24 Presidenta Fujimori: No vamos a parar hasta recuperar la paz y el orden en nuestro país access_time 2.30 PUBLICIDAD PROGRAMATICA LEADER1 (SOLO MOBILE) ////////////////////////////// ASIDE ////////////////////////////// // VIDEO /////////// Video más visto ////////////////////////// LAS MAS LEIDAS ///////////////////////// ////////////////////////// LAS MAS LEIDAS LATERAL///////////////////////// Las más leídas Cronograma de pagos 2026 de sueldos en el Estado peruano Examen de Admisión UNMSM 2027-I: conoce aquí los resultados de las dos primeras fechas Senamhi: fenómeno El Niño entra en fase extraordinaria y favorecerá lluvias extremas Facultades delegadas: Comisión de Constitución del Senado retoma hoy debate Señor de los Milagros: conoce la ruta de su tercera procesión de hoy lunes 19 La Libertad: hallan los primeros vestigios de la cultura Mochica en el valle de Chicama Comisión de Ética de Diputados evaluará hoy lunes denuncias contra tres legisladores Temblor hoy en Perú, lunes 19 de octubre: sismo de magnitud 3.5 se registra en Huarochirí ExpoAmazónica Ucayali 2026:conoce la oferta productiva y turística de la región anfitriona Minsa ofrecerá chequeos gratuitos de cáncer de mama en dos centros comerciales de Lima ////////////////////////// FIN LAS MAS LEIDAS ///////////////////////// //////// PUBLICIDAD INTERNA ////// //////// PUBLICIDAD PROGRAMATICA CENTER1 ////// $(document).ready(function () { $('.materialboxed').materialbox(); }); (function () { var path = window.location.pathname; // ej: "///////noticia-peru-..." // Si path comienza con más de una barra if (/^\/{2,}/.test(path)) { // Reemplazar múltiples '/' por uno solo al inicio var nuevaPath = path.replace(/^\/+/, '/'); // Reconstruir la URL completa var nuevaUrl = window.location.protocol + '//' + window.location.host + nuevaPath + window.location.search + window.location.hash; // Redirigir a la URL limpia window.location.replace(nuevaUrl); console.log(nuevaUrl); } })(); /////////////// FOOTER /////////////// LOGOS CONVENIOS Director(e): Félix Paz Quiroz Gerente General(e): Félix Paz Quiroz Av.
+Alfonso Ugarte 873 Lima 1 Teléfono: (51-1) 315 0400 Fax: 431 2849 ENGLISH VERSION Inicio Lo último Política Economía Locales Regionales Internacional Cultural Ánfora 2026 Deportes Clic Perfiles y Crónicas Ciencia y Tecnología Cambio Climático Canal Online Videos Especiales Interactivos Podcast Newsletter Nosotros Especiales Elecciones 2026 Enfermedades raras en Perú Joyas religiosas en Lima Foro de Cooperación Económica Asia-Pacífico Embarazo adolescente: el costo de la maternidad temprana Perú y Corea hermanados por la gastronomía Inti Raymi: el Sol sale para todos Editora Perú | Acerca de Andina | Términos | Privacidad © 2025 Agencia Peruana de Noticias.
+Todos los derechos reservados.
+(function () { 'use strict'; function fechaConsulta() { var meses = ['enero', 'febrero', 'marzo', 'abril', 'mayo', 'junio', 'julio', 'agosto', 'septiembre', 'octubre', 'noviembre', 'diciembre']; var d = new Date(); return d.getDate() + ' de ' + meses[d.getMonth()] + ' de ' + d.getFullYear(); } function tituloLimpio() { var t = (document.title || '').replace(/\s*\|\s*ANDINA.*$/i, '') .replace(/^Agencia Peruana de Noticias\s*\|\s*/i, '') .trim(); return t || 'Agencia Peruana de Noticias Andina'; } document.addEventListener('copy', function (e) { var seleccion = (window.getSelection ? window.getSelection().toString() : ''); if (!seleccion || seleccion.length &lt; 50) return; var url = window.location.href; var titulo = tituloLimpio(); var fecha = fechaConsulta(); var encabezado = 'Este contenido puede reproducirse citando a la Agencia Andina ©️ Editora Perú\n\n'; var cierre = '\n\nLea más en: ' + url; var textoFinal = encabezado + seleccion + cierre; if (e.clipboardData &amp;&amp; e.clipboardData.setData) { e.clipboardData.setData('text/plain', textoFinal); e.preventDefault(); } else if (window.clipboardData &amp;&amp; window.clipboardData.setData) { window.clipboardData.setData('Text', textoFinal); e.returnValue = false; } }); function copiarTexto(texto) { if (navigator.clipboard &amp;&amp; navigator.clipboard.writeText) { navigator.clipboard.writeText(texto); } else { var ta = document.createElement('textarea'); ta.value = texto; ta.style.position = 'fixed'; ta.style.opacity = '0'; document.body.appendChild(ta); ta.select(); try { document.execCommand('copy'); } catch (e) { } ta.remove(); } } function mostrarMenuPersonalizado(x, y, img) { var anterior = document.getElementById('andina-img-menu'); if (anterior) anterior.parentNode.removeChild(anterior); var menu = document.createElement('div'); menu.id = 'andina-img-menu'; menu.style.cssText = 'position:fixed;top:' + y + 'px;left:' + x + 'px;' + 'background:#fff;border:1px solid #d0d0d0;border-radius:5px;' + 'box-shadow:0 6px 20px rgba(0,0,0,.18);padding:5px 0;' + 'font-family:Arial,sans-serif;font-size:13px;min-width:240px;' + 'z-index:1;'; var opciones = [ { txt: 'Abrir imagen en nueva pestaña', fn: function () { window.open(img.src, '_blank'); } }, { txt: 'Copiar dirección de la imagen', fn: function () { copiarTexto(img.src); } } ]; opciones.forEach(function (opt) { var item = document.createElement('div'); item.textContent = opt.txt; item.style.cssText = 'padding:9px 18px;cursor:pointer;color:#222;user-select:none;'; item.addEventListener('mouseenter', function () { item.style.background = '#eef3f9'; }); item.addEventListener('mouseleave', function () { item.style.background = 'transparent'; }); item.addEventListener('click', function () { opt.fn(); if (menu.parentNode) menu.parentNode.removeChild(menu); }); menu.appendChild(item); }); var sep = document.createElement('div'); sep.style.cssText = 'border-top:1px solid #eee;margin:4px 0;'; menu.appendChild(sep); var pie = document.createElement('div'); pie.textContent = 'Foto: ANDINA / Editora Perú'; pie.style.cssText = 'padding:6px 18px;font-size:11px;color:#888;font-style:italic;'; menu.appendChild(pie); document.body.appendChild(menu); var rect = menu.getBoundingClientRect(); if (rect.right &gt; window.innerWidth) menu.style.left = (window.innerWidth - rect.width - 10) + 'px'; if (rect.bottom &gt; window.innerHeight) menu.style.top = (window.innerHeight - rect.height - 10) + 'px'; setTimeout(function () { document.addEventListener('click', function cerrar(ev) { if (!menu.contains(ev.target)) { if (menu.parentNode) menu.parentNode.removeChild(menu); document.removeEventListener('click', cerrar); } }); document.addEventListener('contextmenu', function cerrarCtx(ev) { if (!menu.contains(ev.target)) { if (menu.parentNode) menu.parentNode.removeChild(menu); document.removeEventListener('contextmenu', cerrarCtx); } }); }, 0); } function mostrarModalImagen(img, callback) { var anterior = document.getElementById('andina-img-modal'); if (anterior) anterior.parentNode.removeChild(anterior); var rect = img.getBoundingClientRect(); var scrollY = window.pageYOffset || document.documentElement.scrollTop; var scrollX = window.pageXOffset || document.documentElement.scrollLeft; // Overlay sobre el área de la imagen, con flexbox para centrar el modal var overlay = document.createElement('div'); overlay.id = 'andina-img-modal'; overlay.style.cssText = 'position:absolute;' + 'top:' + (rect.top + scrollY) + 'px;' + 'left:' + (rect.left + scrollX) + 'px;' + 'width:' + rect.width + 'px;' + 'height:' + rect.height + 'px;' + 'background:rgba(0,0,0,.7);z-index:1;' + 'display:flex;align-items:center;justify-content:center;' + 'font-family:Arial,sans-serif;opacity:0;transition:opacity .2s ease-in;' + 'overflow:hidden;cursor:pointer;'; // Modal con tamaño "natural" (referencia en imagen grande) var anchoNatural = 320; var altoNatural = 170; // Escala proporcional para que quepa con margen del 10% en cualquier imagen var escalaX = (rect.width * 0.90) / anchoNatural; var escalaY = (rect.height * 0.90) / altoNatural; var escala = Math.min(escalaX, escalaY, 1); // máx 1 (no se agranda) var caja = document.createElement('div'); caja.style.cssText = 'background:#fff;border-radius:6px;padding:18px 22px;' + 'width:' + anchoNatural + 'px;' + 'box-shadow:0 12px 40px rgba(0,0,0,.55);' + 'border-top:4px solid #c62828;' + 'text-align:center;box-sizing:border-box;' + 'transform:scale(' + escala + ');' + 'transform-origin:center center;' + 'cursor:auto;'; caja.innerHTML = '&lt;h3 style="margin:0 0 12px 0;color:#c62828;font-size:17px;font-weight:bold;"&gt;Derechos de imagen&lt;/h3&gt;' + '&lt;p style="margin:0 0 16px 0;color:#333;font-size:13px;line-height:1.5;"&gt;' + '&lt;strong&gt;© ANDINA / Editora Perú&lt;/strong&gt;.&lt;br&gt;' + 'Reproducción permitida colocando el crédito de manera obligatoria.' + '&lt;/p&gt;' + '&lt;button id="andina-img-modal-ok" type="button" ' + 'style="background:#c62828;color:#fff;border:none;padding:10px 26px;' + 'border-radius:4px;font-size:13px;cursor:pointer;font-weight:bold;' + 'letter-spacing:.3px;"&gt;Acepta y continúa.&lt;/button&gt;'; // Evita que el clic dentro de la caja cierre el overlay caja.addEventListener('click', function (ev) { ev.stopPropagation(); }); overlay.appendChild(caja); document.body.appendChild(overlay); requestAnimationFrame(function () { overlay.style.opacity = '1'; }); var btn = document.getElementById('andina-img-modal-ok'); btn.focus(); // Si el usuario hace scroll, cerramos el modal (evita que pase bajo el header sticky) function onScrollClose() { cerrar(false); } window.addEventListener('scroll', onScrollClose, { passive: true, once: true }); function cerrar(aceptado) { window.removeEventListener('scroll', onScrollClose); overlay.style.opacity = '0'; setTimeout(function () { if (overlay.parentNode) overlay.parentNode.removeChild(overlay); if (aceptado &amp;&amp; callback) callback(); }, 200); } btn.addEventListener('click', function () { cerrar(true); }); overlay.addEventListener('click', function () { cerrar(false); }); document.addEventListener('keydown', function escListener(ev) { if (ev.key === 'Escape') { document.removeEventListener('keydown', escListener); cerrar(false); } }); } function esImagenDeContenido(img) { var src = (img.getAttribute('src') || '').toLowerCase(); // Patrón CMS Andina: nnnnnnW|M|T.ext (W=wide, M=medium, T=thumbnail) // Mostrar aviso solo en W y M; T es miniatura.
+var match = src.match(/(\d+)([wmt])\.(jpe?g|png|webp|gif)(\?|$)/i); if (match) { var sufijo = match[2].toLowerCase(); return (sufijo === 'w' || sufijo === 'm'); } // Para imágenes que NO siguen el patrón del CMS, aplicar filtros generales: // SVG = ícono/logo if (src.indexOf('.svg') !== -1) return false; var rect = img.getBoundingClientRect(); var anchoNatural = img.naturalWidth || rect.width; var altoNatural = img.naturalHeight || rect.height; if (rect.width &lt; 200 &amp;&amp; rect.height &lt; 200) return false; if (anchoNatural &lt; 250 &amp;&amp; altoNatural &lt; 250) return false; // Contenedores estructurales if (img.closest('header, footer, nav, .sidebar, .menu-sidebar, .floating-btn, ' + '.descargueapp, .convewidth, .logoeditora, .buscador, .cinta')) { return false; } // Clases de logo/ícono if (img.classList.contains('logo') || img.classList.contains('no-watermark')) return false; var cls = img.className || ''; if (/\b(width(\d+)|icon|btn-floating)\b/.test(cls) &amp;&amp; (anchoNatural &lt; 300)) return false; // Nombres de logos/íconos conocidos var skip = ['andina.svg', 'editora_logo', 'appstore', 'googleplay', 'menu.svg', 'search.svg', 'facebook', 'twitter', 'linkedin', 'youtube', 'instagram', 'soundcloud', 'spotify', 'tik-tok', 'more_vert', 'i_class-fecha', 'icono.ico', 'radio_nacional', 'tv_peru', 'ansa.svg', 'centro_de_informacion', 'editora_peru']; for (var i = 0; i &lt; skip.length; i++) { if (src.indexOf(skip[i]) !== -1) return false; } return true; } document.addEventListener('contextmenu', function (e) { var t = e.target; var img = (t &amp;&amp; t.tagName === 'IMG') ? t : (t &amp;&amp; t.closest ? t.closest('img') : null); if (!img) return; // Si el clic está dentro de nuestro menú personalizado, no hacer nada if (t.closest &amp;&amp; t.closest('#andina-img-menu')) return; // Solo bloquear el menú nativo en fotos de contenido if (!esImagenDeContenido(img)) return; e.preventDefault(); var posX = e.clientX, posY = e.clientY; mostrarModalImagen(img, function () { mostrarMenuPersonalizado(posX, posY, img); }); }); })(); /////////////// LLAMADA SCRIPTS/////////////// $('.button-collapse').sideNav({ menuWidth: 300, edge: 'right', closeOnClick: true, draggable: true, onOpen: function (el) { } } ); &lt;!-- Marquee pestaña --&gt; var scrl = " Agencia Andina "; function scrlsts() { scrl = scrl.substring(1, scrl.length) + scrl.substring(0, 1); document.title = scrl; setTimeout("scrlsts()", 280); } $(document).ready(function () { $('.parallax').parallax(); }); $(document).ready(function () { $('.slider').slider(); //Registro de Datalayer en Push }); $(".button-collapse").sideNav(); $(window).scroll(function () { if ($(this).scrollTop() &gt; 265) { $('nav').addClass("fixed").fadeIn(); $('#logomin').empty(); $('#logomin').prepend('&lt;a href="https://andina.pe"&gt;&lt;img src="img/logoandina2.png" loading="lazy" style="margin: 4px 8px; width:110px; margin-right:10px;" alt="#" &gt;&lt;/a&gt;'); } else { $('#logomin').empty(); $('nav').removeClass("fixed"); } }); //Funcion Registro Evento para GTAG Manager RL function registerEventTarget(nombreSeccion) { //Modificacion envio de evento para GTAG Manager Ricardo Lazarte const urlActual = window.location.href; let now = new Date(); window.dataLayer = window.dataLayer || []; window.dataLayer.push({ 'event': 'interaction', //Interaction 'eventAction': 'click', 'eventLabel': nombreSeccion, 'secction': 'Portada', 'eventCategory': 'Header', 'newurl': urlActual }); } //Funcion Registro Evento para GTAG Manager RL BANNERS function registerEventTargetBanner(nombreElemento) { //Modificacion envio de evento para GTAG Manager Ricardo Lazarte const urlActual = window.location.href; let now = new Date(); window.dataLayer = window.dataLayer || []; window.dataLayer.push({ 'event': 'interaction', 'eventAction': 'click', 'eventLabel': nombreElemento, 'secction': 'Portada', 'eventCategory': 'BANN LATERAL', 'newurl': urlActual }); // alert(nombreElemento); } const delay = 7000; //ms const slides = document.querySelector(".slides"); const slidesCount = slides.childElementCount; const maxLeft = (slidesCount - 1) * 100 * -1; let current = 0; function changeSlide(next = true) { if (next) { current += current &gt; maxLeft ? -100 : current * -1; } else { current = current &lt; 0 ? current + 100 : maxLeft; } slides.style.left = current + "%"; } let autoChange = setInterval(changeSlide, delay); const restart = function () { clearInterval(autoChange); autoChange = setInterval(changeSlide, delay); }; // Controls document.querySelector(".next-slide").addEventListener("click", function () { changeSlide(); restart(); }); document.querySelector(".prev-slide").addEventListener("click", function () { changeSlide(false); restart(); }); $(window).scroll(function () { if ($(this).scrollTop() &gt; 265) { $('nav').addClass("fixed").fadeIn(); $('#logomin').empty(); $('#logomin').prepend('&lt;a href="https://andina.pe"&gt;&lt;img src="img/logoandina2.png" style="margin: 4px 8px; width:110px; margin-right:10px;" alt="#" &gt;&lt;/a&gt;'); } else { $('#logomin').empty(); $('nav').removeClass("fixed"); } }); $(window).scroll(function () { if ($(window).width() &lt;= 992) { if ($(this).scrollTop() &gt; 100) { $('#sticky-header2').addClass("fixed").fadeIn(); } else { $('#sticky-header2').removeClass("fixed"); } } else { // Por si el usuario redimensiona la pantalla $('#sticky-header2').removeClass("fixed"); } }); //// Detecta el clic en la clase .floating-btn //document.querySelector('#headers .floating-btn').addEventListener('click', function () { // // Verifica si estamos en un dispositivo móvil (opcional, en base a la resolución) // if (window.innerWidth &lt;= 600) { // this.classList.toggle('hover-active'); // Alterna la clase que activa el hover // } //});</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-region-de-piura-noticia/</t>
+          <t>https://andina.pe/agencia/noticia-presidenta-fujimori-sostuvo-reuniones-trabajo-ministro-educacion-y-canciller-1096370.aspx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>El Comercio</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -1265,17 +1165,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Ayabaca (Piura)</t>
+          <t>Ministerio de Defensa presenta despliegue a gran escala del Ejército ante fenómeno El Niño</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Ayabaca, según el conteo oficial de la ONPE al 99.49% , arroja el siguiente resultado (actualizado el 17/10/2026, a las 10:46.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+          <t>???? ¡Preparados para llegar a donde más nos necesitan!?? Nuestro glorioso @EjercitoPeru demostró sus capacidades de rescate, evacuación y respuesta ante emergencias frente al fenómeno El Niño.¡#ElPerúResponde para proteger a la población!?? https://t.co/fHnSHXKo01 https://t.co/zKOQGWsjwJ — Mindef Perú (@MindefPeru) October 17, 2026 La actividad formó parte de la Reunión de Coordinación Multisectorial organizada por el Comando de Operaciones Terrestres junto a representantes del Sistema Nacional de Gestión del Riesgo de Desastres (Sinagerd).
+Durante la jornada, se realizaron maniobras operativas que incluyeron descensos con cuerdas desde helicópteros MI-17 para zonas de difícil acceso, el empleo de electrobombas y motobombas para drenar áreas anegadas , y el uso de caballos para el traslado en terrenos de difícil tránsito.
+Asimismo, vehículos lanza puentes diseñados para restablecer la circulación en vías interrumpidas.
+Lea también: Ministro de Defensa liderará acciones de emergencia en Piura y Tumbes ante El Niño Por su parte, las unidades especializadas USAR PER-13 y PER-14 ejecutaron ejercicios de rescate acuático , búsqueda bajo el agua, trabajos de corte, rompimiento y evacuación de víctimas.
+A la par, presentó su infraestructura logística para la gestión de desastres, la cual contempla puestos de comando móvil, puestos de atención de salud, bases para grupos de búsqueda y la instalación de albergues temporales con soporte tecnológico.
+Capacidad de respuesta ante emergencias En el plano operativo, el Ejército cuenta con 22 batallones de Ingeniería distribuidos en 15 regiones , equipados con 441 maquinarias pesadas y vehículos de ingeniería destinados a la remoción de escombros, limpieza de cauces y atención directa de emergencias.
+Este despliegue se enmarca en un proceso de preparación iniciado en julio de 2026 , que comprendió cuatro etapas de planeamiento, revisión de experiencias anteriores, simulaciones y coordinación interinstitucional.
+Más en Andina: Intervienen a más de 1,800 extranjeros en megaoperativo nacional https://t.co/KOT1jwbMHa https://t.co/ge3KjV77sN (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 17, 2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-ayabaca-piura-noticia/</t>
+          <t>https://andina.pe/agencia/noticia-ministerio-defensa-presenta-despliegue-a-gran-escala-del-ejercito-ante-fenomeno-nino-1096354.aspx</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1197,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Trabajadores del hospital de Sullana contra nuevos funcionarios</t>
+          <t>Keiko Fujimori anuncia que antes del 30 de noviembre culminarán limpieza del río Piura</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A 70 días de culminar la actual gestión regional, los trabajadores del Hospital de Especialidades de Sullana alzaron su voz de protesta contra las últimas designaciones de funcionarios dispuestas por el gobernador regional Luis Neyra, al cuestionar que algunos de los nuevos responsables no contarían con el perfil técnico ni la experiencia requerida para asumir sus cargos. Mediante un pronunciamiento conjunto, los gremios expresaron su rechazo a estos cambios, entre ellos el del nuevo administrador del establecimiento, y advirtieron que las designaciones realizadas a lo largo de 2026 vienen generando inestabilidad laboral y preocupación entre el personal del nosocomio. Los trabajadores señalaron que esta situación resulta especialmente preocupante debido a que el hospital se encuentra inmerso en el proceso de recategorización para alcanzar el nivel de complejidad III-1. A ello se suma el riesgo que afronta la región ante un eventual fenómeno de El Niño, escenario que exige una adecuada capacidad de respuesta del sistema sanitario. En el documento, los firmantes remarcaron que estas circunstancias demandan estabilidad institucional, continuidad operativa y decisiones responsables, sustentadas en criterios técnicos que permitan garantizar la adecuada prestación de los servicios de salud a la población. Por ello, solicitaron a las autoridades regionales que respeten la estabilidad de los equipos de gestión.</t>
+          <t>La presidenta de la República, Keiko Fujimori Higuchi, anunció que los trabajos de limpieza y descolmatación de los ríos y quebradas de Piura forman parte de las acciones que se ejecutan para reducir los riesgos ante un posible incremento del caudal por el fenómeno El Niño. Durante su visita a la región, la mandataria supervisó las intervenciones y destacó la necesidad de coordinar esfuerzos entre el Gobierno nacional, las autoridades regionales y locales, las Fuerzas Armadas y el sector privado. Keiko Fujimori señaló que antes del 30 de noviembre culminarán limpieza del río Piura. La jefa del Estado hizo un llamado a la unidad de las instituciones y de la ciudadanía para enfrentar los efectos de este evento climático. Según indicó, la magnitud de los fenómenos registrados en distintas partes del mundo obliga a trabajar de manera conjunta y adoptar medidas preventivas. Keiko Fujimori supervisa los trabajos de descolmatación del río Piura Durante su recorrido, Keiko Fujimori verificó las labores que ejecuta la Autoridad Nacional del Agua (ANA), entre ellas la limpieza del cauce, la descolmatación y la conformación de bordos. Estas intervenciones buscan retirar los sedimentos acumulados y mejorar las condiciones para el desplazamiento del agua durante periodos de lluvias intensas. En el sector Los Ejidos-Puente Bolognesi, los trabajos registraban un avance físico del 100% en una extensión de 4.85 kilómetros. Sin embargo, el avance medido por el volumen de material retirado alcanzaba el 85.30%, equivalente a 464,382 metros cúbicos de sedimentos. Estas cifras corresponden a indicadores distintos: mientras el avance físico reporta el cumplimiento de las actividades previstas en el tramo intervenido, el porcentaje de descolmatación refleja el volumen de material retirado respecto de la meta establecida. Por ello, ambos datos permiten evaluar diferentes aspectos de la ejecución de las obras. La información técnica también señala que los trabajos en Los Ejidos-Puente Bolognesi tenían como fecha prevista de culminación el 18 de octubre de 2026. La evolución de estas intervenciones resulta relevante para una región que históricamente ha enfrentado inundaciones y desbordes durante episodios de precipitaciones intensas. ¿Cuál es el avance de la limpieza del río Piura? Además del tramo de Los Ejidos-Puente Bolognesi, las autoridades supervisan otras intervenciones destinadas a mejorar las condiciones de los cauces en la región. De acuerdo con los datos proporcionados, los trabajos en El Milagro-La Encantada registraban un avance del 27.59%, mientras que en Piedra Negra alcanzaban el 20.73%. Estos porcentajes muestran que los trabajos presentan distintos niveles de ejecución y que todavía existen sectores donde las labores deben continuar. El seguimiento de los plazos y del avance físico será importante para conocer si las intervenciones se completan de acuerdo con el cronograma previsto. Durante la visita también se contempló la supervisión de las acciones que tiene a su cargo el Ministerio de Defensa en siete sectores de Piura. La participación de distintas entidades busca ampliar la capacidad de intervención frente a los riesgos asociados con las lluvias y las posibles crecidas de ríos y quebradas. Para consultar información institucional sobre la gestión del agua, los trabajos en cauces y las acciones de prevención, se puede revisar el portal oficial de la Autoridad Nacional del Agua (ANA) . Piura contempla 21 intervenciones ante el fenómeno El Niño En el marco del Decreto de Urgencia N.o 008-2026, se programaron 21 intervenciones en la región Piura, con una meta de 49.35 kilómetros de cauces de ríos y quebradas. Estas acciones están orientadas a mejorar las condiciones hidráulicas de los sectores intervenidos y contribuir a disminuir los riesgos ante posibles aumentos del caudal. La limpieza y descolmatación forman parte de las medidas preventivas porque permiten retirar material acumulado que puede dificultar el paso del agua. No obstante, la ejecución de estas labores no elimina por sí sola el riesgo de inundaciones, ya que sus efectos también dependen de la intensidad de las lluvias, las condiciones de los cauces y la capacidad de las obras de protección. Por esa razón, la preparación ante el fenómeno El Niño requiere tanto la intervención de las autoridades como la planificación de las comunidades expuestas. La identificación de zonas vulnerables, la vigilancia de los caudales y la difusión de información oficial son elementos relevantes para reducir la exposición de la población. La ciudadanía puede consultar las disposiciones y comunicados relacionados con la prevención de emergencias en el portal del Instituto Nacional de Defensa Civil (Indeci) , así como las alertas y reportes de las entidades competentes. Keiko Fujimori pide unidad para enfrentar las lluvias y las inundaciones Durante la supervisión, la presidenta insistió en la importancia de coordinar acciones entre las instituciones públicas y el sector privado. “La única manera en la que vamos a poder salir adelante y enfrentar este fenómeno climático, que como vemos en imágenes de otros países y en otras partes del mundo es de dimensiones muy grandes, la única manera es trabajando unidos”, sostuvo la mandataria. El llamado se produce en un contexto en el que las autoridades deben avanzar con las intervenciones preventivas y mantener informada a la población sobre el estado de las obras. Para los habitantes de Piura, el cumplimiento de los plazos y la atención de los sectores con menor avance son aspectos importantes de cara a la temporada de lluvias. La coordinación entre los gobiernos nacional, regional y local también resulta necesaria para organizar la respuesta ante eventuales emergencias. A ello se suma la participación de las Fuerzas Armadas y de las instituciones responsables de ejecutar y supervisar las obras. Los avances reportados permiten conocer el estado de algunos tramos, pero la evaluación del resultado de las intervenciones dependerá de su culminación, del cumplimiento de las metas técnicas y de las condiciones que se presenten durante el periodo de lluvias. Agenda de Keiko Fujimori incluye obras de prevención en La Libertad Como parte de su agenda de supervisión, Keiko Fujimori también tenía previsto realizar un sobrevuelo en la región La Libertad para verificar los avances de la solución integral de las quebradas San Ildefonso y San Carlos. El proyecto está a cargo de la Autoridad Nacional de Infraestructura (ANIN) y busca reducir los riesgos asociados con las avenidas de agua que pueden afectar a las zonas urbanas y productivas. Según la información técnica proporcionada, las obras registraban avances físicos del 78.82% en San Ildefonso y del 69.52% en San Carlos, con una inversión total de S/ 1,664 millones. El proyecto contempla la construcción de diques, un túnel de 1.5 kilómetros para derivar las aguas de la quebrada San Ildefonso hacia San Carlos, canales de conducción que suman 12.85 kilómetros y defensas ribereñas a lo largo de 17.2 kilómetros del río Moche. La intervención está proyectada para beneficiar a más de 750,000 habitantes de siete distritos de La Libertad. También comprende la protección de alrededor de 9,000 unidades productivas públicas y privadas, entre ellas instituciones educativas, establecimientos de salud, carreteras, canales, terrenos agrícolas y viviendas. La información sobre los proyectos de infraestructura preventiva puede contrastarse con los comunicados de la Autoridad Nacional de Infraestructura y las publicaciones oficiales del Gobierno del Perú . ¿Por qué son importantes los trabajos de descolmatación en Piura? Los trabajos de descolmatación buscan retirar sedimentos y otros materiales acumulados en los cauces para facilitar el paso del agua. En una región expuesta a lluvias intensas, estas labores pueden contribuir a reducir determinados riesgos, siempre que se ejecuten de acuerdo con las condiciones técnicas de cada sector. El resultado depende también del mantenimiento de los cauces, la situación de las quebradas, las defensas ribereñas y la magnitud de las precipitaciones. Por ello, las obras deben complementarse con medidas de prevención, monitoreo y preparación de la población. En Piura, el seguimiento de las 21 intervenciones programadas permitirá conocer el avance de las metas establecidas y el cumplimiento de los trabajos en los diferentes sectores. La información oficial sobre los plazos, las cantidades de material retirado y los kilómetros intervenidos será fundamental para evaluar el desarrollo de estas acciones preventivas.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/trabajadores-del-hospital-de-sullana-contra-nuevos-funcionarios/</t>
+          <t>https://eltiempo.pe/local/keiko-fujimori-anuncia-que-antes-del-30-de-noviembre-culminaran-limpieza-del-rio-piura/</t>
         </is>
       </c>
     </row>
@@ -1349,24 +1256,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Keiko Fujimori anuncia que antes del 30 de noviembre culminarán limpieza del río Piura</t>
+          <t>Almacenes adelantados deben contar con todos los protocolos para conservar bienes de ayuda humanitaria</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>La presidenta de la República, Keiko Fujimori Higuchi, anunció que los trabajos de limpieza y descolmatación de los ríos y quebradas de Piura forman parte de las acciones que se ejecutan para reducir los riesgos ante un posible incremento del caudal por el fenómeno El Niño. Durante su visita a la región, la mandataria supervisó las intervenciones y destacó la necesidad de coordinar esfuerzos entre el Gobierno nacional, las autoridades regionales y locales, las Fuerzas Armadas y el sector privado. Keiko Fujimori señaló que antes del 30 de noviembre culminarán limpieza del río Piura. La jefa del Estado hizo un llamado a la unidad de las instituciones y de la ciudadanía para enfrentar los efectos de este evento climático. Según indicó, la magnitud de los fenómenos registrados en distintas partes del mundo obliga a trabajar de manera conjunta y adoptar medidas preventivas. Keiko Fujimori supervisa los trabajos de descolmatación del río Piura Durante su recorrido, Keiko Fujimori verificó las labores que ejecuta la Autoridad Nacional del Agua (ANA), entre ellas la limpieza del cauce, la descolmatación y la conformación de bordos. Estas intervenciones buscan retirar los sedimentos acumulados y mejorar las condiciones para el desplazamiento del agua durante periodos de lluvias intensas. En el sector Los Ejidos-Puente Bolognesi, los trabajos registraban un avance físico del 100% en una extensión de 4.85 kilómetros. Sin embargo, el avance medido por el volumen de material retirado alcanzaba el 85.30%, equivalente a 464,382 metros cúbicos de sedimentos. Estas cifras corresponden a indicadores distintos: mientras el avance físico reporta el cumplimiento de las actividades previstas en el tramo intervenido, el porcentaje de descolmatación refleja el volumen de material retirado respecto de la meta establecida. Por ello, ambos datos permiten evaluar diferentes aspectos de la ejecución de las obras. La información técnica también señala que los trabajos en Los Ejidos-Puente Bolognesi tenían como fecha prevista de culminación el 18 de octubre de 2026. La evolución de estas intervenciones resulta relevante para una región que históricamente ha enfrentado inundaciones y desbordes durante episodios de precipitaciones intensas. ¿Cuál es el avance de la limpieza del río Piura? Además del tramo de Los Ejidos-Puente Bolognesi, las autoridades supervisan otras intervenciones destinadas a mejorar las condiciones de los cauces en la región. De acuerdo con los datos proporcionados, los trabajos en El Milagro-La Encantada registraban un avance del 27.59%, mientras que en Piedra Negra alcanzaban el 20.73%. Estos porcentajes muestran que los trabajos presentan distintos niveles de ejecución y que todavía existen sectores donde las labores deben continuar. El seguimiento de los plazos y del avance físico será importante para conocer si las intervenciones se completan de acuerdo con el cronograma previsto. Durante la visita también se contempló la supervisión de las acciones que tiene a su cargo el Ministerio de Defensa en siete sectores de Piura. La participación de distintas entidades busca ampliar la capacidad de intervención frente a los riesgos asociados con las lluvias y las posibles crecidas de ríos y quebradas. Para consultar información institucional sobre la gestión del agua, los trabajos en cauces y las acciones de prevención, se puede revisar el portal oficial de la Autoridad Nacional del Agua (ANA) . Piura contempla 21 intervenciones ante el fenómeno El Niño En el marco del Decreto de Urgencia N.o 008-2026, se programaron 21 intervenciones en la región Piura, con una meta de 49.35 kilómetros de cauces de ríos y quebradas. Estas acciones están orientadas a mejorar las condiciones hidráulicas de los sectores intervenidos y contribuir a disminuir los riesgos ante posibles aumentos del caudal. La limpieza y descolmatación forman parte de las medidas preventivas porque permiten retirar material acumulado que puede dificultar el paso del agua. No obstante, la ejecución de estas labores no elimina por sí sola el riesgo de inundaciones, ya que sus efectos también dependen de la intensidad de las lluvias, las condiciones de los cauces y la capacidad de las obras de protección. Por esa razón, la preparación ante el fenómeno El Niño requiere tanto la intervención de las autoridades como la planificación de las comunidades expuestas. La identificación de zonas vulnerables, la vigilancia de los caudales y la difusión de información oficial son elementos relevantes para reducir la exposición de la población. La ciudadanía puede consultar las disposiciones y comunicados relacionados con la prevención de emergencias en el portal del Instituto Nacional de Defensa Civil (Indeci) , así como las alertas y reportes de las entidades competentes. Keiko Fujimori pide unidad para enfrentar las lluvias y las inundaciones Durante la supervisión, la presidenta insistió en la importancia de coordinar acciones entre las instituciones públicas y el sector privado. “La única manera en la que vamos a poder salir adelante y enfrentar este fenómeno climático, que como vemos en imágenes de otros países y en otras partes del mundo es de dimensiones muy grandes, la única manera es trabajando unidos”, sostuvo la mandataria. El llamado se produce en un contexto en el que las autoridades deben avanzar con las intervenciones preventivas y mantener informada a la población sobre el estado de las obras. Para los habitantes de Piura, el cumplimiento de los plazos y la atención de los sectores con menor avance son aspectos importantes de cara a la temporada de lluvias. La coordinación entre los gobiernos nacional, regional y local también resulta necesaria para organizar la respuesta ante eventuales emergencias. A ello se suma la participación de las Fuerzas Armadas y de las instituciones responsables de ejecutar y supervisar las obras. Los avances reportados permiten conocer el estado de algunos tramos, pero la evaluación del resultado de las intervenciones dependerá de su culminación, del cumplimiento de las metas técnicas y de las condiciones que se presenten durante el periodo de lluvias. Agenda de Keiko Fujimori incluye obras de prevención en La Libertad Como parte de su agenda de supervisión, Keiko Fujimori también tenía previsto realizar un sobrevuelo en la región La Libertad para verificar los avances de la solución integral de las quebradas San Ildefonso y San Carlos. El proyecto está a cargo de la Autoridad Nacional de Infraestructura (ANIN) y busca reducir los riesgos asociados con las avenidas de agua que pueden afectar a las zonas urbanas y productivas. Según la información técnica proporcionada, las obras registraban avances físicos del 78.82% en San Ildefonso y del 69.52% en San Carlos, con una inversión total de S/ 1,664 millones. El proyecto contempla la construcción de diques, un túnel de 1.5 kilómetros para derivar las aguas de la quebrada San Ildefonso hacia San Carlos, canales de conducción que suman 12.85 kilómetros y defensas ribereñas a lo largo de 17.2 kilómetros del río Moche. La intervención está proyectada para beneficiar a más de 750,000 habitantes de siete distritos de La Libertad. También comprende la protección de alrededor de 9,000 unidades productivas públicas y privadas, entre ellas instituciones educativas, establecimientos de salud, carreteras, canales, terrenos agrícolas y viviendas. La información sobre los proyectos de infraestructura preventiva puede contrastarse con los comunicados de la Autoridad Nacional de Infraestructura y las publicaciones oficiales del Gobierno del Perú . ¿Por qué son importantes los trabajos de descolmatación en Piura? Los trabajos de descolmatación buscan retirar sedimentos y otros materiales acumulados en los cauces para facilitar el paso del agua. En una región expuesta a lluvias intensas, estas labores pueden contribuir a reducir determinados riesgos, siempre que se ejecuten de acuerdo con las condiciones técnicas de cada sector. El resultado depende también del mantenimiento de los cauces, la situación de las quebradas, las defensas ribereñas y la magnitud de las precipitaciones. Por ello, las obras deben complementarse con medidas de prevención, monitoreo y preparación de la población. En Piura, el seguimiento de las 21 intervenciones programadas permitirá conocer el avance de las metas establecidas y el cumplimiento de los trabajos en los diferentes sectores. La información oficial sobre los plazos, las cantidades de material retirado y los kilómetros intervenidos será fundamental para evaluar el desarrollo de estas acciones preventivas.</t>
+          <t>El Gobierno Regional realiza coordinaciones con los 17 municipios, con los que tiene convenios para el funcionamiento de los almacenes adelantados, a efectos que mejoren las condiciones de la infraestructura, ambiente y seguridad de los mismos. Todo esto, debido a que dichos locales deben garantizar las condiciones de la reserva hasta su uso, que consiste en 113.29 toneladas de bienes de ayuda humanitaria que les ha entregado el GORE. Fuentes de la Oficina Regional de Seguridad y Defensa Nacional, señalaron que en una reciente jornada de supervisión de estos depósitos, se detectaron varias deficiencias, por lo que se notificó documentadamente a los gobiernos locales apara que levanten las observaciones, en cuyo proceso, los municipios, se encuentran abocados según han reportado a la Orsydn. Los almacenes adelantados garantizarán una rápida respuesta ante una emergencia.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/keiko-fujimori-anuncia-que-antes-del-30-de-noviembre-culminaran-limpieza-del-rio-piura/</t>
+          <t>https://eltiempo.pe/local/almacenes-adelantados-deben-contar-con-todos-los-protocolos-para-conservar-bienes-de-ayuda-humanitaria/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -1374,67 +1281,67 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alcalde electo de VDO, Percy Fiestas, denuncia extorsión en Piura y amenazas contra su familia</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Sullana (Piura)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>El virtual alcalde del distrito de Veintiséis de Octubre, Percy Fiestas Aquino , denunció haber recibido amenazas de muerte y mensajes extorsivos dirigidos contra él y sus familiares, días después de ser elegido como nueva autoridad municipal. Según su testimonio, los presuntos responsables le exigen dinero y buscan obligarlo a entablar una negociación bajo el argumento de brindarle seguridad. El caso ha generado preocupación en Piura , especialmente por los antecedentes de violencia contra autoridades municipales en el distrito. Las comunicaciones recibidas por Fiestas incluirían llamadas telefónicas, mensajes intimidatorios y un video en el que un sujeto exhibe un arma de fuego y exige una respuesta en un plazo de 24 horas. De acuerdo con lo informado por el virtual alcalde, los remitentes se identifican como presuntos integrantes de la organización criminal Nueva Generación del Norte. Sin embargo, la identidad de los autores y su posible vinculación con alguna banda delictiva deberán ser determinadas por las autoridades encargadas de la investigación. Percy Fiestas denuncia extorsión en Piura y amenazas contra su familia Las primeras comunicaciones llegaron el 15 de octubre, alrededor de las 10 de la mañana, según relató Fiestas. Los mensajes estuvieron acompañados de llamadas telefónicas y material audiovisual en el que un hombre, que asegura pertenecer a la mencionada organización, intenta presionarlo para que acepte una negociación. “Nos exigen pagos de dinero y, además, que entremos en comunicación con ellos para que, entre comillas, nos brinden seguridad. Envían amenazas y videos donde muestran armas de fuego y también amenazan a mi familia”, declaró el virtual alcalde. Según las capturas de pantalla difundidas, los presuntos extorsionadores afirman conocer la dirección de su vivienda, los nombres de sus familiares y sus movimientos. En uno de los mensajes, el remitente establece un plazo de 24 horas para recibir una respuesta y advierte que acudirá al domicilio si no obtiene contestación. El video enviado a Fiestas contiene nuevas advertencias. En la grabación, un sujeto le pide que dialogue y acepte negociar, al mismo tiempo que menciona a su esposa y a su hija. El contenido busca generar presión mediante referencias directas a sus seres queridos. “Mire doctor Percy, es mejor que dialogues con nosotros, entrar en una negociación y llevar la fiesta en paz, ya nosotros sabemos todos tus movimientos. Espero una respuesta tuya lo más antes posible, dentro de las 24 horas. Si ignoras, después no te quejes”, se escucha en el material difundido. Policía Nacional investiga las amenazas contra el virtual alcalde Percy Fiestas informó que presentó la denuncia correspondiente y entregó a la Policía Nacional del Perú (PNP) el teléfono celular en el que recibió los mensajes y las llamadas. El caso quedó a cargo de la División de Investigación Criminal (Divincri), que deberá realizar las diligencias para establecer el origen de las comunicaciones e identificar a los responsables. El virtual alcalde señaló que no tenía identificado a ningún sospechoso y que, hasta el momento de sus declaraciones, no había recibido nuevas amenazas durante ese día. No obstante, explicó que las llamadas y los mensajes se prolongaron durante varias horas, y que una de las comunicaciones fue contestada por su esposa. “Las amenazas mencionan la dirección exacta de mi casa y los nombres de los miembros de mi familia. Como entenderán, esto nos genera temor, por eso hacemos un llamado a las autoridades para que se investigue el caso y se pueda sancionar a los responsables”, manifestó. Tras conocerse la denuncia, se dispusieron patrullajes en los alrededores de su vivienda. Además, se cursaron oficios a las comisarías de San Martín y Veintiséis de Octubre para solicitar acciones de seguridad, según la información proporcionada sobre el caso. Fiestas también indicó que tuvo que asumir el costo de su seguridad personal ante el temor generado por las amenazas. Su principal preocupación, sostuvo, es la integridad de sus familiares, quienes también habrían sido mencionados en las comunicaciones intimidatorias. Otro aspecto que le preocupa es la falta de cámaras de vigilancia en su vivienda y en los alrededores. Según explicó, el sector no cuenta con equipos de videovigilancia que permitan registrar posibles movimientos sospechosos y que podrían contribuir a las investigaciones. ¿Por qué las amenazas contra Percy Fiestas generan preocupación en Veintiséis de Octubre? La denuncia adquiere especial relevancia por el antecedente de violencia que afectó a la municipalidad del distrito. El 21 de mayo de 2026, el entonces alcalde de Veintiséis de Octubre, Víctor Hugo Febre , fue asesinado en un ataque armado atribuido a sicarios. Según Percy Fiestas, los remitentes de los mensajes hicieron referencia a ese crimen para incrementar el temor y presionarlo a responder a sus exigencias. La mención del asesinato de su antecesor habría intensificado la preocupación de su entorno familiar, debido a que el hecho ocurrió en la misma jurisdicción donde ejercerá funciones municipales. “Si estamos en un distrito en el cual un alcalde murió a manos de sicarios, entenderán que estamos pasando una situación familiar bastante preocupante. Los delincuentes hacen referencia a ese hecho como una herramienta para infundirnos mayor temor”, señaló. El antecedente pone nuevamente en discusión las condiciones de seguridad para las autoridades locales en Piura, donde las amenazas extorsivas representan un desafío para las familias afectadas y para las instituciones responsables de prevenir e investigar los delitos. En este caso, corresponde a la Policía y al Ministerio Público determinar si las comunicaciones proceden de una organización criminal, establecer la posible relación entre los mensajes y otros hechos delictivos y reunir las pruebas necesarias para identificar a los responsables. Hasta que concluyan las diligencias, las afirmaciones sobre la autoría de las amenazas deben considerarse parte de la denuncia y no hechos judicialmente acreditados. Percy Fiestas pide reforzar la seguridad frente a la extorsión en Piura Ante esta situación, el virtual alcalde pidió a las autoridades profundizar las investigaciones y sancionar a quienes resulten responsables. También hizo un llamado al Gobierno central para fortalecer la lucha contra la extorsión y mejorar la coordinación entre las instituciones nacionales y los gobiernos locales. Fiestas advirtió que las amenazas no solo afectan a quienes ocupan cargos públicos, sino también a sus familiares, especialmente cuando los mensajes incluyen información sobre sus domicilios y actividades cotidianas. Por ello, insistió en la necesidad de adoptar medidas que permitan proteger a las personas afectadas y evitar que las intimidaciones escalen a hechos de violencia. La denuncia se produce cuando el distrito de Veintiséis de Octubre se prepara para una nueva gestión municipal. Mientras avanzan las diligencias policiales, la identificación de los remitentes, la verificación del material audiovisual y el análisis de las llamadas serán elementos importantes para esclarecer lo ocurrido. ¿Dónde denunciar casos de extorsión en Piura? Las personas que reciban amenazas, mensajes extorsivos o llamadas en las que se les exija dinero pueden acudir a una dependencia policial para presentar una denuncia. Es importante conservar las conversaciones, los números telefónicos, las capturas de pantalla, los audios y los videos recibidos, evitando eliminar los archivos que podrían servir como evidencia. También se recomienda no negociar ni realizar pagos por presión sin comunicar previamente el caso a las autoridades. Si existen amenazas inmediatas contra la vida o la integridad de una persona, se debe solicitar ayuda policial de manera urgente y evitar exponerse a encuentros con los presuntos responsables. Para obtener orientación y conocer los canales oficiales de atención, se puede consultar el portal de la Ministerio del Interior y la página institucional de la Policía Nacional del Perú . Asimismo, el Ministerio Público ofrece información institucional sobre sus funciones y los servicios vinculados a la recepción e investigación de denuncias.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Sullana, según el conteo oficial de la ONPE al 98.088% , arroja el siguiente resultado (actualizado el 17/10/2026, a las 18:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/alcalde-electo-de-vdo-percy-fiestas-denuncia-extorsion-en-piura-y-amenazas-contra-su-familia/</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-sullana-piura-noticia/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dos alumnas ante la Fiscalía por caso de presunto abuso sexual en Talara</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Talara (Piura)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Dos escolares desfilarán ante la Fiscalía de la Familia de Talara con relación a las investigaciones en curso por abuso sexual en manada contra una alumna. Ambas han sido citadas para que rindan su declaración a fin de esclarecer lo ocurrido en el salón de clases. Se conoció que las dos estudiantes habrían engañada a su compañera de aula para que ingresara, para luego sujetarla de las manos y permitir que los seis a ocho alumnos entren para supuestamente abusar sexualmente de ella, en horario de recreo. ESTRICTO CONTROL El director de la I. E. Santa Rosa de Lima, Víctor Atarama, indicó que mientras las investigaciones avanzan en estricta reserva, en la escuela del nivel inicial, primario y secundario, se han implementado nuevas medidas de control en los pabellones de cada grado, con la estricta participación de todos los docentes. También señaló que, el protocolo no les impide conversar con los estudiantes para evitar la revictimización, y que solo le corresponde a la fiscalía realizar esa acción. Sin embargo, refirió que el mismo exige contactar a los padres para informar los hechos ocurridos para que asuman sus respectivos compromisos. UGEL PDE CELERIDAD Por otro lado. la UGEL Talara pide a las autoridades que aceleren las investigaciones a fin de determinar si hubo un real abuso sexual, o fue un hostigamiento o tocamientos indebidos contra la alumna. El consejero regional por Talara, Carlos Castillo Ipanaqué, informó que solicitará la intervención de las comisiones de Educación o la de Mujer y Poblaciones Vulnerables del Congreso de la República, para que el caso no quede impune.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Talara, según el conteo oficial de la ONPE al 98.177% , arroja el siguiente resultado (actualizado el 17/10/2026, a las 18:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/dos-alumnas-ante-la-fiscalia-por-caso-de-presunto-abuso-sexual-en-talara/</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-talara-piura-noticia/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Somos Perú pide recontar los votos en Piura: se acorta distancia entre La Torre y Paz</t>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Ayabaca (Piura)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Durante la audiencia pública virtual convocada por el Jurado Nacional de Elecciones (JNE) para evaluar el caso de la nulidad de las elecciones en San Juan de Bigote, la defensa legal de Somos Perú, Ubaldo Pizarro, se mantuvo firme sobre el pedido del recuento de votos que se encuentran en poder de la Fiscalía de Morropón. Sin embargo, el abogado Juan Carlos Álamo fue tajante en señalar que el acta fiscal solo da cuenta de la recuperación de una parte del material electoral y no del todo el proceso, por lo que ratificó su posición de la nulidad de las elecciones. Ahora será el JNE la entidad que deberá tomar la decisión del caso. En tanto, sigue la disputa por el segundo lugar: al 97.662% del reporte de la ONPE, el candidato Guillermo La Torre (Podemos) seguía en segundo lugar con 175,657 votos, mientras que Santiago Paz (Somos Perú) tenía 174,122 votos. La diferencia entre ambos es de 1535 votos.</t>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Ayabaca, según el conteo oficial de la ONPE al 99.49% , arroja el siguiente resultado (actualizado el 17/10/2026, a las 10:46.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/somos-peru-pide-recontar-los-votos-en-piura-se-acorta-distancia-entre-la-torre-y-paz/</t>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-ayabaca-piura-noticia/</t>
         </is>
       </c>
     </row>
@@ -1445,64 +1352,419 @@
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Neyra, en manos del JNE: abogado espera fallo y denuncia al gobernador y consejeros</t>
+          <t>Anuncian corte de servicio eléctrico por trabajos de reforzamiento de redes en VDO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>El abogado Juan Mejía Seminario informó que una persona suplantó la identidad de una funcionaria del Jurado Nacional de Elecciones (JNE) para comunicarle que dicha entidad había fallado a favor de su solicitud de suspender al gobernador regional Luis Neyra. De acuerdo con el letrado, su pedido se sustentaba en la presunta omisión de funciones de Neyra León respecto a las medidas de prevención frente a El Niño. Sin embargo, indicó a LA HORA que todo se habría tratado de una “suplantación de identidad” y de una “trampa política”. En tanto, la Procuraduría del JNE ha iniciado las diligencias respectivas; Mejía deberá acreditar su habilitación como abogado y el pago de un arancel, por lo que espera que la próxima semana se lleve a cabo la audiencia y, en un plazo de 48 horas posteriores a la audiencia, se emita el fallo correspondiente. “En 10 días ya se conocerá el desenlace”, indicó, al mismo tiempo que informó que ya realizó la denuncia penal contra el gobernador por omisión de deberes funcionales. Dijo que la denuncia alcanza a los consejeros.</t>
+          <t>Como parte de las acciones preventivas ante la llegada del FEN, Enosa realizará trabajos de reforzamiento de redes de media tensión en Veintiséis de Octubre, a fin de fortalecer la infraestructura eléctrica frente a las posibles condiciones que genere el periodo de lluvias. La intervención se realizará mañana domingo, de 7 a. m. a 3 p. m. Durante ese horario, el corte del servicio comprenderá las urbanizaciones Villas del Sol, Las Casuarinas IV y V Etapa, Las Colinas del Chipe I Etapa, manzanas B a F, Los Parques del Chipe II Etapa, Las Praderas del Chipe, Alameda del Chipe y Las Lomas del Chipe. Asimismo, los residenciales Condominio Club Parques del Chipe I y II Etapa, Alameda del Chipe y Condominio Parques del Chipe.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/neyra-en-manos-del-jne-abogado-espera-fallo-y-denuncia-al-gobernador-y-consejeros/</t>
+          <t>https://eltiempo.pe/local/anuncian-corte-de-servicio-electrico-por-trabajos-de-reforzamiento-de-redes-en-vdo/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Piura: Decomisan mercadería en operativo contra comercio ambulatorio en jr. Moretta</t>
+          <t>Temblor hoy en Perú: sismo de magnitud 4.1 en Piura eleva a 739 los reportados este año</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tras el retiro de motocicletas en el Jr. Gonzalo Farfán del Complejo de Mercados, ayer personal de la subgerencia de Fiscalización ejecutó un operativo en el Jr, Moretta con el decomiso de mercadería a los informales tras desacatar las notificaciones que los conminaba a no invadir los espacios públicos. El subgerente de Fiscalización, Danilo Gallo, explicó que los comerciantes habían sido notificados; no obstante, permanecieron en el lugar con estructuras de palos, toldos, guayaquiles y otros enseres en plena vía pública. “Desacataron la notificación. En base a ello, hemos procedido con el retiro y decomiso de dichos materiales de la vía pública”, dijo el funcionario, quien agregó que seguirán recuperando espacios públicos con apoyo policial.</t>
+          <t>El movimiento telúrico ocurrió a la 05:53 horas, y su epicentro fue localizado a 104 kilómetros al este del distrito de Ayabaca, provincia del mismo nombre.
+Las autoridades regionales y locales de Defensa Civil no han reportado hasta el momento daños personales o materiales a consecuencia de este sismo.
+Con este temblor, el Perú acumula 739 sismos reportados en el país por el Centro Sismológico Nacional en lo que va del año.
+Perú registra permanente actividad sísmica El territorio peruano presenta una elevada actividad sísmica debido principalmente al proceso de subducción de la placa de Nazca bajo la placa Sudamericana.
+Ante la ocurrencia de un sismo, el Instituto Nacional de Defensa Civil (Indeci) recomienda mantener la calma, ubicarse en una zona segura previamente identificada y alejarse de ventanas, objetos que puedan caer y estructuras que representen peligro.
+También aconseja contar con una mochila para emergencias y una caja de reserva con artículos básicos para afrontar las primeras horas posteriores a una emergencia.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-decomisan-mercaderia-en-operativo-contra-comercio-ambulatorio-en-jr-moretta/</t>
+          <t>https://andina.pe/agencia/noticia-temblor-hoy-peru-sismo-magnitud-41-piura-eleva-a-739-los-reportados-este-ano-1096310.aspx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>46312</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>JNE declara fundado pedido de nulidad de elecciones en San Juan de Bigote</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>El Jurado Nacional de Elecciones (JNE) declaró fundado el pedido relacionado con las elecciones en el distrito de San Juan de Bigote , ubicado en la provincia de Morropón, región Piura. La decisión fue celebrada por el candidato Santiago Paz, quien destacó que el resultado representa un avance en la defensa de la voluntad popular. A través de sus redes sociales, el candidato de Somos Perú, Santiago Paz, manifestó que el pronunciamiento responde a las protestas y acciones emprendidas por ciudadanos que exigían que se respete el resultado de los comicios. ¿Qué decidió el JNE sobre las elecciones en San Juan de Bigote? La publicación del Jurado Nacional de Elecciones indica que el pedido fue declarado fundado. Este pronunciamiento está relacionado con la controversia surgida por la anulación de los comicios regionales y municipales en San Juan de Bigote , una localidad de la provincia de Morropón que se convirtió en escenario de reclamos ciudadanos. De acuerdo con la información difundida, el caso llegó a esta instancia electoral después de que se cuestionara la resolución que había dispuesto anular las elecciones en el distrito. Frente a esa situación, se presentó una apelación para que el organismo electoral revisara la decisión. Para conocer la información institucional, los ciudadanos pueden consultar el portal del Jurado Nacional de Elecciones , donde se publican documentos y pronunciamientos vinculados con sus competencias. Santiago Paz celebra la decisión del organismo electoral Tras conocerse el pronunciamiento, el candidato Santiago Paz expresó su satisfacción y sostuvo que la decisión representa una victoria para los ciudadanos de Piura, más allá de las diferencias partidarias. “Este es el resultado de la lucha de todos los piuranos. San Juan de Bigote podrá ver el resultado de sus elecciones. Hemos logrado que la voluntad popular se respete. Que oigan nuestra voz”, manifestó en su publicación. El representante de Somos Perú también remarcó que, desde su perspectiva, el resultado no debe atribuirse exclusivamente a una organización política o a una candidatura, sino al reclamo de quienes participaron en las movilizaciones. “Este logro no es por Somos Perú, ni por Santiago Paz, este logro es por la democracia de nuestra región y de nuestro país”, señaló. Sus declaraciones reflejan la posición del candidato frente a la controversia electoral. Sin embargo, el alcance jurídico de la decisión deberá determinarse a partir de los fundamentos y disposiciones que figuren en el documento oficial del JNE. Las protestas ciudadanas por el proceso electoral en Piura La controversia en San Juan de Bigote generó expresiones de rechazo entre ciudadanos que exigían una respuesta de las autoridades electorales. Según lo expresado por Santiago Paz, las movilizaciones fueron parte de una protesta que buscaba defender la voluntad de los electores y cuestionar la anulación de los comicios. El candidato afirmó que las manifestaciones trascendieron los intereses de una agrupación política y que tuvieron como principal objetivo exigir que las instituciones del Estado atendieran el reclamo de la población. “Independientemente del partido político, esta es una voz de protesta que fue escuchada”, expresó en redes sociales. Asimismo, sostuvo que los ciudadanos estaban cansados de determinadas prácticas políticas y consideró que las movilizaciones debían quedar registradas como una muestra de participación democrática en la región. “Que estas marchas marquen una historia, que cuenten que el día que se quiso torcer la voluntad, hubo piuranos y piuranas que salimos, caminamos, protestamos y luchamos en las calles por el respeto a la democracia de nuestra región”, indicó. Estas afirmaciones corresponden a la valoración política de Santiago Paz sobre el conflicto. Para determinar las razones que motivaron la anulación inicial y los argumentos aceptados por el organismo electoral, será necesario revisar los documentos oficiales del expediente. ¿Qué pasará ahora con las elecciones en San Juan de Bigote? El siguiente paso dependerá de lo establecido en la resolución del Jurado Nacional de Elecciones. El documento permitirá conocer qué efectos tendrá la decisión sobre el proceso electoral y qué acciones deberán ejecutar las autoridades competentes. En particular, será importante determinar si corresponde restablecer los resultados electorales, realizar alguna actuación complementaria o cumplir con otras disposiciones. Por ahora, no es posible confirmar cuál de esos escenarios corresponde al caso sin contar con el contenido íntegro del fallo. Los ciudadanos pueden seguir las actualizaciones mediante el portal oficial del JNE y las publicaciones institucionales relacionadas con el proceso. También pueden consultar la información de la Oficina Nacional de Procesos Electorales (ONPE) , entidad encargada de organizar y ejecutar los procesos electorales dentro de sus competencias.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/jne-declara-fundado-pedido-de-nulidad-de-elecciones-en-san-juan-de-bigote/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cierre del año escolar será el 27 de noviembre en la región Piura</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>El año escolar 2026 culminará en Piura el próximo 27 de noviembre, según el acuerdo tomado por las 12 Unidades de Gestión Educativa Local (UGEL) de Piura que acordaron adelantar la culminación de las clases sin afectar el calendario académico, debido al anuncio de lluvias de fuerte intensidad para los próximos meses y la vulnerabilidad de las escuelas. Con el acuerdo tomado, el año escolar dejará de culminar el 18 de diciembre, como lo establecía la programación inicial. II. EE., ‘EN JAQUE’ Por su parte, la secretaria general del Sutep Regional Piura, Juana Rosa Ordinola, informó que más de 250 instituciones educativas requieren mantenimiento inmediato. Espera que próximamente empiece a proveerse de calaminones, calaminas y otros materiales necesarios a los colegios que requieren mantenimiento urgente. “Hay instituciones educativas que no tienen ni cerco perimétrico, están trabajando en un estado calamitoso. Hay colegios sin auxiliares, sin personal de servicio. El Gobierno tiene que dar mayor presupuesto, por eso una comisión va a viajar a Lima y exigir mayor presupuesto al MEF”, señaló la vocera del magisterio, quien espera celeridad tras el anuncio de las lluvias en la región.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/cierre-del-ano-escolar-sera-el-27-de-noviembre-en-la-region-piura/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Keiko Fujimori pide unidad ante fenómeno El Niño: “Esperemos que este mensaje llegue también al Congreso de la República”</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>La presidenta de la República, Keiko Fujimori, hizo un llamado a trabajar en unidad para prevenir los daños que generará la llegada del fenómeno El Niño. En ese contexto, pidió explícitamente que su exhortación llegue al Congreso, donde hay expectativa en el Senado sobre el reinicio del debate sobre el pedido de facultades legislativas con reclamos de la oposición. “Estamos tomando todas las medidas. Por eso es tan importante que en estos momentos que vamos a enfrentar un periodo de emergencia estemos todos unidos y este mensaje, esperemos que llegue también al Congreso de la República”, dijo ante la prensa antes de retirarse de Piura. Previamente, la mandataria había destacado la importancia de realizar obras y trabajos preventivos para enfrentar El Niño. Al respecto, destacó la necesidad de que haya unidad entre todos los peruanos. “La única manera en la que vamos a poder salir adelante, enfrentar este fenómeno climatológico como vemos en imágenes de otros países y otras partes del mundo que son de dimensiones muy grandes, la única manera es trabajando unidos”, exclamó. La mandataria viajó a Piura este viernes para supervisar la labor de descolmatación de ríos y desde ahí resaltó la importancia del trabajo conjunto. Posteriormente, tiene agendado trasladarse a La Libertad para vigilar también trabajos de prevención. Keiko Fujimori insistió en su invocación para que las autoridades locales de Piura, así como el gobierno central, trabajen unidos. Mencionó que hoy también visitará La Libertad como parte de su recorrido para supervisar las zonas más vulnerables ante El Niño. “Estaremos preparados pero no sabemos si será suficiente (...) Hago un llamado para que todos los ciudadanos colaboren. Hay mucha maneras de poder ayudar”, exhortó. La presidenta mencionó como ejemplo preparar las casas, conocer las rutas de evacuación y no contaminar los ríos. Según informó la Presidencia de la República, la mandataria, junto a los ministros de Desarrollo Agrario y Riego, Marco Vinelli, y Defensa, Rafael Belaúnde, supervisan las intervenciones preventivas ante el fenómeno El Niño en Piura y La Libertad. Se trata de trabajos en puntos críticos y obras de protección para reducir los riesgos de inundaciones y huaicos. Detalló que en Piura, la jefa de Estado supervisará los trabajos de limpieza, descolmatación y conformación de bordos ejecutados por la Autoridad Nacional del Agua (ANA). Además, supervisarán las intervenciones a cargo del Ministerio de Defensa en siete sectores de la región. La sesión de la Comisión de Constitución del Senado este 15 de octubre se vio frustrada cuando la oposición planteó una cuestión de orden sobre los límites reglamentarios del Senado. Durante la votación, el senador Alejandro Aguinaga no emitió su voto y el resultado preliminar favoreció a la oposición con seis votos contra cinco. El presidente del grupo de trabajo, Carlos Mesía, declaró desestimada la moción e intentó un segundo llamado para incluir a Aguinaga, pero la secretaría técnica cerró el escrutinio. Esto generó reclamos de los legisladores opositores, quienes abandonaron la sala y la presidencia suspendió la sesión hasta nueva convocatoria.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/politica/gobierno/keiko-fujimori-la-unica-manera-en-la-que-vamos-a-poder-salir-adelante-es-trabajando-unidos-fenomeno-el-nino-ultimas-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Keiko Fujimori ante llegada del Fenómeno El Niño: “Se está trabajando para establecer albergues y atender a cerca de 30.000 personas”</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Desde Piura, donde viene supervisando las acciones frente a la llegada del Fenómeno El Niño, la presidenta Keiko Fujimori indicó que se está trabajando para establecer módulos temporales y así ayudar las familias que deban abandonar sus viviendas durante las inundaciones a causas de las fuertes lluvias. “Se está trabajando ya en establecer albergues para poder atender a cerca de 30.000 personas, esperemos que estos no sean necesitados”, señaló. Sin embargo, a quienes viven en zonas de riesgo, exhortó evaluar alternativas de alojamiento con familiares para evitar desplazamientos de último hora. Sobre las alertas ante estos desastres naturales, Fujimori Higuchi recalcó que en varias regiones del Perú hay un margen entre tres a cuatros horas para que así la población evacúe a las zonas más seguras. “Acá lo importante es saber hacia dónde evacuar, no acercarse al río”, advirtió. En esa misma línea, pidió a los ciudadanos no arrojar residuos a los cauces y mantenerse informados sobre las alertas oficiales. La presidenta dejó en claro que el río Piura ha sido limpiado hasta donde lo permiten las intervenciones realizadas: “Más que eso no podemos hacer. Pero el Mega Niño puede ser mucho más grande de lo que nosotros tenemos planificado”, apuntó. “Se están tomando todas las medidas. Por eso es tan importante que en estos momentos que vamos a enfrentar un período de medidas de emergencia, estemos todos unidos. Y este mensaje esperemos que llegue también al Congreso de la República”, dijo a los medios. Cabe resaltar que uno de los sectores con mayor avance es Los Ejidos–Puente Bolognesi, donde los trabajos alcanzaron el 100% de ejecución física: se intervinieron los 4,85 kilómetros previstos. Sin embargo, el avance en volumen de descolmatación llega al 85,30%, equivalente a 464.382 metros cúbicos.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/peru/piura/fenomeno-el-nino-keiko-fujimori-se-esta-trabajando-para-establecer-albergues-y-atender-a-cerca-de-30000-personas-ultimas-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Huancabamba (Piura)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Huancabamba, según el conteo oficial de la ONPE al 99.721% , arroja el siguiente resultado (actualizado el 16/10/2026, a las 15:46.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-huancabamba-piura-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fenómeno El Niño: Keiko Fujimori inspecciona obras de prevención ante inundaciones y huaicos en Piura y La Libertad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>La presidenta de la República, Keiko Fujimori, supervisa este viernes las obras de prevención ante el fenómeno El Niño en las regiones de Piura y La Libertad. La mandataria realiza la visita junto con el ministro de Desarrollo Agrario y Riego, Marco Vinelli, y el ministro de Defensa, Rafael Belaúnde, para verificar los avances de las intervenciones destinadas a reducir el riesgo de inundaciones y huaicos. La jornada forma parte del viaje de trabajo número 21 de la jefa de Estado y comprende la inspección de trabajos de limpieza y descolmatación de cauces, la conformación de bordos y las obras de protección en puntos críticos de ambas regiones. En Piura, Fujimori supervisará las intervenciones ejecutadas por la Autoridad Nacional del Agua (ANA), que incluyen la limpieza, descolmatación y conformación de bordos para facilitar el desplazamiento del agua ante eventuales crecidas. Uno de los sectores con mayor avance es Los Ejidos–Puente Bolognesi, donde los trabajos alcanzaron el 100% de ejecución física: se intervinieron los 4,85 kilómetros previstos. Sin embargo, el avance en volumen de descolmatación llega al 85,30%, equivalente a 464.382 metros cúbicos. En otros puntos, las labores continúan en ejecución. El sector El Milagro–La Encantada registra un avance físico del 27,59%, mientras que Piedra Negra alcanza el 20,73%. Las autoridades también verificarán las intervenciones a cargo del Ministerio de Defensa en siete sectores de la región. Estas acciones forman parte de las medidas preventivas previstas para mejorar la capacidad de los cauces de ríos y quebradas frente a posibles incrementos del caudal. En el marco del Decreto de Urgencia N.° 008-2026, se programaron 21 intervenciones en Piura, con una meta conjunta de 49,35 kilómetros de cauces de ríos y quebradas. Los trabajos buscan reducir la acumulación de sedimentos y mejorar las condiciones para el tránsito del agua, con el objetivo de disminuir los riesgos de desbordes e inundaciones durante el fenómeno El Niño. Según la información proporcionada, la culminación de las labores en Los Ejidos–Puente Bolognesi está prevista para el 18 de octubre de 2026. La supervisión permitirá verificar el estado de las intervenciones y el cumplimiento de los plazos establecidos. En La Libertad, la presidenta realizará un sobrevuelo para verificar el progreso de la solución integral de las quebradas San Ildefonso y San Carlos, proyecto ejecutado por la Autoridad Nacional de Infraestructura (ANIN). De acuerdo con el reporte técnico proporcionado, las obras presentan avances físicos de 78,82% en San Ildefonso y 69,52% en San Carlos. La inversión total asciende a S/ 1.664 millones. El proyecto contempla la construcción de diques, un túnel de 1,5 kilómetros para derivar las aguas de la quebrada San Ildefonso hacia San Carlos, canales de conducción que suman 12,85 kilómetros y defensas ribereñas a lo largo de 17,2 kilómetros del río Moche. Estas infraestructuras buscan encauzar las aguas y reducir la exposición de las zonas urbanas y productivas ante eventuales lluvias intensas y huaicos.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/peru/piura/fenomeno-el-nino-keiko-fujimori-inspecciona-obras-de-prevencion-ante-inundaciones-y-huaicos-en-piura-y-la-libertad-ultimas-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Sechura (Piura)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Sechura, según el conteo oficial de la ONPE al 100% , arroja el siguiente resultado (actualizado el 16/10/2026, a las 18:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-sechura-piura-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Paita (Piura)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Paita, según el conteo oficial de la ONPE al 100% , arroja el siguiente resultado (actualizado el 16/10/2026, a las 18:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-paita-piura-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>El Comercio</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Piura (Piura)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Piura, según el conteo oficial de la ONPE al 99.357% , arroja el siguiente resultado (actualizado el 16/10/2026, a las 20:06.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-piura-piura-noticia/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Dos alumnas ante la Fiscalía por caso de presunto abuso sexual en Talara</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Dos escolares desfilarán ante la Fiscalía de la Familia de Talara con relación a las investigaciones en curso por abuso sexual en manada contra una alumna. Ambas han sido citadas para que rindan su declaración a fin de esclarecer lo ocurrido en el salón de clases. Se conoció que las dos estudiantes habrían engañada a su compañera de aula para que ingresara, para luego sujetarla de las manos y permitir que los seis a ocho alumnos entren para supuestamente abusar sexualmente de ella, en horario de recreo. ESTRICTO CONTROL El director de la I. E. Santa Rosa de Lima, Víctor Atarama, indicó que mientras las investigaciones avanzan en estricta reserva, en la escuela del nivel inicial, primario y secundario, se han implementado nuevas medidas de control en los pabellones de cada grado, con la estricta participación de todos los docentes. También señaló que, el protocolo no les impide conversar con los estudiantes para evitar la revictimización, y que solo le corresponde a la fiscalía realizar esa acción. Sin embargo, refirió que el mismo exige contactar a los padres para informar los hechos ocurridos para que asuman sus respectivos compromisos. UGEL PDE CELERIDAD Por otro lado. la UGEL Talara pide a las autoridades que aceleren las investigaciones a fin de determinar si hubo un real abuso sexual, o fue un hostigamiento o tocamientos indebidos contra la alumna. El consejero regional por Talara, Carlos Castillo Ipanaqué, informó que solicitará la intervención de las comisiones de Educación o la de Mujer y Poblaciones Vulnerables del Congreso de la República, para que el caso no quede impune.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/dos-alumnas-ante-la-fiscalia-por-caso-de-presunto-abuso-sexual-en-talara/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Somos Perú pide recontar los votos en Piura: se acorta distancia entre La Torre y Paz</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Durante la audiencia pública virtual convocada por el Jurado Nacional de Elecciones (JNE) para evaluar el caso de la nulidad de las elecciones en San Juan de Bigote, la defensa legal de Somos Perú, Ubaldo Pizarro, se mantuvo firme sobre el pedido del recuento de votos que se encuentran en poder de la Fiscalía de Morropón. Sin embargo, el abogado Juan Carlos Álamo fue tajante en señalar que el acta fiscal solo da cuenta de la recuperación de una parte del material electoral y no del todo el proceso, por lo que ratificó su posición de la nulidad de las elecciones. Ahora será el JNE la entidad que deberá tomar la decisión del caso. En tanto, sigue la disputa por el segundo lugar: al 97.662% del reporte de la ONPE, el candidato Guillermo La Torre (Podemos) seguía en segundo lugar con 175,657 votos, mientras que Santiago Paz (Somos Perú) tenía 174,122 votos. La diferencia entre ambos es de 1535 votos.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/somos-peru-pide-recontar-los-votos-en-piura-se-acorta-distancia-entre-la-torre-y-paz/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Neyra, en manos del JNE: abogado espera fallo y denuncia al gobernador y consejeros</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>El abogado Juan Mejía Seminario informó que una persona suplantó la identidad de una funcionaria del Jurado Nacional de Elecciones (JNE) para comunicarle que dicha entidad había fallado a favor de su solicitud de suspender al gobernador regional Luis Neyra. De acuerdo con el letrado, su pedido se sustentaba en la presunta omisión de funciones de Neyra León respecto a las medidas de prevención frente a El Niño. Sin embargo, indicó a LA HORA que todo se habría tratado de una “suplantación de identidad” y de una “trampa política”. En tanto, la Procuraduría del JNE ha iniciado las diligencias respectivas; Mejía deberá acreditar su habilitación como abogado y el pago de un arancel, por lo que espera que la próxima semana se lleve a cabo la audiencia y, en un plazo de 48 horas posteriores a la audiencia, se emita el fallo correspondiente. “En 10 días ya se conocerá el desenlace”, indicó, al mismo tiempo que informó que ya realizó la denuncia penal contra el gobernador por omisión de deberes funcionales. Dijo que la denuncia alcanza a los consejeros.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/neyra-en-manos-del-jne-abogado-espera-fallo-y-denuncia-al-gobernador-y-consejeros/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Piura: Decomisan mercadería en operativo contra comercio ambulatorio en jr. Moretta</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Tras el retiro de motocicletas en el Jr. Gonzalo Farfán del Complejo de Mercados, ayer personal de la subgerencia de Fiscalización ejecutó un operativo en el Jr, Moretta con el decomiso de mercadería a los informales tras desacatar las notificaciones que los conminaba a no invadir los espacios públicos. El subgerente de Fiscalización, Danilo Gallo, explicó que los comerciantes habían sido notificados; no obstante, permanecieron en el lugar con estructuras de palos, toldos, guayaquiles y otros enseres en plena vía pública. “Desacataron la notificación. En base a ello, hemos procedido con el retiro y decomiso de dichos materiales de la vía pública”, dijo el funcionario, quien agregó que seguirán recuperando espacios públicos con apoyo policial.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/piura-decomisan-mercaderia-en-operativo-contra-comercio-ambulatorio-en-jr-moretta/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>46311</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Transporte de carga pesada y mototaxistas anuncian paro en Piura</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Mientras los transportistas de carga pesada anuncian una paralización nacional para los días 16, 17 y 18 de noviembre, en protesta por el incremento del precio de los combustibles y otras demandas que afectan al sector, los mototaxistas de Piura, acordaron plegarse a la medida de fuerza. Los mototaxistas están agrupados en la Federación Unificada de Mototaxistas Organizados de Piura (Fedumop) y atenderán a la convocatoria de la Federación Nacional de Mototaxistas del Perú el próximo 12 de noviembre. Así lo comunicó a La Hora el directivo Julio Farfán Correa, quien espera que se ponga freno al alza en el precio del combutible y que instituciones como Osinergmin y Fiscalía de Prevención del Delito tomen cartas en el asunto por el “alza indiscriminada” en Piura. “Queremos que vean que en Piura se paga una diferencia de tres a cuatro soles con respecto al gasohol regular y premium. Por ejemplo, en Sullana, [el regular] está 19.90 y acá, 24 soles; en Trujillo está 20 soles, y en Lima, 19 soles. El premium está 24.70 y acá en Piura, 29 soles. No es posible teniendo una refinería de Talara tan cerca se pague más caro el combustible”, indicó. OTRAS DEMANDAS El directivo de la Fedumop indicó que con la paralización del servicio también demandarán se levante la suspensión de la ley N° 31917 y reglamento N° 011-2025 de la Ley de Vehículos Menores. “Con esa ley le daban plazos a los gobiernos locales y distritales para que en un plazo de 180 días envíen el acervo documentario al MTC y así puedan saber cuántos vehículos hay a nivel nacional, pero eso quedó suspendido”, dijo. Finalmente Farfán Correa señaló que durante el paro regional que acatarán el próximo 12 de noviembre exigirán la eliminación de la tarjeta única dentro de los lineamientos normativos, entre otras demandas. CONVOCATORIA Farfán indicó que convocarán a otras modalidades del servicio público, como buses urbanos, para que se adhieran a la protesta del próximo mes.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/transporte-de-carga-pesada-y-mototaxistas-anuncian-paro-en-piura/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
+      <c r="B48" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Presidenta Fujimori llega a La Libertad para supervisar obras frente a fenómeno El Niño</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Más temprano, la mandataria estuvo en Piura junto con los ministros de Desarrollo Agrario y Riego, Marco Vinelli, y de Defensa, Rafael Belaunde, a fin de supervisar trabajos en puntos críticos y obras de protección destinadas a reducir el riesgo de inundaciones y huaicos.
 Estas intervenciones buscan reducir la vulnerabilidad de las zonas expuestas a los efectos de las lluvias asociadas al fenómeno climático.
@@ -1514,52 +1776,52 @@
 https://t.co/3BsdfJ4QOP https://t.co/PUinoukL6y (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 16, 2026</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-presidenta-fujimori-llega-a-libertad-para-supervisar-obras-frente-a-fenomeno-nino-1096223.aspx</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Piura (Piura)</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Piura, según el conteo oficial de la ONPE al 99.357% , arroja el siguiente resultado (actualizado el 16/10/2026, a las 20:06.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-piura-piura-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sechura cierra filas y no permitirá desvío del río Piura por Cristo Nos Valga</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Los sechuranos se mantienen firmes en no permitir el inicio de obras para el desvío del río Piura por río Loco, en el distrito Cristo Nos Valga, porque temen una inundación como la registrada con el fenómeno El Niño de 1998. Así lo expresaron ayer durante la sesión que realizó la Comisión Agraria de la Cámara de Diputados del Congreso de la República, donde representantes de diversas instituciones se pronunciaron sobre las actividades de mitigación para enfrentar el fenómeno El Niño. ESPERAN A KEIKO Juan Pablo Chunga, del Frente de Sechura, indicó que de ninguna manera van a permitir el inicio de trabajos, por lo que esperan hoy la llegada de la presidenta de la República, Keiko Fujimori, para dejar sentada su posición en defensa de la población que se dedica a la agricultura, ganadería y otras actividades económicas en la zona. “En la zona hay agricultura, ganadería, hay más de 25 mil cabezas de ganado caprino que se verían afectadas”, expresó el dirigente, quien fue respaldado por otros dirigentes de Sechura que también aprovecharon la sesión parlamentaria para pedir un alto a la importación del arroz dado el perjuicio que ello les genera. EN EVALUACIÓN Mientras tanto, el director de la Autoridad Administrativa del Agua, Marcos Castillo, aseguró que la propuesta de desviación del río Piura hacia el río Loco todavía está en evaluación. Además, anunció que intensificarán próximamente los trabajos de descolmatación en el tramo hacia el Bajo Piura.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/sechura-cierra-filas-y-no-permitira-desvio-del-rio-piura-por-cristo-nos-valga/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B36" s="2" t="n">
+      <c r="B50" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>Presidenta: Desde que inició el Gobierno trabajamos en regiones donde lloverá muy fuerte</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>“Se viene trabajando en todas las regiones donde sabemos que va a llover muy fuerte”, afirmó la mandataria desde el sector Los Ejidos-Puente Bolognesi, ubicado en el distrito y provincia de Piura, durante su viaje de trabajo número 21.
 En ese contexto, recordó que el pasado 3 de agosto llegó al río Piura y encontró que el cauce no había sido limpiado durante décadas, pese a las advertencias sobre la llegada del fenómeno climático.
@@ -1604,59 +1866,27 @@
 ?? https://t.co/hDy3JdT7kL (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 16, 2026</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-presidenta-desde-inicio-gobierno-trabajamos-regiones-donde-llovera-muy-fuerte-1096228.aspx</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B51" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ministro Vinelli pide a comisión del Senado evaluar con rapidez facultades legislativas</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>“Nosotros hemos ido todas las veces que fuimos requeridos a exponer las facultades, así que esperemos que la Comisión de Constitución del Senado pueda evaluar rápidamente porque ya es mucho tiempo que esperamos ”, señaló.
-Lea también: Presidenta: Desde que inició el Gobierno trabajamos en regiones donde lloverá muy fuerte Vinelli explicó que las 20 facultades otorgadas inicialmente por la Cámara de Diputados no son suficientes para fortalecer la respuesta del Gobierno frente a la inseguridad ciudadana y el fenómeno El Niño.
-Entre las medidas solicitadas destacó la posibilidad de que el Instituto Nacional de Defensa Civil (Indeci) intervenga directamente cuando ocurra una emergencia.
-“ Hay un pedido para que el Indeci atienda cuando ocurra una emergencia de manera directa, porque hoy día el sistema no funciona de esa manera.
-Entonces, si no se aprueba, no va a poder el Indeci atender de manera directa y vamos a tener que transitar por el mismo sistema que sabemos que no es tan rápido al momento de atender a los damnificados ”, manifestó.
-Supervisión de obras El titular de Desarrollo Agrario y Riego brindó estas apreciaciones tras acompañar a la presidenta de la república, Keiko Fujimori, en la supervisión de obras preventivas ante el fenómeno El Niño realizada en Piura y La Libertad .
-En Trujillo, Vinelli informó sobre las intervenciones en las quebradas de San Carlos y San Ildefonso, que comprenden, según señaló, la construcción de 61 diques, cinco barreras dinámicas y trabajos en unos 12 kilómetros de canales ; además de un túnel para desviar las aguas hacia el río Moche.
-Señaló, asimismo, que el sobrevuelo previsto para inspeccionar los diques y las barreras fue cancelado por razones de seguridad comunicadas por el piloto del helicóptero que trasladaba a las autoridades.</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-ministro-vinelli-pide-a-comision-del-senado-evaluar-rapidez-facultades-legislativas-1096244.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C38" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>MML inaugura feria Lima Lee 2026: más 70 actividades gratuitas para todas las edades</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Durante los diez días de feria se ofrecerán más de 70 actividades para públicos de todas las edades, entre conversatorios, encuentros con autores, presentaciones de novedades literarias, talleres, cuentacuentos, recitales de poesía y espectáculos musicales y artísticos.
 Lee también: UNI ofrece conferencias gratuitas para becas en Francia, Alemania y Brasil: ¿Cuándo? La inauguración contará con la participación de Fabiola Morales Castillo, teniente alcaldesa de la Municipalidad Metropolitana de Lima, y Miguel Molinari Portal, representante principal de la Gerencia de Cultura.
@@ -1684,28 +1914,28 @@
 Más en Andina: ?? El @Minsa_Peru certificó a más de 91,000 personas con discapacidad en lo que va de 2026 https://t.co/Y5EgNjrRYU https://t.co/zIZ6lFc32h (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 16, 2026</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-mml-inaugura-feria-lima-lee-2026-mas-70-actividades-gratuitas-para-todas-las-edades-1096247.aspx</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B52" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>Alianza Lima vs.
 Atlético Grau: Hora y canal para ver partido a jugarse en Matute</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Con la última victoria ante Cusco FC de visita (2-1) , los blanquiazules volvieron a ponerse en carrera por el título del segundo torneo del año.
 Alianza Lima está (19) a 6 puntos del líder Sport Huancayo (25) y un triunfo contra el 'Patrimonio de Piura' es fundamental para los dirigidos por Pablo Guede .
@@ -1721,27 +1951,27 @@
 Más en Andina: ? Conoce la fecha y la sede para el nuevo partido amistoso de Perú ante Bolivia https://t.co/3gdK2lU2BE https://t.co/ahf2oGrL1g (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 16, 2026</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-alianza-lima-vs-atletico-grau-hora-y-canal-para-ver-partido-a-jugarse-matute-1096255.aspx</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B40" s="2" t="n">
+      <c r="B53" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Indecopi eliminó más de 4,000 barreras burocráticas en primer semestre del año</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>La información está contenida en los rankings de barreras burocráticas (positivo, negativo, de funcionarios y preventivo) que semestralmente publica el Indecopi para visibilizar el cumplimiento de las normas de simplificación administrativa y la eliminación de barreras en entidades del Estado.
 Suscriben convenio para el Censo Nacional de la Pequeña Minería y Minería Artesanal El ranking positivo mide las acciones de oficio que permitieron la eliminación voluntaria de 4,011 barreras por parte de diversas entidades.
@@ -1754,27 +1984,27 @@
 Más en Andina: Cronograma de pagos 2026 de sueldos en el Estado peruano ?? https://t.co/UFEWll23L0 https://t.co/I24MIQYbj9 (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 16, 2026</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-indecopi-elimino-mas-4000-barreras-burocraticas-primer-semestre-del-ano-1096256.aspx</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B54" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>JNE convoca a encuentros juveniles en macrorregiones para impulsar participación ciudadana</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>#MGPNoticias La Marina de Guerra del Perú rindió sentido homenaje a la imagen del Señor de los Milagros en un acto litúrgico celebrado en el Santuario Nacional y Monasterio de Las Nazarenas, donde se elevó una oración para que bendiga a cada miembro de la Institución en el país.
 https://t.co/TGMVL228cH — Marina de Guerra del Perú (@naval_peru) October 16, 2026 Esta iniciativa descentralizada reunirá a jóvenes afiliados y militantes de organizaciones políticas, así como a líderes de la sociedad civil , activistas comunitarios y jóvenes independientes con vocación de gestión pública.
@@ -1793,326 +2023,27 @@
 Durante esta jornada se integrarán y priorizarán las propuestas recogidas en los encuentros previos, con el propósito de construir una agenda nacional que impulse acciones conjuntas para fortalecer la participación política juvenil en el país.</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-jne-convoca-a-encuentros-juveniles-macrorregiones-para-impulsar-participacion-ciudadana-1096268.aspx</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B42" s="2" t="n">
+      <c r="B55" s="2" t="n">
         <v>46311</v>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Senamhi: fenómeno El Niño entra en fase extraordinaria y favorecerá lluvias extremas</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>La afirmó que esta condición podría prolongarse, por lo menos, hasta febrero y coincidir con el periodo de lluvias más frecuentes en el país.
-Por ello, pidió mantener actualizada la información meteorológica y adoptar medidas preventivas ante los posibles impactos del evento climático.
-Lea también: El Niño Costero: ¿Qué indicadores señalan que es extraordinario y cómo impactaría en Perú? En declaraciones a canal N, Ávalos explicó que los episodios de El Niño extraordinario se caracterizan por un calentamiento excepcional del mar frente a la costa norte peruana, situación que favorece la disponibilidad de humedad en la atmósfera y puede desencadenar precipitaciones de gran intensidad.
-“Un Niño extraordinario es cuando supera los 3.5 grados de anomalía del mar.
-Este evento está por encima de los 4 grados”, precisó.
-Lea también: Senamhi: Niño Costero extraordinario provocará picos de 40 °C en la costa norte La especialista recordó que los antecedentes de una intensidad comparable corresponden a los eventos de 1982-1983 y 1997-1998, periodos en los que se registraron lluvias intensas y frecuentes en diferentes zonas del país.
-Lluvias podrían alcanzar entre 250 y 300 milímetros Para dimensionar la magnitud de las precipitaciones que podrían presentarse en el norte peruano, Ávalos explicó que, en condiciones normales, durante el periodo de mayor lluvia se pueden registrar acumulados de entre 20 y 30 milímetros, mientras que en un contexto de El Niño los valores podrían alcanzar entre 250 y 300 milímetros.
-La especialista utilizó un ejemplo para explicar el volumen de agua que representan estas precipitaciones: una lluvia de 300 milímetros equivale a acumular aproximadamente 300 litros de agua por metro cuadrado.
-Esta cantidad de lluvia, especialmente si se concentra en periodos cortos o se mantiene de manera persistente, puede incrementar el riesgo de inundaciones, desbordes y activación de quebradas.
-Lea también: Enfen: El Niño extraordinario ha provocado el adelanto de las lluvias en la costa norte Ávalos remarcó que el peligro no se limita a las altas temperaturas que ya se registran en la costa peruana, sino que comprende principalmente las precipitaciones intensas y sus efectos sobre las poblaciones asentadas en zonas vulnerables.
-Costa norte y central, entre las zonas expuestas La especialista indicó que las proyecciones presentadas durante la entrevista muestran condiciones favorables para lluvias por encima de lo normal desde Tumbes y Piura hasta sectores de la costa central.
-Explicó que la franja costera es una de las áreas más expuestas debido al calentamiento del mar.
-En contraste, al otro lado de la cordillera se prevén condiciones más secas, que podrían favorecer la ocurrencia de sequías intensas e incendios forestales.
-Ávalos también alertó sobre la vulnerabilidad de las quebradas de la vertiente occidental de los Andes, que pueden activarse ante precipitaciones intensas.
-En ese contexto, mencionó los sectores de Chosica y Chaclacayo, en Lima este, como zonas cercanas a la capital donde podrían observarse cambios importantes asociados a las lluvias y a la activación de quebradas.
-La especialista recordó los efectos de las precipitaciones registradas durante el fenómeno El Niño costero de 2017 y advirtió que el escenario actual corresponde, según sus declaraciones, a una intensidad extraordinaria.
-Senamhi incorporará nuevos radares meteorológicos Como parte de las herramientas para mejorar el seguimiento de este evento, Ávalos destacó la incorporación de dos estaciones con radar meteorológico, ubicadas en Piura e Ica, que permitirán estudiar las características de las precipitaciones asociadas al fenómeno.
-Explicó que estos equipos proporcionan información más detallada sobre las nubes en desplazamiento, el tipo de gotas y la concentración de agua que transportan los sistemas nubosos.
-Esta información permitirá conocer mejor la tipología de las lluvias y contribuirá a fortalecer los servicios de alerta temprana, con el objetivo de disponer de datos más precisos para las acciones de prevención y respuesta.
-La especialista consideró que esta nueva tecnología representa un avance para el Senamhi y para el país, en un contexto en el que resulta fundamental anticipar los posibles impactos de las precipitaciones.
-Preparación ante los posibles impactos Ante el escenario previsto, Ávalos insistió en la importancia de contar con información actualizada y adoptar medidas de seguridad, especialmente en las localidades expuestas a inundaciones y activación de quebradas.
-Los antecedentes de anteriores episodios extraordinarios muestran que las lluvias pueden ser intensas, frecuentes y persistentes, lo que dificulta las labores de recuperación cuando los daños se producen de manera sucesiva.
-Por ello, la especialista subrayó la necesidad de que las autoridades y la población estén preparadas antes del inicio de las lluvias más intensas, con especial atención a los sectores vulnerables de la costa norte y central.
-Más en Andina: ?? El 17 de octubre se celebra en Perú el Día de las Áreas Naturales Protegidas.
-¿Cómo aportan al desarrollo sostenible del país? https://t.co/RyKvBjrH9W https://t.co/LPvFs1CNTy (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 16, 2026</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>https://andina.pe/agencia/noticia-senamhi-fenomeno-nino-entra-fase-extraordinaria-y-favorecera-lluvias-extremas-1096225.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Transporte de carga pesada y mototaxistas anuncian paro en Piura</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Mientras los transportistas de carga pesada anuncian una paralización nacional para los días 16, 17 y 18 de noviembre, en protesta por el incremento del precio de los combustibles y otras demandas que afectan al sector, los mototaxistas de Piura, acordaron plegarse a la medida de fuerza. Los mototaxistas están agrupados en la Federación Unificada de Mototaxistas Organizados de Piura (Fedumop) y atenderán a la convocatoria de la Federación Nacional de Mototaxistas del Perú el próximo 12 de noviembre. Así lo comunicó a La Hora el directivo Julio Farfán Correa, quien espera que se ponga freno al alza en el precio del combutible y que instituciones como Osinergmin y Fiscalía de Prevención del Delito tomen cartas en el asunto por el “alza indiscriminada” en Piura. “Queremos que vean que en Piura se paga una diferencia de tres a cuatro soles con respecto al gasohol regular y premium. Por ejemplo, en Sullana, [el regular] está 19.90 y acá, 24 soles; en Trujillo está 20 soles, y en Lima, 19 soles. El premium está 24.70 y acá en Piura, 29 soles. No es posible teniendo una refinería de Talara tan cerca se pague más caro el combustible”, indicó. OTRAS DEMANDAS El directivo de la Fedumop indicó que con la paralización del servicio también demandarán se levante la suspensión de la ley N° 31917 y reglamento N° 011-2025 de la Ley de Vehículos Menores. “Con esa ley le daban plazos a los gobiernos locales y distritales para que en un plazo de 180 días envíen el acervo documentario al MTC y así puedan saber cuántos vehículos hay a nivel nacional, pero eso quedó suspendido”, dijo. Finalmente Farfán Correa señaló que durante el paro regional que acatarán el próximo 12 de noviembre exigirán la eliminación de la tarjeta única dentro de los lineamientos normativos, entre otras demandas. CONVOCATORIA Farfán indicó que convocarán a otras modalidades del servicio público, como buses urbanos, para que se adhieran a la protesta del próximo mes.</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/transporte-de-carga-pesada-y-mototaxistas-anuncian-paro-en-piura/</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Sechura cierra filas y no permitirá desvío del río Piura por Cristo Nos Valga</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Los sechuranos se mantienen firmes en no permitir el inicio de obras para el desvío del río Piura por río Loco, en el distrito Cristo Nos Valga, porque temen una inundación como la registrada con el fenómeno El Niño de 1998. Así lo expresaron ayer durante la sesión que realizó la Comisión Agraria de la Cámara de Diputados del Congreso de la República, donde representantes de diversas instituciones se pronunciaron sobre las actividades de mitigación para enfrentar el fenómeno El Niño. ESPERAN A KEIKO Juan Pablo Chunga, del Frente de Sechura, indicó que de ninguna manera van a permitir el inicio de trabajos, por lo que esperan hoy la llegada de la presidenta de la República, Keiko Fujimori, para dejar sentada su posición en defensa de la población que se dedica a la agricultura, ganadería y otras actividades económicas en la zona. “En la zona hay agricultura, ganadería, hay más de 25 mil cabezas de ganado caprino que se verían afectadas”, expresó el dirigente, quien fue respaldado por otros dirigentes de Sechura que también aprovecharon la sesión parlamentaria para pedir un alto a la importación del arroz dado el perjuicio que ello les genera. EN EVALUACIÓN Mientras tanto, el director de la Autoridad Administrativa del Agua, Marcos Castillo, aseguró que la propuesta de desviación del río Piura hacia el río Loco todavía está en evaluación. Además, anunció que intensificarán próximamente los trabajos de descolmatación en el tramo hacia el Bajo Piura.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/sechura-cierra-filas-y-no-permitira-desvio-del-rio-piura-por-cristo-nos-valga/</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Cierre del año escolar será el 27 de noviembre en la región Piura</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>El año escolar 2026 culminará en Piura el próximo 27 de noviembre, según el acuerdo tomado por las 12 Unidades de Gestión Educativa Local (UGEL) de Piura que acordaron adelantar la culminación de las clases sin afectar el calendario académico, debido al anuncio de lluvias de fuerte intensidad para los próximos meses y la vulnerabilidad de las escuelas. Con el acuerdo tomado, el año escolar dejará de culminar el 18 de diciembre, como lo establecía la programación inicial. II. EE., ‘EN JAQUE’ Por su parte, la secretaria general del Sutep Regional Piura, Juana Rosa Ordinola, informó que más de 250 instituciones educativas requieren mantenimiento inmediato. Espera que próximamente empiece a proveerse de calaminones, calaminas y otros materiales necesarios a los colegios que requieren mantenimiento urgente. “Hay instituciones educativas que no tienen ni cerco perimétrico, están trabajando en un estado calamitoso. Hay colegios sin auxiliares, sin personal de servicio. El Gobierno tiene que dar mayor presupuesto, por eso una comisión va a viajar a Lima y exigir mayor presupuesto al MEF”, señaló la vocera del magisterio, quien espera celeridad tras el anuncio de las lluvias en la región.</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/cierre-del-ano-escolar-sera-el-27-de-noviembre-en-la-region-piura/</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Paita (Piura)</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Paita, según el conteo oficial de la ONPE al 100% , arroja el siguiente resultado (actualizado el 16/10/2026, a las 18:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-paita-piura-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Sechura (Piura)</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Sechura, según el conteo oficial de la ONPE al 100% , arroja el siguiente resultado (actualizado el 16/10/2026, a las 18:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-sechura-piura-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Morropón (Piura)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Morropón, según el conteo oficial de la ONPE al 94.556% , arroja el siguiente resultado (actualizado el 16/10/2026, a las 16:26.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-morropon-piura-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Fenómeno El Niño: Keiko Fujimori inspecciona obras de prevención ante inundaciones y huaicos en Piura y La Libertad</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>La presidenta de la República, Keiko Fujimori, supervisa este viernes las obras de prevención ante el fenómeno El Niño en las regiones de Piura y La Libertad. La mandataria realiza la visita junto con el ministro de Desarrollo Agrario y Riego, Marco Vinelli, y el ministro de Defensa, Rafael Belaúnde, para verificar los avances de las intervenciones destinadas a reducir el riesgo de inundaciones y huaicos. La jornada forma parte del viaje de trabajo número 21 de la jefa de Estado y comprende la inspección de trabajos de limpieza y descolmatación de cauces, la conformación de bordos y las obras de protección en puntos críticos de ambas regiones. En Piura, Fujimori supervisará las intervenciones ejecutadas por la Autoridad Nacional del Agua (ANA), que incluyen la limpieza, descolmatación y conformación de bordos para facilitar el desplazamiento del agua ante eventuales crecidas. Uno de los sectores con mayor avance es Los Ejidos–Puente Bolognesi, donde los trabajos alcanzaron el 100% de ejecución física: se intervinieron los 4,85 kilómetros previstos. Sin embargo, el avance en volumen de descolmatación llega al 85,30%, equivalente a 464.382 metros cúbicos. En otros puntos, las labores continúan en ejecución. El sector El Milagro–La Encantada registra un avance físico del 27,59%, mientras que Piedra Negra alcanza el 20,73%. Las autoridades también verificarán las intervenciones a cargo del Ministerio de Defensa en siete sectores de la región. Estas acciones forman parte de las medidas preventivas previstas para mejorar la capacidad de los cauces de ríos y quebradas frente a posibles incrementos del caudal. En el marco del Decreto de Urgencia N.° 008-2026, se programaron 21 intervenciones en Piura, con una meta conjunta de 49,35 kilómetros de cauces de ríos y quebradas. Los trabajos buscan reducir la acumulación de sedimentos y mejorar las condiciones para el tránsito del agua, con el objetivo de disminuir los riesgos de desbordes e inundaciones durante el fenómeno El Niño. Según la información proporcionada, la culminación de las labores en Los Ejidos–Puente Bolognesi está prevista para el 18 de octubre de 2026. La supervisión permitirá verificar el estado de las intervenciones y el cumplimiento de los plazos establecidos. En La Libertad, la presidenta realizará un sobrevuelo para verificar el progreso de la solución integral de las quebradas San Ildefonso y San Carlos, proyecto ejecutado por la Autoridad Nacional de Infraestructura (ANIN). De acuerdo con el reporte técnico proporcionado, las obras presentan avances físicos de 78,82% en San Ildefonso y 69,52% en San Carlos. La inversión total asciende a S/ 1.664 millones. El proyecto contempla la construcción de diques, un túnel de 1,5 kilómetros para derivar las aguas de la quebrada San Ildefonso hacia San Carlos, canales de conducción que suman 12,85 kilómetros y defensas ribereñas a lo largo de 17,2 kilómetros del río Moche. Estas infraestructuras buscan encauzar las aguas y reducir la exposición de las zonas urbanas y productivas ante eventuales lluvias intensas y huaicos.</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/peru/piura/fenomeno-el-nino-keiko-fujimori-inspecciona-obras-de-prevencion-ante-inundaciones-y-huaicos-en-piura-y-la-libertad-ultimas-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Elecciones Regionales y Municipales 2026: resultados oficiales de ONPE en la provincia de Huancabamba (Piura)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Este domingo 4 de octubre se realizaron las Elecciones Regionales y Municipales 2026 (ERM 2026), proceso en el que más de 26 millones de peruanos definieron, con su voto, el futuro de sus distritos, provincias y regiones. Los comicios comenzaron a las 7 a.m. y se extendieron hasta las 5 p.m., hora en que se cerraron los centros de votación. En estas ERM 2026, los ciudadanos habilitados para sufragar eligieron a 25 gobernadores regionales, 196 alcaldes provinciales, 1696 alcaldes distritales, 364 consejeros regionales y 10.842 regidores provinciales y distritales. La votación en Huancabamba, según el conteo oficial de la ONPE al 99.721% , arroja el siguiente resultado (actualizado el 16/10/2026, a las 15:46.): Esta penalidad no es igual para todos, debido a que depende de la clasificación socioeconómica del distrito donde el ciudadano omiso al sufragio está registrado en su Documento Nacional de Identidad (DNI). La multa se calcula en función del monto de la UIT 2026, que es de S/5.500. Sí, y en este caso la penalidad equivale al 5% de una UIT, es decir, S/275.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/elecciones/elecciones-regionales-y-municipales-2026-resultados-oficiales-de-onpe-en-la-provincia-de-huancabamba-piura-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Keiko Fujimori ante llegada del Fenómeno El Niño: “Se está trabajando para establecer albergues y atender a cerca de 30.000 personas”</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Desde Piura, donde viene supervisando las acciones frente a la llegada del Fenómeno El Niño, la presidenta Keiko Fujimori indicó que se está trabajando para establecer módulos temporales y así ayudar las familias que deban abandonar sus viviendas durante las inundaciones a causas de las fuertes lluvias. “Se está trabajando ya en establecer albergues para poder atender a cerca de 30.000 personas, esperemos que estos no sean necesitados”, señaló. Sin embargo, a quienes viven en zonas de riesgo, exhortó evaluar alternativas de alojamiento con familiares para evitar desplazamientos de último hora. Sobre las alertas ante estos desastres naturales, Fujimori Higuchi recalcó que en varias regiones del Perú hay un margen entre tres a cuatros horas para que así la población evacúe a las zonas más seguras. “Acá lo importante es saber hacia dónde evacuar, no acercarse al río”, advirtió. En esa misma línea, pidió a los ciudadanos no arrojar residuos a los cauces y mantenerse informados sobre las alertas oficiales. La presidenta dejó en claro que el río Piura ha sido limpiado hasta donde lo permiten las intervenciones realizadas: “Más que eso no podemos hacer. Pero el Mega Niño puede ser mucho más grande de lo que nosotros tenemos planificado”, apuntó. “Se están tomando todas las medidas. Por eso es tan importante que en estos momentos que vamos a enfrentar un período de medidas de emergencia, estemos todos unidos. Y este mensaje esperemos que llegue también al Congreso de la República”, dijo a los medios. Cabe resaltar que uno de los sectores con mayor avance es Los Ejidos–Puente Bolognesi, donde los trabajos alcanzaron el 100% de ejecución física: se intervinieron los 4,85 kilómetros previstos. Sin embargo, el avance en volumen de descolmatación llega al 85,30%, equivalente a 464.382 metros cúbicos.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/peru/piura/fenomeno-el-nino-keiko-fujimori-se-esta-trabajando-para-establecer-albergues-y-atender-a-cerca-de-30000-personas-ultimas-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Keiko Fujimori pide unidad ante fenómeno El Niño: “Esperemos que este mensaje llegue también al Congreso de la República”</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>La presidenta de la República, Keiko Fujimori, hizo un llamado a trabajar en unidad para prevenir los daños que generará la llegada del fenómeno El Niño. En ese contexto, pidió explícitamente que su exhortación llegue al Congreso, donde hay expectativa en el Senado sobre el reinicio del debate sobre el pedido de facultades legislativas con reclamos de la oposición. “Estamos tomando todas las medidas. Por eso es tan importante que en estos momentos que vamos a enfrentar un periodo de emergencia estemos todos unidos y este mensaje, esperemos que llegue también al Congreso de la República”, dijo ante la prensa antes de retirarse de Piura. Previamente, la mandataria había destacado la importancia de realizar obras y trabajos preventivos para enfrentar El Niño. Al respecto, destacó la necesidad de que haya unidad entre todos los peruanos. “La única manera en la que vamos a poder salir adelante, enfrentar este fenómeno climatológico como vemos en imágenes de otros países y otras partes del mundo que son de dimensiones muy grandes, la única manera es trabajando unidos”, exclamó. La mandataria viajó a Piura este viernes para supervisar la labor de descolmatación de ríos y desde ahí resaltó la importancia del trabajo conjunto. Posteriormente, tiene agendado trasladarse a La Libertad para vigilar también trabajos de prevención. Keiko Fujimori insistió en su invocación para que las autoridades locales de Piura, así como el gobierno central, trabajen unidos. Mencionó que hoy también visitará La Libertad como parte de su recorrido para supervisar las zonas más vulnerables ante El Niño. “Estaremos preparados pero no sabemos si será suficiente (...) Hago un llamado para que todos los ciudadanos colaboren. Hay mucha maneras de poder ayudar”, exhortó. La presidenta mencionó como ejemplo preparar las casas, conocer las rutas de evacuación y no contaminar los ríos. Según informó la Presidencia de la República, la mandataria, junto a los ministros de Desarrollo Agrario y Riego, Marco Vinelli, y Defensa, Rafael Belaúnde, supervisan las intervenciones preventivas ante el fenómeno El Niño en Piura y La Libertad. Se trata de trabajos en puntos críticos y obras de protección para reducir los riesgos de inundaciones y huaicos. Detalló que en Piura, la jefa de Estado supervisará los trabajos de limpieza, descolmatación y conformación de bordos ejecutados por la Autoridad Nacional del Agua (ANA). Además, supervisarán las intervenciones a cargo del Ministerio de Defensa en siete sectores de la región. La sesión de la Comisión de Constitución del Senado este 15 de octubre se vio frustrada cuando la oposición planteó una cuestión de orden sobre los límites reglamentarios del Senado. Durante la votación, el senador Alejandro Aguinaga no emitió su voto y el resultado preliminar favoreció a la oposición con seis votos contra cinco. El presidente del grupo de trabajo, Carlos Mesía, declaró desestimada la moción e intentó un segundo llamado para incluir a Aguinaga, pero la secretaría técnica cerró el escrutinio. Esto generó reclamos de los legisladores opositores, quienes abandonaron la sala y la presidencia suspendió la sesión hasta nueva convocatoria.</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/politica/gobierno/keiko-fujimori-la-unica-manera-en-la-que-vamos-a-poder-salir-adelante-es-trabajando-unidos-fenomeno-el-nino-ultimas-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>46311</v>
-      </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>Enfen: lluvias aumentarán más de lo normal en la costa y la sierra hasta fines de 2026</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>En la sierra sur y la Amazonía, las precipitaciones continuarían de normal a inferior; y para el verano de 2027, lluvias sobre lo normal en la costa norte, costa central y sierra norte occidental; y de normal a inferior en la sierra sur, centro oriental y la región amazónica central y sur, precisa el comunicado oficial Enfen n.° 18-2026.
 Según el documento —que mantiene la "alerta de El Niño Costero"—, frente a la costa peruana (región Niño 1+2) es más probable que calentamiento del mar (El Niño Costero) se mantenga con una magnitud de extraordinaria hasta enero de 2027, para luego disminuir a fuerte hasta inicios del otoño de 2027.
@@ -2136,84 +2067,41 @@
 La nueva especie vegetal se llama "Salvia messii" y es endémica de los Andes del centro y sur del Perú https://t.co/JpI0u66FYs https://t.co/mkHrFhW9GN (function(w,q){w[q]=w[q]||[];w[q].push(["_mgc.load"])})(window,"_mgq"); — Agencia Andina (@Agencia_Andina) October 16, 2026</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-enfen-lluvias-aumentaran-mas-de-normal-la-costa-y-sierra-hasta-fines-2026-1096285.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>46310</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Más de 3 millones de hectáreas de bosque seco resisten en el norte: la lucha por recuperar un ecosistema degradado</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Lleva casi 40 años recorriendo un bosque que conoce de memoria. José Guevara Huamán es guardaparque voluntario y desde 1988 ha entregado buena parte de su vida a custodiar la flora y fauna del lugar, pero también a protegerlas de la acción humana. Sus raíces están en el bosque seco que hoy integra el Área de Conservación Regional Salitral-Huarmaca, en Piura. El vínculo con este territorio empezó mucho antes de que fuera reconocido como área de conservación, en 2011. “Nosotros de este bosque vivimos”, repite. La jornada de Guevara no transcurre desde una caseta, como muchos podrían imaginar. Empieza temprano, a veces cuando todavía no ha salido el sol. Puede internarse en el bosque a las cinco de la mañana y regresar recién a las cuatro o cinco de la tarde. Durante horas recorre a pie sectores como El Oso, La Caña Brava o El Guabo. En el camino, el aroma del palo santo acompaña parte del recorrido entre hualtacos y pasallos, mientras el ganado avanza entre los árboles y, en algún punto del bosque, se esconden venados, pumas, sajinos y la pava aliblanca, un ave endémica y en peligro de extinción que tiene aquí su hábitat. Mientras camina, el hombre también busca las huellas de quienes entran al bosque para depredarlo. Una de sus tareas es detectar la extracción ilegal de especies como el palo santo y reportarla. “La gente lo extrae, se lo lleva para el mercado. Lo cortan verde y lo dejan que se seque”, cuenta. Un árbol menos puede parecer poco frente a la extensión del paisaje, pero la extracción repetida durante años es precisamente una de las presiones que enfrenta este ecosistema. El bosque que vigila es apenas una parte de uno mucho mayor. Los bosques secos ocupan 3.422.904 hectáreas entre Tumbes, Piura, Lambayeque y La Libertad. Su apariencia cambia con el agua: durante largos periodos secos pierden verdor y, cuando regresan las lluvias, semillas que permanecían en el suelo germinan y la vegetación vuelve a abrirse paso. Sin embargo, detrás de esa capacidad para recuperarse existe una realidad mucho más compleja: alrededor del 95% de estos bosques se encuentra degradado por procesos históricos de fragmentación y pérdida de cobertura. El Comercio viajó hasta Piura para conocer qué se está haciendo para conservar y recuperar este ecosistema. La visita se realizó durante el X Congreso Regional Forestal (COREFOR), un espacio que reúne investigaciones y experiencias vinculadas a la gestión de los bosques. Pero el viaje fue más allá de las exposiciones. Permitió internarse en uno de estos territorios y conocer el trabajo que ocurre todos los días lejos de los auditorios: guardaparques que recorren durante horas el bosque, comunidades que intentan recuperar zonas degradadas, especies que luchan por conservar su hábitat y alternativas productivas que parten de una misma idea, que quienes viven del bosque puedan seguir haciéndolo sin acabar con él. Un ecosistema degradado que vuelve a reverdecer Ese bosque que José Guevara recorre desde hace décadas no luce igual durante todo el año. En septiembre, cuando El Comercio ingresó a Salitral-Huarmaca, buena parte del camino estaba dominado por tonos secos, ramas desnudas y un suelo que levantaba polvo con cada paso. Es una imagen que puede resultar engañosa para quien llega por primera vez. Aunque se les conoce simplemente como bosques secos, su denominación técnica es “bosques estacionalmente secos”. Mirbel Epiquién, director general de Diversidad Biológica del Ministerio del Ambiente (Minam), explicó que la sequedad forma parte de un ciclo y que, durante las temporadas de lluvia, un territorio aparentemente árido puede volver a cubrirse de vegetación. “En realidad el nombre técnico es bosques estacionalmente secos del norte del Perú. Hay épocas normales de lluvias en donde comienzan a reverdecer”, explicó. La transformación puede ser considerable. Las lluvias intensas asociadas a fenómenos como El Niño, pese a los daños que pueden ocasionar en las ciudades del norte, favorecen dentro del bosque la recarga de acuíferos, la germinación de semillas y la recuperación de cobertura vegetal. “El fenómeno de El Niño tiene un efecto negativo sobre las actividades económicas en general, pero tiene un efecto muy positivo en recarga de acuífero, ampliación del bosque y demás”, señaló Anton Willems, director ejecutivo de Profonanpe. Epiquién explica esa respuesta a partir de la resiliencia del propio ecosistema. Incluso después de largos periodos sin agua, permanecen semillas capaces de germinar cuando vuelven a encontrar las condiciones necesarias. “Viene la lluvia y las semillas comienzan a germinar nuevamente. Los árboles también comienzan a protegerse entre ellos, dándole cobijo, refugio a otros arbolitos”, señaló. Esa capacidad, agregó, permite que el bosque resista amenazas naturales y aquellas provocadas por la actividad humana. Ayudar al bosque a recuperarse Pero que el bosque sea capaz de reverdecer no significa que pueda recuperarse solo de décadas de degradación. En los mismos caminos que recorre Guevara, el ganado se desplaza libremente entre los árboles. Vacas y cabras forman parte del paisaje y también de la economía de las familias, pero para un brote que apenas empieza a crecer pueden convertirse en una amenaza. Por eso, en algunos pilotos de restauración se dispersaron semillas antes de las lluvias y luego se protegieron las nuevas plantas. Sergio Lazo, coordinador del proyecto Bosque Seco, explica que las comunidades utilizan ramas para construir pequeñas estructuras alrededor de los brotes. Las llaman “nodrizas”. “Las semillas, el árbol crece y está la presión de sus mismos animales. Entonces, se les ha enseñado que eso lo tienen que proteger con unas ramas y eso se llama nodrizas”, explicó Lazo. La protección permanece hasta que el árbol alcanza una altura suficiente para reducir el riesgo de ser consumido. La escena ayuda a entender una de las dificultades de recuperar este ecosistema: aquello que se busca conservar convive con las actividades de quienes dependen de él. Y esa relación no necesariamente tiene que ser negativa. Cuando llegan las lluvias hay más alimento para el ganado, aumenta la floración y también puede mejorar la producción de miel. “Es una oportunidad porque se alimentan mejor los animales de los que viven las comunidades. Hay mejor floración, hay mejor miel. Esas comunidades que viven de esos animales producen mejor queso, hay mejor ingreso económico”, señaló Lazo. Recuperar caminos Durante el recorrido por Salitral-Huarmaca, los guardaparques pidieron guardar silencio en algunos tramos. La razón estaba en algún punto entre los árboles: la pava aliblanca. El ave, endémica y en peligro de extinción, necesita del bosque para alimentarse, reproducirse y desplazarse. Ese movimiento ayuda a entender por qué restaurar no significa solamente plantar árboles. Visto desde arriba, buena parte de las áreas conservadas aparecen como “manchones” separados entre sí. Para la fauna, la distancia entre uno y otro puede significar la pérdida de un corredor que antes formaba parte de un mismo hábitat. “Si tú ves en un mapa las áreas naturales, vas a ver manchones que son las áreas protegidas. En el tema de conectividad, lo que busca este componente es cómo esos manchones, que parecen mosaicos dispersos, comienzan a conectarse de manera que las especies puedan trasladarse de un lado a otro”, explicó Lazo. El proyecto Bosque Seco ha alcanzado acuerdos sobre unas 42.000 hectáreas para favorecer esa conectividad y tiene como objetivo llegar a 80.000. Además, cerca de 1.900 hectáreas se encuentran en proceso de restauración frente a una meta de 2.278. Las intervenciones involucran a 16 comunidades campesinas. Epiquién advierte que por eso el resultado no puede medirse únicamente contando hectáreas recuperadas. La ubicación también importa. Restaurar un espacio entre dos fragmentos puede volver a abrir el paso para animales y permitir que las semillas encuentren vegetación, humedad y condiciones para desarrollarse. “Un bosque necesita tener conectividad, es decir, continuidad, para que pueda haber flujos, sobre todo de especies de fauna”, señaló. “Por eso tenemos que garantizar que haya un corredor. Eso se llama corredores de bosque”. Vivir del bosque sin acabar con él La caminata también deja claro algo que las cifras no siempre muestran. Este no es un territorio aislado de las personas. Hay ganado entre los árboles, guardaparques que pertenecen a las propias comunidades y familias que durante generaciones han encontrado aquí alimento y recursos. El propio Guevara lo resumió al iniciar el recorrido: “Nosotros de este bosque vivimos”. Por eso, recuperar el bosque sin ofrecer alternativas a quienes dependen de él sería resolver solo una parte del problema. El proyecto trabaja en cerca de 60 intervenciones, 34 de ellas vinculadas a restauración, y busca que ese proceso avance junto con actividades económicas asociadas a los propios recursos del ecosistema. “Vamos a hacer la restauración, comenzamos a armar el piloto y vamos haciendo la actividad productiva también a la paralela”, explicó Lazo. El algarrobo, la ganadería caprina y la producción de miel forman parte de esa relación histórica. A ellas se suman el turismo, la meliponicultura, el aprovechamiento de fibras naturales y otras actividades que buscan generar ingresos sin perder de vista la conservación. En Piura, durante el I Festival Bosque Seco, 30 asociaciones mostraron parte de ese trabajo. Había miel de abeja y de meliponas, algarrobina, derivados lácteos de leche de cabra, cacao y artesanías. Productos distintos nacidos de un mismo territorio. Para Willems, allí está uno de los principales retos. “La economía en el norte es un boom y eso es algo que deberíamos aplaudir. Pero solamente va a ser sostenible si esa economía te permite disfrutar de un ambiente sano, si te permite disfrutar de los servicios ecosistémicos que necesitamos”, sostuvo. Del palo santo a las abejas sin aguijón Horas después de haber iniciado la caminata con las estrellas todavía sobre nuestras cabezas, el sol ya caía con fuerza sobre Serrán. El recorrido terminó por llevarnos hasta el vivero, donde la conservación adquiría una escala mucho más pequeña: en un espacio acondicionado, varias cajas de madera resguardaban colonias de abejas nativas. Son meliponas y otras especies que comparten una característica particular: no tienen aguijón. Cumplen un papel importante como polinizadoras y algunas forman naturalmente sus enjambres dentro de árboles como el palo santo y el hualtaco. El palo santo vuelve a aparecer aquí, pero desde otro ángulo. Es el mismo árbol cuyo aroma acompañó buena parte de la caminata y uno de los que Guevara vigila para evitar que sea cortado ilegalmente. También puede convertirse en refugio para abejas necesarias para el propio bosque. María Adriana Requena Moscol, bióloga que trabaja en la jefatura del ACR Salitral-Huarmaca, explica que el palo santo puede ser aprovechado cuando el árbol muere y seca naturalmente. El problema comienza cuando se cortan ejemplares todavía vivos para dejarlos secar y comercializarlos. “De por sí sí se puede aprovechar, pero el palo santo seco. Lo que hacen ellos es cortarlo verde, esperan a que se seque y se lo llevan. Eso es lo que no debería pasar”, explicó. La tala no es la única amenaza que encuentran los guardaparques. Cerca de algunas quebradas, cazadores construyen pequeños escondites desde donde esperan que bajen los venados. Son conocidos como “hornos de cacería” y, cuando son encontrados durante los patrullajes, son destruidos. “Ellos se esconden dentro de estas cuevitas, esperan a que el venado baje y lo cazan. Eso también ellos lo reportan”, explicó Requena. “Aquí no se permite ningún tipo de caza porque es un área protegida. Si hay venado, se espera que se desarrolle libremente, no para consumo”. Frente a esas amenazas, las pequeñas cajas del meliponario representan otra manera de relacionarse con el mismo territorio. En lugar de extraer un árbol vivo, la apuesta es obtener valor de un bosque que permanece en pie. “Ahorita lo que se está haciendo con Bosque Seco es el tema de las meliponas, de las abejas nativas. Se está tratando de que se aproveche como un bionegocio la producción de miel”, explicó Requena. El mismo principio se extiende a otros recursos. La fibra del fruto del ceibo, por ejemplo, puede procesarse para elaborar hilos, textiles y rellenos para almohadas, chalecos o colchones. “Se encuentra dentro del bosque, es un recurso aprovechable”, agregó. La apuesta, finalmente, es que esas actividades crezcan al mismo tiempo que el bosque logra recuperarse. No será un proceso rápido. Guevara lo sabe después de casi cuatro décadas caminando entre estos árboles: conservar implica vigilar lo que permanece, pero también darle tiempo a aquello que intenta volver a crecer. “Restaurar una hectárea de bosque seco es un proceso que toma muchísimos años; sin embargo, tienes que hacerlo”, resumió Willems.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/peru/mas-de-3-millones-de-hectareas-de-bosque-seco-resisten-en-el-norte-la-lucha-por-recuperar-un-ecosistema-degradado-noticia/</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>El Comercio</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>46310</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Piura: entregan títulos de propiedad a más de 900 familias</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Tras más de 18 años de espera, familias piuranas avanzaron hacia la seguridad jurídica de sus viviendas como parte de una jornada en la que el Organismo de Formalización de la Propiedad Informal (Cofopri) entregó 922 títulos de propiedad a familias de la región, beneficiando a más de 3,680 ciudadanos. En el asentamiento humano Los Libertadores, en el distrito de Castilla, se entregaron los títulos a sus beneficiarios. En dicha zona, algunas familias ya avanzan con la construcción de sus viviendas mediante el programa Techo Propio, tras completar los procedimientos de formalización correspondientes. La inscripción registral de sus predios constituye un aspecto relevante para acreditar la propiedad y continuar con sus proyectos habitacionales, de acuerdo con los requisitos aplicables a cada caso. “Ha sido gratificante venir desde Lima especialmente para acompañar a la Oficina Zonal de Cofopri en Piura en esta entrega de más de 920 títulos de propiedad, sobre todo porque se trata de posesiones informales que ya han avanzado en el acceso al programa Techo Propio y que necesitan contar con el título de propiedad para consolidar esos avances”, refirió la directora ejecutiva de Cofopri, Cecilia Castro Torres, quien espera que este logro sea un modelo a seguir por otros asentamientos humanos de la región. Durante las entregas de los documentos en Castilla, los beneficiarios compartieron la importancia de contar con el título de propiedad después de años de espera, al representar un respaldo jurídico para sus viviendas y una base para proyectar mejoras en sus hogares. La titulación también llegó a Las Lomas La intervención regional se extendió al distrito de Las Lomas, donde la entrega de títulos comenzó un día antes mediante visitas domiciliarias. Entre los sectores atendidos estuvieron Campo Santo, con 142 títulos; San Francisco de Yuscay, con 83; y Viviano Espinoza, con 55, además de otros sectores del distrito. La jornada también comprendió la entrega de tres títulos para el sector Educación y uno para el sector Salud, destinados a formalizar predios vinculados con la prestación de servicios públicos. Entre las instituciones beneficiadas figuró la Institución Educativa Inicial San Francisco de Yuscay, creada en 2016, cuyo terreno obtuvo formalización mediante la inscripción correspondiente. Con estas acciones, Cofopri continuó impulsando la formalización de la propiedad urbana en Piura, tanto para las familias que buscan consolidar la seguridad jurídica de sus viviendas como para las instituciones que requieren contar con predios formalizados para el desarrollo de sus actividades.</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https://elcomercio.pe/lima/sucesos/piura-entregan-titulos-de-propiedad-a-mas-de-900-familias-noticia/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Candidato Guillermo La Torre se mantiene en segundo lugar y sería rival de Hilbck</t>
+          <t>Ministro Vinelli pide a comisión del Senado evaluar con rapidez facultades legislativas</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>En 1,953 votos se fijó la diferencia entre el candidato de Podemos, Guillermo La Torre, y el postulante de Somos Perú, Santiago Paz, quienes pugnan por llegar a la segunda vuelta electoral programada para el 6 de diciembre. Así consta en la página oficial de la ONPE. Según el reporte de la ONPE actualizado al 97.206% que mantenía al candidato Reynaldo Hilbck en primer lugar con 21.992%, segundo lugar Podemos con 18.039% (174,813 votos) y Somos Perú con 17.837% (132,860 votos). Esto según el reporte de la ONPE actualizado al 97.206% que mantenía al candidato Reynaldo Hilbck en primer lugar con 21.992%, segundo lugar Podemos con 18.039% (174.813 votos) y Somos Perú con 17.837% (132.860 votos). Según la información oficial, existen 147 actas para envío al Jurado Electoral Especial; mientras que actas pendientes ya no se registran en el sistema de ONPE. SUPUESTO FRAUDE En tanto, la actualización del reporte de la ONPE avanza con lentitud, ayer el candidato Santiago Paz y simpatizantes de Somos Perú protestaron en horas de la tarde en los exteriores del Ministerio Público, en la calle Lima de Piura. El candidato insistió en señalar un supuesto fraude en las elecciones realizadas el 4 de octubre y cuestionó la nulidad de las elecciones en San Juan de Bigote. Asimismo, Paz demandó a la Fiscalía celeridad en las investigaciones para identificar aquellos que vulneraron el proceso electoral. “Ya deberían estar en prisión porque lo que han hecho es sumamente grave”, dijo.</t>
+          <t>“Nosotros hemos ido todas las veces que fuimos requeridos a exponer las facultades, así que esperemos que la Comisión de Constitución del Senado pueda evaluar rápidamente porque ya es mucho tiempo que esperamos ”, señaló.
+Lea también: Presidenta: Desde que inició el Gobierno trabajamos en regiones donde lloverá muy fuerte Vinelli explicó que las 20 facultades otorgadas inicialmente por la Cámara de Diputados no son suficientes para fortalecer la respuesta del Gobierno frente a la inseguridad ciudadana y el fenómeno El Niño.
+Entre las medidas solicitadas destacó la posibilidad de que el Instituto Nacional de Defensa Civil (Indeci) intervenga directamente cuando ocurra una emergencia.
+“ Hay un pedido para que el Indeci atienda cuando ocurra una emergencia de manera directa, porque hoy día el sistema no funciona de esa manera.
+Entonces, si no se aprueba, no va a poder el Indeci atender de manera directa y vamos a tener que transitar por el mismo sistema que sabemos que no es tan rápido al momento de atender a los damnificados ”, manifestó.
+Supervisión de obras El titular de Desarrollo Agrario y Riego brindó estas apreciaciones tras acompañar a la presidenta de la república, Keiko Fujimori, en la supervisión de obras preventivas ante el fenómeno El Niño realizada en Piura y La Libertad .
+En Trujillo, Vinelli informó sobre las intervenciones en las quebradas de San Carlos y San Ildefonso, que comprenden, según señaló, la construcción de 61 diques, cinco barreras dinámicas y trabajos en unos 12 kilómetros de canales ; además de un túnel para desviar las aguas hacia el río Moche.
+Señaló, asimismo, que el sobrevuelo previsto para inspeccionar los diques y las barreras fue cancelado por razones de seguridad comunicadas por el piloto del helicóptero que trasladaba a las autoridades.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/candidato-guillermo-la-torre-se-mantiene-en-segundo-lugar-y-seria-rival-de-hilbck/</t>
+          <t>https://andina.pe/agencia/noticia-ministro-vinelli-pide-a-comision-del-senado-evaluar-rapidez-facultades-legislativas-1096244.aspx</t>
         </is>
       </c>
     </row>
@@ -2228,24 +2116,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Detienen en Piura a médico gastroenterólogo sentenciado por violación</t>
+          <t>Essalud en alerta: Reportan 1609 casos de dengue</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>La Policía Nacional del Perú (PNP) capturó en Piura al médico gastroenterólogo Luis Enrique Vásquez Elera , quien registraba una condena de 18 años de prisión por el delito de violación sexual y una orden de captura vigente. El profesional fue intervenido por agentes de la División de Investigación Criminal (Divincri) cuando se encontraba en el consultorio de una clínica local, donde atendía a sus pacientes. Según informó el jefe de la Divincri Piura, coronel PNP Javier Méndez, el sentenciado era requerido por la justicia desde 2023, en virtud de una orden emitida por un órgano jurisdiccional de Lima. Tras verificar su identidad y confirmar el mandato judicial, los efectivos procedieron con su detención para ponerlo a disposición de las autoridades competentes. ¿Cómo fue la captura del médico sentenciado en Piura? La intervención policial se realizó al interior del consultorio médico donde trabajaba Vásquez Elera. De acuerdo con la información proporcionada por la Policía, el personal de la Divincri llegó al establecimiento para verificar la identidad del profesional, quien era buscado por las autoridades judiciales. Durante el procedimiento, el médico se habría negado inicialmente a identificarse e intentado evitar la verificación de sus documentos. Sin embargo, los agentes continuaron con las diligencias correspondientes y corroboraron sus datos en los sistemas policiales. Una vez confirmada la existencia de la orden de captura, los efectivos ejecutaron la intervención. El caso llamó la atención debido a que el sentenciado se encontraba trabajando en la región norte del país pese a la condena impuesta por la justicia. El coronel PNP Javier Méndez señaló que el mandato judicial había sido emitido en 2023 por un juzgado de Lima. Según la información policial, el intervenido habría utilizado identidades falsas para mantenerse fuera del alcance de las autoridades, un aspecto que deberá ser esclarecido mediante las diligencias correspondientes. ¿Por qué condenaron a 18 años de prisión a Luis Vásquez Elera? La condena contra el gastroenterólogo fue impuesta por la Corte Superior de Justicia de Lima Norte por la violación sexual de la madre de su hijo. Los hechos ocurrieron la noche del 18 de diciembre de 2021, en la vivienda de la agraviada, ubicada en el distrito limeño de San Martín de Porres. De acuerdo con la información publicada por La República sobre el proceso judicial, el tribunal determinó que el acusado empleó fuerza física para cometer el delito. Durante el juicio se evaluaron distintos elementos probatorios, entre ellos grabaciones de video, conversaciones registradas y pericias psicológicas relacionadas con el testimonio de la víctima. La relación entre ambos había sido sentimental y de ella nació un hijo en 2016. Sin embargo, según los antecedentes expuestos durante el proceso, la pareja ya no mantenía una relación estable cuando ocurrieron los hechos denunciados. Durante el juicio, la defensa del acusado sostuvo que anteriormente habían existido encuentros íntimos entre ambos. No obstante, el órgano jurisdiccional consideró que esa afirmación no acreditaba el consentimiento de la agraviada para el acto ocurrido el 18 de diciembre de 2021. ¿Por qué la pena se redujo de 20 a 18 años? Inicialmente, el Ministerio Público solicitó una pena de 20 años de prisión. Sin embargo, el Juzgado Penal Colegiado Transitorio de Lima Norte impuso una condena de 18 años, teniendo en cuenta el principio del interés superior del niño, debido a que el sentenciado tiene un hijo menor de edad en común con la agraviada. La decisión judicial también incluyó otras medidas. Según los detalles difundidos sobre la sentencia, Vásquez Elera recibió 10 años de inhabilitación para acercarse o comunicarse con la víctima y deberá pagar S/ 7.000 por concepto de reparación civil. Asimismo, se dispuso que el condenado se someta a tratamiento terapéutico como parte de las medidas vinculadas a su proceso de readaptación social. Las pruebas consideradas durante el proceso judicial Uno de los aspectos relevantes del caso fue la valoración de las grabaciones realizadas por la agraviada. Según los antecedentes difundidos sobre el juicio, parte de los registros contenía imágenes del hecho y conversaciones posteriores en las que el sentenciado pedía perdón y hacía referencia a la posibilidad de ir a prisión. Estos elementos fueron considerados por el tribunal junto con las demás pruebas presentadas durante el proceso. La sentencia también abordó los argumentos de la defensa relacionados con un conflicto familiar previo, incluidos asuntos vinculados con la manutención del menor. Los jueces concluyeron que dicho antecedente no constituía, por sí mismo, una razón suficiente para considerar falsa la denuncia. El tribunal también remarcó que una relación sentimental previa o la existencia de encuentros íntimos anteriores no implican consentimiento para una relación sexual posterior. ¿Qué pasará con el médico detenido en Piura? Tras su captura, el médico fue trasladado bajo medidas de seguridad y se informó que sería conducido a Lima para quedar a disposición del órgano jurisdiccional correspondiente y cumplir la condena impuesta. La intervención estuvo a cargo de agentes de la Divincri de Piura, unidad policial que realizó las verificaciones necesarias para ejecutar el mandato judicial. La situación del detenido deberá continuar por los canales legales establecidos para el cumplimiento de las sentencias penales. La Policía también señaló que el profesional se encontraba ejerciendo labores médicas pese a registrar una condena judicial. Las circunstancias relacionadas con su identidad y su permanencia fuera del alcance de las autoridades forman parte de los aspectos que deberán ser esclarecidos por las instancias competentes.</t>
+          <t>El incremento de casos de dengue en la región siguen encendiendo las alertas de las autoridades. En este caso, la Red Asistencial Piura de EsSalud reportó un acumulado de 1609 casos de dengue entre sus asegurados, hasta la semana epidemiológica 40. De este reporte total, 1052 casos están confirmados y 557 son probables. Los establecimientos de EsSalud que registran más casos son los de Sullana, con 362; Chulucanas, con 358; y Tambogrande, con 339. Edward Pozo Súclupe, jefe de Inteligencia Sanitaria de la institución, recomendó a los asegurados no automedicarse si presentan síntomas compatibles con el dengue y acudir a un establecimiento de salud para recibir una evaluación médica. En tanto EsSalud sigue con la campaña de vacunación contra el dengue dirigida a la población de 10 a 20 años cumplidos.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/detienen-en-piura-a-medico-gastroenterologo-sentenciado-por-violacion/</t>
+          <t>https://eltiempo.pe/local/essalud-en-alerta-reportan-1609-casos-de-dengue/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
@@ -2253,24 +2141,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Talara: Se complica investigación de presunto abuso en aula de colegio</t>
+          <t>Piura: entregan títulos de propiedad a más de 900 familias</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Las investigaciones sobre el sonado caso de un presunto abuso sexual contra una escolar en el interior de la I. E. “Santa Rosa de Lima” podría dar un inesperado giro debido a que, mientras avanzan las pesquisas que llevan a cabo el Ministerio Público y la Policía, los exámenes médicos legales practicados a la potencial víctima obligarían a replantear las acusaciones. LA HORA conoció que el resultado del examen físico practicado a la menor fue negativo para desfloración himeneal, pero sí se encontró desfloración antigua, sin evidencia de lesiones traumáticas recientes, por lo que llevaría a reevaluar la tipificación de los hechos y orientar la búsqueda de pruebas complementarias. Esto podría darse con los resultados de los exámenes psicológicos practicados a la escolar. Este diario también obtuvo información referente a la identificación de los presuntos involucrados. La menor reconoció con precisión a sus dos compañeras de clases, quienes serían las que -según su versión- la engañaron y sujetaron en el interior del aula, pero no logra identificar a los varones, entre seis a ocho, que habrían intentado agredirla. DEFENSORÍA Por su parte, la Defensoría del Pueblo ha intervenido de oficio tras tomar conocimiento de la presunta agresión sexual sufrida por una estudiante en la institución educativa “Santa Rosa de Lima”. La institución recomendó cumplir con el registro obligatorio en el libro de incidencias y el portal SíSeVe. En ese sentido recordó que los colegios deben priorizar el bienestar de los educandos.</t>
+          <t>Tras más de 18 años de espera, familias piuranas avanzaron hacia la seguridad jurídica de sus viviendas como parte de una jornada en la que el Organismo de Formalización de la Propiedad Informal (Cofopri) entregó 922 títulos de propiedad a familias de la región, beneficiando a más de 3,680 ciudadanos. En el asentamiento humano Los Libertadores, en el distrito de Castilla, se entregaron los títulos a sus beneficiarios. En dicha zona, algunas familias ya avanzan con la construcción de sus viviendas mediante el programa Techo Propio, tras completar los procedimientos de formalización correspondientes. La inscripción registral de sus predios constituye un aspecto relevante para acreditar la propiedad y continuar con sus proyectos habitacionales, de acuerdo con los requisitos aplicables a cada caso. “Ha sido gratificante venir desde Lima especialmente para acompañar a la Oficina Zonal de Cofopri en Piura en esta entrega de más de 920 títulos de propiedad, sobre todo porque se trata de posesiones informales que ya han avanzado en el acceso al programa Techo Propio y que necesitan contar con el título de propiedad para consolidar esos avances”, refirió la directora ejecutiva de Cofopri, Cecilia Castro Torres, quien espera que este logro sea un modelo a seguir por otros asentamientos humanos de la región. Durante las entregas de los documentos en Castilla, los beneficiarios compartieron la importancia de contar con el título de propiedad después de años de espera, al representar un respaldo jurídico para sus viviendas y una base para proyectar mejoras en sus hogares. La titulación también llegó a Las Lomas La intervención regional se extendió al distrito de Las Lomas, donde la entrega de títulos comenzó un día antes mediante visitas domiciliarias. Entre los sectores atendidos estuvieron Campo Santo, con 142 títulos; San Francisco de Yuscay, con 83; y Viviano Espinoza, con 55, además de otros sectores del distrito. La jornada también comprendió la entrega de tres títulos para el sector Educación y uno para el sector Salud, destinados a formalizar predios vinculados con la prestación de servicios públicos. Entre las instituciones beneficiadas figuró la Institución Educativa Inicial San Francisco de Yuscay, creada en 2016, cuyo terreno obtuvo formalización mediante la inscripción correspondiente. Con estas acciones, Cofopri continuó impulsando la formalización de la propiedad urbana en Piura, tanto para las familias que buscan consolidar la seguridad jurídica de sus viviendas como para las instituciones que requieren contar con predios formalizados para el desarrollo de sus actividades.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/talara-se-complica-investigacion-de-presunto-abuso-en-aula-de-colegio/</t>
+          <t>https://elcomercio.pe/lima/sucesos/piura-entregan-titulos-de-propiedad-a-mas-de-900-familias-noticia/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -2278,17 +2166,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Detienen a tres policías por cobros irregulares en La Matanza</t>
+          <t>Más de 3 millones de hectáreas de bosque seco resisten en el norte: la lucha por recuperar un ecosistema degradado</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Tres policías de la Comisaría de La Matanza, de la provincia de Morropón, fueron detenidos por sus colegas de armas y cinco fiscales de la Fecof para ser investigados por el presunto delito de cohecho pasivo propio en el ejercicio de la función policial. La intervención se realizó ayer en estricto cumplimiento a una orden judicial de detención preliminar, allanamiento con descerraje, registro personal, incautación y levantamiento del secreto de las comunicaciones de los tres agentes y civiles. LAS DILIGENCIAS La diligencia fue dirigida por el fiscal provincial Jesús Aranguren Martínez, con la participación de los fiscales adjuntos José Jiménez, Carlos Pizarro (quien tiene a cargo la investigación), Miguel Berrú y Cinthya Janeth Rondoy Bances, y contó con apoyo del personal especializado del Departamento Desconcentrado Contra la Corrupción (Depdicc) y la Dircocor, interviniendo los inmuebles autorizados judicialmente para asegurar elementos probatorios. Los hechos investigados por el Ministerio Público y Policía especializada habrían ocurrido entre el 23 y 24 de marzo último, luego que una ciudadana acudiera a la Comisaría La Matanza para denunciar haber sido víctima de un presunto delito de agresión sexual. LOS INVESTIGADOS Durante la intervención, el suboficial de segunda de la Policía Nacional, D. P. C.; suboficial de segunda, J. H. C. J.; y el suboficial de tercera de la Policía Nacional, O. A. I. con los presuntos agresores (denunciados) V. H. S. A. y H. A. R. R., habrían coordinado presuntos cobros e intercambios de dinero indebidos, utilizando el aplicativo Yape y cuentas bancarias. Todo esto habría sido utilizado para concertar pagos irregulares, a fin que la agraviada no continúe con la denuncia. Asimismo, se atribuye a los efectivos policiales involucrados haber utilizado el vehículo policial asignado a la dependencia para trasladar a la agraviada fuera de su jurisdicción hasta la ciudad de Piura, entregándole parte del dinero recolectado en efectivo y realizando depósitos bancarios para que no continuara con la grave denuncia sentada por una joven.</t>
+          <t>Lleva casi 40 años recorriendo un bosque que conoce de memoria. José Guevara Huamán es guardaparque voluntario y desde 1988 ha entregado buena parte de su vida a custodiar la flora y fauna del lugar, pero también a protegerlas de la acción humana. Sus raíces están en el bosque seco que hoy integra el Área de Conservación Regional Salitral-Huarmaca, en Piura. El vínculo con este territorio empezó mucho antes de que fuera reconocido como área de conservación, en 2011. “Nosotros de este bosque vivimos”, repite. La jornada de Guevara no transcurre desde una caseta, como muchos podrían imaginar. Empieza temprano, a veces cuando todavía no ha salido el sol. Puede internarse en el bosque a las cinco de la mañana y regresar recién a las cuatro o cinco de la tarde. Durante horas recorre a pie sectores como El Oso, La Caña Brava o El Guabo. En el camino, el aroma del palo santo acompaña parte del recorrido entre hualtacos y pasallos, mientras el ganado avanza entre los árboles y, en algún punto del bosque, se esconden venados, pumas, sajinos y la pava aliblanca, un ave endémica y en peligro de extinción que tiene aquí su hábitat. Mientras camina, el hombre también busca las huellas de quienes entran al bosque para depredarlo. Una de sus tareas es detectar la extracción ilegal de especies como el palo santo y reportarla. “La gente lo extrae, se lo lleva para el mercado. Lo cortan verde y lo dejan que se seque”, cuenta. Un árbol menos puede parecer poco frente a la extensión del paisaje, pero la extracción repetida durante años es precisamente una de las presiones que enfrenta este ecosistema. El bosque que vigila es apenas una parte de uno mucho mayor. Los bosques secos ocupan 3.422.904 hectáreas entre Tumbes, Piura, Lambayeque y La Libertad. Su apariencia cambia con el agua: durante largos periodos secos pierden verdor y, cuando regresan las lluvias, semillas que permanecían en el suelo germinan y la vegetación vuelve a abrirse paso. Sin embargo, detrás de esa capacidad para recuperarse existe una realidad mucho más compleja: alrededor del 95% de estos bosques se encuentra degradado por procesos históricos de fragmentación y pérdida de cobertura. El Comercio viajó hasta Piura para conocer qué se está haciendo para conservar y recuperar este ecosistema. La visita se realizó durante el X Congreso Regional Forestal (COREFOR), un espacio que reúne investigaciones y experiencias vinculadas a la gestión de los bosques. Pero el viaje fue más allá de las exposiciones. Permitió internarse en uno de estos territorios y conocer el trabajo que ocurre todos los días lejos de los auditorios: guardaparques que recorren durante horas el bosque, comunidades que intentan recuperar zonas degradadas, especies que luchan por conservar su hábitat y alternativas productivas que parten de una misma idea, que quienes viven del bosque puedan seguir haciéndolo sin acabar con él. Un ecosistema degradado que vuelve a reverdecer Ese bosque que José Guevara recorre desde hace décadas no luce igual durante todo el año. En septiembre, cuando El Comercio ingresó a Salitral-Huarmaca, buena parte del camino estaba dominado por tonos secos, ramas desnudas y un suelo que levantaba polvo con cada paso. Es una imagen que puede resultar engañosa para quien llega por primera vez. Aunque se les conoce simplemente como bosques secos, su denominación técnica es “bosques estacionalmente secos”. Mirbel Epiquién, director general de Diversidad Biológica del Ministerio del Ambiente (Minam), explicó que la sequedad forma parte de un ciclo y que, durante las temporadas de lluvia, un territorio aparentemente árido puede volver a cubrirse de vegetación. “En realidad el nombre técnico es bosques estacionalmente secos del norte del Perú. Hay épocas normales de lluvias en donde comienzan a reverdecer”, explicó. La transformación puede ser considerable. Las lluvias intensas asociadas a fenómenos como El Niño, pese a los daños que pueden ocasionar en las ciudades del norte, favorecen dentro del bosque la recarga de acuíferos, la germinación de semillas y la recuperación de cobertura vegetal. “El fenómeno de El Niño tiene un efecto negativo sobre las actividades económicas en general, pero tiene un efecto muy positivo en recarga de acuífero, ampliación del bosque y demás”, señaló Anton Willems, director ejecutivo de Profonanpe. Epiquién explica esa respuesta a partir de la resiliencia del propio ecosistema. Incluso después de largos periodos sin agua, permanecen semillas capaces de germinar cuando vuelven a encontrar las condiciones necesarias. “Viene la lluvia y las semillas comienzan a germinar nuevamente. Los árboles también comienzan a protegerse entre ellos, dándole cobijo, refugio a otros arbolitos”, señaló. Esa capacidad, agregó, permite que el bosque resista amenazas naturales y aquellas provocadas por la actividad humana. Ayudar al bosque a recuperarse Pero que el bosque sea capaz de reverdecer no significa que pueda recuperarse solo de décadas de degradación. En los mismos caminos que recorre Guevara, el ganado se desplaza libremente entre los árboles. Vacas y cabras forman parte del paisaje y también de la economía de las familias, pero para un brote que apenas empieza a crecer pueden convertirse en una amenaza. Por eso, en algunos pilotos de restauración se dispersaron semillas antes de las lluvias y luego se protegieron las nuevas plantas. Sergio Lazo, coordinador del proyecto Bosque Seco, explica que las comunidades utilizan ramas para construir pequeñas estructuras alrededor de los brotes. Las llaman “nodrizas”. “Las semillas, el árbol crece y está la presión de sus mismos animales. Entonces, se les ha enseñado que eso lo tienen que proteger con unas ramas y eso se llama nodrizas”, explicó Lazo. La protección permanece hasta que el árbol alcanza una altura suficiente para reducir el riesgo de ser consumido. La escena ayuda a entender una de las dificultades de recuperar este ecosistema: aquello que se busca conservar convive con las actividades de quienes dependen de él. Y esa relación no necesariamente tiene que ser negativa. Cuando llegan las lluvias hay más alimento para el ganado, aumenta la floración y también puede mejorar la producción de miel. “Es una oportunidad porque se alimentan mejor los animales de los que viven las comunidades. Hay mejor floración, hay mejor miel. Esas comunidades que viven de esos animales producen mejor queso, hay mejor ingreso económico”, señaló Lazo. Recuperar caminos Durante el recorrido por Salitral-Huarmaca, los guardaparques pidieron guardar silencio en algunos tramos. La razón estaba en algún punto entre los árboles: la pava aliblanca. El ave, endémica y en peligro de extinción, necesita del bosque para alimentarse, reproducirse y desplazarse. Ese movimiento ayuda a entender por qué restaurar no significa solamente plantar árboles. Visto desde arriba, buena parte de las áreas conservadas aparecen como “manchones” separados entre sí. Para la fauna, la distancia entre uno y otro puede significar la pérdida de un corredor que antes formaba parte de un mismo hábitat. “Si tú ves en un mapa las áreas naturales, vas a ver manchones que son las áreas protegidas. En el tema de conectividad, lo que busca este componente es cómo esos manchones, que parecen mosaicos dispersos, comienzan a conectarse de manera que las especies puedan trasladarse de un lado a otro”, explicó Lazo. El proyecto Bosque Seco ha alcanzado acuerdos sobre unas 42.000 hectáreas para favorecer esa conectividad y tiene como objetivo llegar a 80.000. Además, cerca de 1.900 hectáreas se encuentran en proceso de restauración frente a una meta de 2.278. Las intervenciones involucran a 16 comunidades campesinas. Epiquién advierte que por eso el resultado no puede medirse únicamente contando hectáreas recuperadas. La ubicación también importa. Restaurar un espacio entre dos fragmentos puede volver a abrir el paso para animales y permitir que las semillas encuentren vegetación, humedad y condiciones para desarrollarse. “Un bosque necesita tener conectividad, es decir, continuidad, para que pueda haber flujos, sobre todo de especies de fauna”, señaló. “Por eso tenemos que garantizar que haya un corredor. Eso se llama corredores de bosque”. Vivir del bosque sin acabar con él La caminata también deja claro algo que las cifras no siempre muestran. Este no es un territorio aislado de las personas. Hay ganado entre los árboles, guardaparques que pertenecen a las propias comunidades y familias que durante generaciones han encontrado aquí alimento y recursos. El propio Guevara lo resumió al iniciar el recorrido: “Nosotros de este bosque vivimos”. Por eso, recuperar el bosque sin ofrecer alternativas a quienes dependen de él sería resolver solo una parte del problema. El proyecto trabaja en cerca de 60 intervenciones, 34 de ellas vinculadas a restauración, y busca que ese proceso avance junto con actividades económicas asociadas a los propios recursos del ecosistema. “Vamos a hacer la restauración, comenzamos a armar el piloto y vamos haciendo la actividad productiva también a la paralela”, explicó Lazo. El algarrobo, la ganadería caprina y la producción de miel forman parte de esa relación histórica. A ellas se suman el turismo, la meliponicultura, el aprovechamiento de fibras naturales y otras actividades que buscan generar ingresos sin perder de vista la conservación. En Piura, durante el I Festival Bosque Seco, 30 asociaciones mostraron parte de ese trabajo. Había miel de abeja y de meliponas, algarrobina, derivados lácteos de leche de cabra, cacao y artesanías. Productos distintos nacidos de un mismo territorio. Para Willems, allí está uno de los principales retos. “La economía en el norte es un boom y eso es algo que deberíamos aplaudir. Pero solamente va a ser sostenible si esa economía te permite disfrutar de un ambiente sano, si te permite disfrutar de los servicios ecosistémicos que necesitamos”, sostuvo. Del palo santo a las abejas sin aguijón Horas después de haber iniciado la caminata con las estrellas todavía sobre nuestras cabezas, el sol ya caía con fuerza sobre Serrán. El recorrido terminó por llevarnos hasta el vivero, donde la conservación adquiría una escala mucho más pequeña: en un espacio acondicionado, varias cajas de madera resguardaban colonias de abejas nativas. Son meliponas y otras especies que comparten una característica particular: no tienen aguijón. Cumplen un papel importante como polinizadoras y algunas forman naturalmente sus enjambres dentro de árboles como el palo santo y el hualtaco. El palo santo vuelve a aparecer aquí, pero desde otro ángulo. Es el mismo árbol cuyo aroma acompañó buena parte de la caminata y uno de los que Guevara vigila para evitar que sea cortado ilegalmente. También puede convertirse en refugio para abejas necesarias para el propio bosque. María Adriana Requena Moscol, bióloga que trabaja en la jefatura del ACR Salitral-Huarmaca, explica que el palo santo puede ser aprovechado cuando el árbol muere y seca naturalmente. El problema comienza cuando se cortan ejemplares todavía vivos para dejarlos secar y comercializarlos. “De por sí sí se puede aprovechar, pero el palo santo seco. Lo que hacen ellos es cortarlo verde, esperan a que se seque y se lo llevan. Eso es lo que no debería pasar”, explicó. La tala no es la única amenaza que encuentran los guardaparques. Cerca de algunas quebradas, cazadores construyen pequeños escondites desde donde esperan que bajen los venados. Son conocidos como “hornos de cacería” y, cuando son encontrados durante los patrullajes, son destruidos. “Ellos se esconden dentro de estas cuevitas, esperan a que el venado baje y lo cazan. Eso también ellos lo reportan”, explicó Requena. “Aquí no se permite ningún tipo de caza porque es un área protegida. Si hay venado, se espera que se desarrolle libremente, no para consumo”. Frente a esas amenazas, las pequeñas cajas del meliponario representan otra manera de relacionarse con el mismo territorio. En lugar de extraer un árbol vivo, la apuesta es obtener valor de un bosque que permanece en pie. “Ahorita lo que se está haciendo con Bosque Seco es el tema de las meliponas, de las abejas nativas. Se está tratando de que se aproveche como un bionegocio la producción de miel”, explicó Requena. El mismo principio se extiende a otros recursos. La fibra del fruto del ceibo, por ejemplo, puede procesarse para elaborar hilos, textiles y rellenos para almohadas, chalecos o colchones. “Se encuentra dentro del bosque, es un recurso aprovechable”, agregó. La apuesta, finalmente, es que esas actividades crezcan al mismo tiempo que el bosque logra recuperarse. No será un proceso rápido. Guevara lo sabe después de casi cuatro décadas caminando entre estos árboles: conservar implica vigilar lo que permanece, pero también darle tiempo a aquello que intenta volver a crecer. “Restaurar una hectárea de bosque seco es un proceso que toma muchísimos años; sin embargo, tienes que hacerlo”, resumió Willems.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/detienen-a-tres-policias-por-cobros-irregulares-en-la-matanza/</t>
+          <t>https://elcomercio.pe/peru/mas-de-3-millones-de-hectareas-de-bosque-seco-resisten-en-el-norte-la-lucha-por-recuperar-un-ecosistema-degradado-noticia/</t>
         </is>
       </c>
     </row>
@@ -2303,17 +2191,17 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Erradican motocicletas de vías públicas en Complejo de Mercados</t>
+          <t>Sechura, en pie de lucha para evitar futura inundación</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>La Municipalidad Provincial de Piura intenta reordenar el Complejo de Mercados. Esta vez personal municipal realizó un operativo de recuperación de espacios públicos en el jirón Gonzalo Farfán y sectores colindantes. Para ello procedieron con el retiro de motocicletas estacionadas en zonas prohibidas, a fin de garantizar una circulación en el principal centro de abastos. Ruth Oliva, gerente de Desarrollo Económico y Servicios Comerciales de la comuna provincial, explicó que estas acciones buscan eliminar los obstáculos que dificultan el desplazamiento de compradores y comerciantes. Asimismo, precisó que los involucrados fueron notificados previamente y que las intervenciones se coordinan con la Policía Nacional del Perú (PNP).</t>
+          <t>Diversas instituciones de Sechura, así como directivos, han decidido levantar su voz de protesta y rechazar la intervención denominada “Limpieza, descolmatación y conformación de bordos con material propio del cauce del río Piura–bifurcación a río Loco”, que cuenta con un presupuesto del gobierno de S/55 millones 639 mil 212.12. El Comité Local de Sechura del Colegio de Ingenieros del Perú rechazó dicha intervención por considerar que el dren Sechura no tiene capacidad para soportar mayores caudales. Para ello hacen mención que en 1998 “con solamente 500 m3/s Sechura se inundó totalmente”, afectando a la población del sector oeste y norte, además de los distritos Cristo Nos Valga, Bernal, y Rinconada Llicuar, además de los sectores productivos. Por ello piden respetar la alternativa contemplada en el Plan Maestro del río Piura que plantea conducir las aguas hacia la zona del Reventazón. En tanto, la Municipalidad de Sechura también emitió un pronunciamiento en el cual dejan en claro que la obra que se pretende ejecutar carece de viabilidad técnica, social y ambiental, y advierten que podría incrementar el riesgo de inundación en otras localidades. Por ello, la comuna solicitó al Ministerio de Desarrollo Agrario y Riego (Midagri), a la Autoridad Nacional del Agua (ANA) y al Gobierno Regional de Piura dejar sin efecto la intervención y convocar una mesa técnica interinstitucional para evaluar alternativas de evacuación de los caudales del río. Por su parte, las Asociaciones Agropecuarias del Valle de Sechura exhortaron a las autoridades “dejar sin efecto los trabajos de conexión del río Piura con el dren 1308 (río Loco)”, en tanto no se demuestre con un estudio técnico que Sechura no correrá ningún riesgo. En tanto, el presidente del Frente de defensa de los pueblos afectados por el Niño Costero, Víctor Chunga, indicó que la población no va permitir el inicio de la obras.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/erradican-motocicletas-de-vias-publicas-en-complejo-de-mercados/</t>
+          <t>https://eltiempo.pe/local/sechura-en-pie-de-lucha-para-evitar-futura-inundacion/</t>
         </is>
       </c>
     </row>
@@ -2328,17 +2216,17 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Essalud en alerta: Reportan 1609 casos de dengue</t>
+          <t>Con paro regional, maestros exigirán pagos de beneficios laborales</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>El incremento de casos de dengue en la región siguen encendiendo las alertas de las autoridades. En este caso, la Red Asistencial Piura de EsSalud reportó un acumulado de 1609 casos de dengue entre sus asegurados, hasta la semana epidemiológica 40. De este reporte total, 1052 casos están confirmados y 557 son probables. Los establecimientos de EsSalud que registran más casos son los de Sullana, con 362; Chulucanas, con 358; y Tambogrande, con 339. Edward Pozo Súclupe, jefe de Inteligencia Sanitaria de la institución, recomendó a los asegurados no automedicarse si presentan síntomas compatibles con el dengue y acudir a un establecimiento de salud para recibir una evaluación médica. En tanto EsSalud sigue con la campaña de vacunación contra el dengue dirigida a la población de 10 a 20 años cumplidos.</t>
+          <t>Los maestros de la región continúan en pie de lucha para exigir el cumplimiento de sus beneficios laborales. Por ello el Sindicato Magisterial (SIMA) de la región Piura, liderado por el dirigente Miguel Puescas, anunció una huelga preventiva de 48 horas que acatarán el próximo 29 y 30 de octubre. Según indicaron, la paralización responde al incumplimiento de compromisos por parte del Gobierno Regional de Piura y de las autoridades nacionales. Puescas sostuvo que las gestiones ante el Ministerio de Educación, el Ministerio de Economía y el Congreso no generaron soluciones efectivas para las demandas del sector. Entre sus demandas figura el pago de la deuda social del 30 % y 35 % por preparación de clases, monto que supera los 80 mil soles por docente y afecta a unos 12 mil profesores con sentencia judicial. El pago de CTS y protestan por el supuesto desvío de aportes descontados para EsSalud, la ONP y las AFP.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/essalud-en-alerta-reportan-1609-casos-de-dengue/</t>
+          <t>https://eltiempo.pe/local/con-paro-regional-maestros-exigiran-pagos-de-beneficios-laborales/</t>
         </is>
       </c>
     </row>
@@ -2353,17 +2241,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Con paro regional, maestros exigirán pagos de beneficios laborales</t>
+          <t>Detienen a tres policías por cobros irregulares en La Matanza</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Los maestros de la región continúan en pie de lucha para exigir el cumplimiento de sus beneficios laborales. Por ello el Sindicato Magisterial (SIMA) de la región Piura, liderado por el dirigente Miguel Puescas, anunció una huelga preventiva de 48 horas que acatarán el próximo 29 y 30 de octubre. Según indicaron, la paralización responde al incumplimiento de compromisos por parte del Gobierno Regional de Piura y de las autoridades nacionales. Puescas sostuvo que las gestiones ante el Ministerio de Educación, el Ministerio de Economía y el Congreso no generaron soluciones efectivas para las demandas del sector. Entre sus demandas figura el pago de la deuda social del 30 % y 35 % por preparación de clases, monto que supera los 80 mil soles por docente y afecta a unos 12 mil profesores con sentencia judicial. El pago de CTS y protestan por el supuesto desvío de aportes descontados para EsSalud, la ONP y las AFP.</t>
+          <t>Tres policías de la Comisaría de La Matanza, de la provincia de Morropón, fueron detenidos por sus colegas de armas y cinco fiscales de la Fecof para ser investigados por el presunto delito de cohecho pasivo propio en el ejercicio de la función policial. La intervención se realizó ayer en estricto cumplimiento a una orden judicial de detención preliminar, allanamiento con descerraje, registro personal, incautación y levantamiento del secreto de las comunicaciones de los tres agentes y civiles. LAS DILIGENCIAS La diligencia fue dirigida por el fiscal provincial Jesús Aranguren Martínez, con la participación de los fiscales adjuntos José Jiménez, Carlos Pizarro (quien tiene a cargo la investigación), Miguel Berrú y Cinthya Janeth Rondoy Bances, y contó con apoyo del personal especializado del Departamento Desconcentrado Contra la Corrupción (Depdicc) y la Dircocor, interviniendo los inmuebles autorizados judicialmente para asegurar elementos probatorios. Los hechos investigados por el Ministerio Público y Policía especializada habrían ocurrido entre el 23 y 24 de marzo último, luego que una ciudadana acudiera a la Comisaría La Matanza para denunciar haber sido víctima de un presunto delito de agresión sexual. LOS INVESTIGADOS Durante la intervención, el suboficial de segunda de la Policía Nacional, D. P. C.; suboficial de segunda, J. H. C. J.; y el suboficial de tercera de la Policía Nacional, O. A. I. con los presuntos agresores (denunciados) V. H. S. A. y H. A. R. R., habrían coordinado presuntos cobros e intercambios de dinero indebidos, utilizando el aplicativo Yape y cuentas bancarias. Todo esto habría sido utilizado para concertar pagos irregulares, a fin que la agraviada no continúe con la denuncia. Asimismo, se atribuye a los efectivos policiales involucrados haber utilizado el vehículo policial asignado a la dependencia para trasladar a la agraviada fuera de su jurisdicción hasta la ciudad de Piura, entregándole parte del dinero recolectado en efectivo y realizando depósitos bancarios para que no continuara con la grave denuncia sentada por una joven.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/con-paro-regional-maestros-exigiran-pagos-de-beneficios-laborales/</t>
+          <t>https://eltiempo.pe/local/detienen-a-tres-policias-por-cobros-irregulares-en-la-matanza/</t>
         </is>
       </c>
     </row>
@@ -2378,17 +2266,17 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sechura, en pie de lucha para evitar futura inundación</t>
+          <t>Erradican motocicletas de vías públicas en Complejo de Mercados</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Diversas instituciones de Sechura, así como directivos, han decidido levantar su voz de protesta y rechazar la intervención denominada “Limpieza, descolmatación y conformación de bordos con material propio del cauce del río Piura–bifurcación a río Loco”, que cuenta con un presupuesto del gobierno de S/55 millones 639 mil 212.12. El Comité Local de Sechura del Colegio de Ingenieros del Perú rechazó dicha intervención por considerar que el dren Sechura no tiene capacidad para soportar mayores caudales. Para ello hacen mención que en 1998 “con solamente 500 m3/s Sechura se inundó totalmente”, afectando a la población del sector oeste y norte, además de los distritos Cristo Nos Valga, Bernal, y Rinconada Llicuar, además de los sectores productivos. Por ello piden respetar la alternativa contemplada en el Plan Maestro del río Piura que plantea conducir las aguas hacia la zona del Reventazón. En tanto, la Municipalidad de Sechura también emitió un pronunciamiento en el cual dejan en claro que la obra que se pretende ejecutar carece de viabilidad técnica, social y ambiental, y advierten que podría incrementar el riesgo de inundación en otras localidades. Por ello, la comuna solicitó al Ministerio de Desarrollo Agrario y Riego (Midagri), a la Autoridad Nacional del Agua (ANA) y al Gobierno Regional de Piura dejar sin efecto la intervención y convocar una mesa técnica interinstitucional para evaluar alternativas de evacuación de los caudales del río. Por su parte, las Asociaciones Agropecuarias del Valle de Sechura exhortaron a las autoridades “dejar sin efecto los trabajos de conexión del río Piura con el dren 1308 (río Loco)”, en tanto no se demuestre con un estudio técnico que Sechura no correrá ningún riesgo. En tanto, el presidente del Frente de defensa de los pueblos afectados por el Niño Costero, Víctor Chunga, indicó que la población no va permitir el inicio de la obras.</t>
+          <t>La Municipalidad Provincial de Piura intenta reordenar el Complejo de Mercados. Esta vez personal municipal realizó un operativo de recuperación de espacios públicos en el jirón Gonzalo Farfán y sectores colindantes. Para ello procedieron con el retiro de motocicletas estacionadas en zonas prohibidas, a fin de garantizar una circulación en el principal centro de abastos. Ruth Oliva, gerente de Desarrollo Económico y Servicios Comerciales de la comuna provincial, explicó que estas acciones buscan eliminar los obstáculos que dificultan el desplazamiento de compradores y comerciantes. Asimismo, precisó que los involucrados fueron notificados previamente y que las intervenciones se coordinan con la Policía Nacional del Perú (PNP).</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/sechura-en-pie-de-lucha-para-evitar-futura-inundacion/</t>
+          <t>https://eltiempo.pe/local/erradican-motocicletas-de-vias-publicas-en-complejo-de-mercados/</t>
         </is>
       </c>
     </row>
@@ -2399,21 +2287,21 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bajo extrema reserva se investiga violación contra una menor en aula de colegio en Talara</t>
+          <t>Talara: Se complica investigación de presunto abuso en aula de colegio</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Con total hermetismo y bajo estrictas medidas de seguridad las autoridades del Ministerio Público, en coordinación con el personal de criminalística de la comisaría de Talara Baja llevan a cabo las pesquisas sobre el presunto abuso sexual cometido hace una semana a una menor escolar en el interior de un aula de la I. E. N.o 15038 “Santa Rosa de Lima”. A pesar de que el preocupante caso se maneja bajo siete llaves, LA HORA tuvo conocimiento que las diligencias, a cargo de la fiscal de familia Eliana Ríos, se llevan bajo los protocolos de protección integral a favor de la estudiante, no sin antes haberse realizado -después de la demanda- la respectiva inspección en los ambientes del colegio estatal, con el propósito de establecer el horario, el modo del presunto abuso sexual, los autores y posibles cómplices. Asimismo, se supo que las autoridades mencionadas están llevando con suma cautela las pericias médicas a favor de la menor, quien al parecer se encuentra bajo tratamiento psicológico, para luego proceder a la plena identificación de los presuntos autores y otros implicados del ataque sexual. ENOJO COLECTIVO Tras revelarse la agresión sexual en manada cometida contra una menor de edad escolar, los padres de familia señalaron que lo ocurrido es una muestra clara de las deficiencias administrativas de la institución educativa donde prima una severa falta de control interno y desorden institucional.</t>
+          <t>Las investigaciones sobre el sonado caso de un presunto abuso sexual contra una escolar en el interior de la I. E. “Santa Rosa de Lima” podría dar un inesperado giro debido a que, mientras avanzan las pesquisas que llevan a cabo el Ministerio Público y la Policía, los exámenes médicos legales practicados a la potencial víctima obligarían a replantear las acusaciones. LA HORA conoció que el resultado del examen físico practicado a la menor fue negativo para desfloración himeneal, pero sí se encontró desfloración antigua, sin evidencia de lesiones traumáticas recientes, por lo que llevaría a reevaluar la tipificación de los hechos y orientar la búsqueda de pruebas complementarias. Esto podría darse con los resultados de los exámenes psicológicos practicados a la escolar. Este diario también obtuvo información referente a la identificación de los presuntos involucrados. La menor reconoció con precisión a sus dos compañeras de clases, quienes serían las que -según su versión- la engañaron y sujetaron en el interior del aula, pero no logra identificar a los varones, entre seis a ocho, que habrían intentado agredirla. DEFENSORÍA Por su parte, la Defensoría del Pueblo ha intervenido de oficio tras tomar conocimiento de la presunta agresión sexual sufrida por una estudiante en la institución educativa “Santa Rosa de Lima”. La institución recomendó cumplir con el registro obligatorio en el libro de incidencias y el portal SíSeVe. En ese sentido recordó que los colegios deben priorizar el bienestar de los educandos.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/bajo-extrema-reserva-se-investiga-violacion-contra-una-menor-en-aula-de-colegio-en-talara/</t>
+          <t>https://eltiempo.pe/local/talara-se-complica-investigacion-de-presunto-abuso-en-aula-de-colegio/</t>
         </is>
       </c>
     </row>
@@ -2424,21 +2312,21 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Detectan más de S/500 millones sin sustento: Municipalidad de Piura anuncia correctivos</t>
+          <t>Detienen en Piura a médico gastroenterólogo sentenciado por violación</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>El informe de auditoría financiera N.° 018-2026-3-0446-DF ha puesto en la mira a la Municipalidad Provincial de Piura por la advertencia de inconsistencias en sus cuentas y por más de S/500 millones que no habrían sido sustentados. Según el informe, las observaciones incluyen S/120.563.241,36 de cuentas por cobrar con el SATP, S/8.551 275,54 por suministros y bienes de almacén, S/160.250 661,94 por concepto de infraestructura educativa, agua y saneamiento no transferidas, S/58.130 926,30 por obras concluidas que todavía figurarían contablemente como proyectos en construcción, y S/ 116.119.603,12 por provisiones por beneficios sociales, incluida la CTS de trabajadores. La comuna informa que las observaciones señaladas no constituyen, por sí solas, pruebas de delitos o actos de corrupción. En todo caso anuncian medidas correctivas y que los puntos identificados corresponden a aspectos técnicos, administrativos y contables que requieren conciliaciones, actualización de información y regularización de saldos. Asimismo,indican que se encuentra ejecutando un plan de acción para atender las observaciones conforme a la normativa vigente.</t>
+          <t>La Policía Nacional del Perú (PNP) capturó en Piura al médico gastroenterólogo Luis Enrique Vásquez Elera , quien registraba una condena de 18 años de prisión por el delito de violación sexual y una orden de captura vigente. El profesional fue intervenido por agentes de la División de Investigación Criminal (Divincri) cuando se encontraba en el consultorio de una clínica local, donde atendía a sus pacientes. Según informó el jefe de la Divincri Piura, coronel PNP Javier Méndez, el sentenciado era requerido por la justicia desde 2023, en virtud de una orden emitida por un órgano jurisdiccional de Lima. Tras verificar su identidad y confirmar el mandato judicial, los efectivos procedieron con su detención para ponerlo a disposición de las autoridades competentes. ¿Cómo fue la captura del médico sentenciado en Piura? La intervención policial se realizó al interior del consultorio médico donde trabajaba Vásquez Elera. De acuerdo con la información proporcionada por la Policía, el personal de la Divincri llegó al establecimiento para verificar la identidad del profesional, quien era buscado por las autoridades judiciales. Durante el procedimiento, el médico se habría negado inicialmente a identificarse e intentado evitar la verificación de sus documentos. Sin embargo, los agentes continuaron con las diligencias correspondientes y corroboraron sus datos en los sistemas policiales. Una vez confirmada la existencia de la orden de captura, los efectivos ejecutaron la intervención. El caso llamó la atención debido a que el sentenciado se encontraba trabajando en la región norte del país pese a la condena impuesta por la justicia. El coronel PNP Javier Méndez señaló que el mandato judicial había sido emitido en 2023 por un juzgado de Lima. Según la información policial, el intervenido habría utilizado identidades falsas para mantenerse fuera del alcance de las autoridades, un aspecto que deberá ser esclarecido mediante las diligencias correspondientes. ¿Por qué condenaron a 18 años de prisión a Luis Vásquez Elera? La condena contra el gastroenterólogo fue impuesta por la Corte Superior de Justicia de Lima Norte por la violación sexual de la madre de su hijo. Los hechos ocurrieron la noche del 18 de diciembre de 2021, en la vivienda de la agraviada, ubicada en el distrito limeño de San Martín de Porres. De acuerdo con la información publicada por La República sobre el proceso judicial, el tribunal determinó que el acusado empleó fuerza física para cometer el delito. Durante el juicio se evaluaron distintos elementos probatorios, entre ellos grabaciones de video, conversaciones registradas y pericias psicológicas relacionadas con el testimonio de la víctima. La relación entre ambos había sido sentimental y de ella nació un hijo en 2016. Sin embargo, según los antecedentes expuestos durante el proceso, la pareja ya no mantenía una relación estable cuando ocurrieron los hechos denunciados. Durante el juicio, la defensa del acusado sostuvo que anteriormente habían existido encuentros íntimos entre ambos. No obstante, el órgano jurisdiccional consideró que esa afirmación no acreditaba el consentimiento de la agraviada para el acto ocurrido el 18 de diciembre de 2021. ¿Por qué la pena se redujo de 20 a 18 años? Inicialmente, el Ministerio Público solicitó una pena de 20 años de prisión. Sin embargo, el Juzgado Penal Colegiado Transitorio de Lima Norte impuso una condena de 18 años, teniendo en cuenta el principio del interés superior del niño, debido a que el sentenciado tiene un hijo menor de edad en común con la agraviada. La decisión judicial también incluyó otras medidas. Según los detalles difundidos sobre la sentencia, Vásquez Elera recibió 10 años de inhabilitación para acercarse o comunicarse con la víctima y deberá pagar S/ 7.000 por concepto de reparación civil. Asimismo, se dispuso que el condenado se someta a tratamiento terapéutico como parte de las medidas vinculadas a su proceso de readaptación social. Las pruebas consideradas durante el proceso judicial Uno de los aspectos relevantes del caso fue la valoración de las grabaciones realizadas por la agraviada. Según los antecedentes difundidos sobre el juicio, parte de los registros contenía imágenes del hecho y conversaciones posteriores en las que el sentenciado pedía perdón y hacía referencia a la posibilidad de ir a prisión. Estos elementos fueron considerados por el tribunal junto con las demás pruebas presentadas durante el proceso. La sentencia también abordó los argumentos de la defensa relacionados con un conflicto familiar previo, incluidos asuntos vinculados con la manutención del menor. Los jueces concluyeron que dicho antecedente no constituía, por sí mismo, una razón suficiente para considerar falsa la denuncia. El tribunal también remarcó que una relación sentimental previa o la existencia de encuentros íntimos anteriores no implican consentimiento para una relación sexual posterior. ¿Qué pasará con el médico detenido en Piura? Tras su captura, el médico fue trasladado bajo medidas de seguridad y se informó que sería conducido a Lima para quedar a disposición del órgano jurisdiccional correspondiente y cumplir la condena impuesta. La intervención estuvo a cargo de agentes de la Divincri de Piura, unidad policial que realizó las verificaciones necesarias para ejecutar el mandato judicial. La situación del detenido deberá continuar por los canales legales establecidos para el cumplimiento de las sentencias penales. La Policía también señaló que el profesional se encontraba ejerciendo labores médicas pese a registrar una condena judicial. Las circunstancias relacionadas con su identidad y su permanencia fuera del alcance de las autoridades forman parte de los aspectos que deberán ser esclarecidos por las instancias competentes.</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/detectan-mas-de-s-500-millones-sin-sustento-municipalidad-de-piura-anuncia-correctivos/</t>
+          <t>https://eltiempo.pe/local/detienen-en-piura-a-medico-gastroenterologo-sentenciado-por-violacion/</t>
         </is>
       </c>
     </row>
@@ -2449,21 +2337,21 @@
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Primera procesión del Señor de los Milagros partirá hoy desde la capilla La Merced</t>
+          <t>Candidato Guillermo La Torre se mantiene en segundo lugar y sería rival de Hilbck</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Hoy se realizará el primer recorrido procesional del Señor de los Milagros. La sagrada imagen será llevada en hombros por los miembros de la Hermandad del Señor de los Milagros desde la Capilla Nuestra Señora de la Merced (Capilla Arzobispal), hacia la Basílica Catedral De Piura. El traslado será desde la calle Libertad, Apurímac, Lima, Ayacucho, Tacna hasta llegar a la Basílica Catedral de Piura. De esta manera los fieles podrán acompañar la sagrada imagen, como parte de una tradición de profunda fe y devoción la cual congrega a cientos de fieles de votos. El 18 de octubre se realizará la segunda procesión y se ha previsto que la imagen ingrese a la parroquita Cruz del Norte. El 19 y 28 de de octubre se ha previsto dos procesiones más. El último recorrido está previsto para el 1 de noviembre y marcará el retorno de la venerada imagen a la Capilla Arzobispal.</t>
+          <t>En 1,953 votos se fijó la diferencia entre el candidato de Podemos, Guillermo La Torre, y el postulante de Somos Perú, Santiago Paz, quienes pugnan por llegar a la segunda vuelta electoral programada para el 6 de diciembre. Así consta en la página oficial de la ONPE. Según el reporte de la ONPE actualizado al 97.206% que mantenía al candidato Reynaldo Hilbck en primer lugar con 21.992%, segundo lugar Podemos con 18.039% (174,813 votos) y Somos Perú con 17.837% (132,860 votos). Esto según el reporte de la ONPE actualizado al 97.206% que mantenía al candidato Reynaldo Hilbck en primer lugar con 21.992%, segundo lugar Podemos con 18.039% (174.813 votos) y Somos Perú con 17.837% (132.860 votos). Según la información oficial, existen 147 actas para envío al Jurado Electoral Especial; mientras que actas pendientes ya no se registran en el sistema de ONPE. SUPUESTO FRAUDE En tanto, la actualización del reporte de la ONPE avanza con lentitud, ayer el candidato Santiago Paz y simpatizantes de Somos Perú protestaron en horas de la tarde en los exteriores del Ministerio Público, en la calle Lima de Piura. El candidato insistió en señalar un supuesto fraude en las elecciones realizadas el 4 de octubre y cuestionó la nulidad de las elecciones en San Juan de Bigote. Asimismo, Paz demandó a la Fiscalía celeridad en las investigaciones para identificar aquellos que vulneraron el proceso electoral. “Ya deberían estar en prisión porque lo que han hecho es sumamente grave”, dijo.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/primera-procesion-del-senor-de-los-milagros-partira-hoy-desde-la-capilla-la-merced/</t>
+          <t>https://eltiempo.pe/local/candidato-guillermo-la-torre-se-mantiene-en-segundo-lugar-y-seria-rival-de-hilbck/</t>
         </is>
       </c>
     </row>
